--- a/docs/xlsx/jobs-2026-10-09.xlsx
+++ b/docs/xlsx/jobs-2026-10-09.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="949" uniqueCount="630">
   <si>
     <t>Title</t>
   </si>
@@ -38,13 +38,1879 @@
   </si>
   <si>
     <t>Link</t>
+  </si>
+  <si>
+    <t>Animal Care Specialist</t>
+  </si>
+  <si>
+    <t>Edisto Beach State Park</t>
+  </si>
+  <si>
+    <t>Edisto Island, SC</t>
+  </si>
+  <si>
+    <t>Temporary</t>
+  </si>
+  <si>
+    <t>$12 per hour</t>
+  </si>
+  <si>
+    <t>wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-animal-care-specialist-edisto-island-south-carolina/3643340562</t>
+  </si>
+  <si>
+    <t>Assistant Project Biologist</t>
+  </si>
+  <si>
+    <t>SWCA Environmental Consultants</t>
+  </si>
+  <si>
+    <t>Austin, TX</t>
+  </si>
+  <si>
+    <t>Permanent</t>
+  </si>
+  <si>
+    <t>$28.67 - $37.40 per hour</t>
+  </si>
+  <si>
+    <t>ecology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-assistant-project-biologist-austin-texas/1338512061</t>
+  </si>
+  <si>
+    <t>Assistant/Associate Professor of Biology - Plant</t>
+  </si>
+  <si>
+    <t>Adams State University</t>
+  </si>
+  <si>
+    <t>Alamosa, CO</t>
+  </si>
+  <si>
+    <t>Faculty / Postdoc</t>
+  </si>
+  <si>
+    <t>$50,469 - $73,578 per year</t>
+  </si>
+  <si>
+    <t>botany</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-assistantassociate-professor-of-biology---plant-alamosa-colorado/2541316499</t>
+  </si>
+  <si>
+    <t>Chief Product Officer</t>
+  </si>
+  <si>
+    <t>SERCA administered by North Carolina Zoological Society</t>
+  </si>
+  <si>
+    <t>Global, Remote</t>
+  </si>
+  <si>
+    <t>$80,000 - $100,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-chief-product-officer-global-remote/6392014033</t>
+  </si>
+  <si>
+    <t>Community Engagement Manager</t>
+  </si>
+  <si>
+    <t>Champlain Area Trails</t>
+  </si>
+  <si>
+    <t>Westport, NY</t>
+  </si>
+  <si>
+    <t>$52,000 - $58,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-community-engagement-manager-westport-new-york/3055311414</t>
+  </si>
+  <si>
+    <t>Computer Scientist - Acoustic Telemetry Data Processing</t>
+  </si>
+  <si>
+    <t>Pacific States Marine Fisheries Commission</t>
+  </si>
+  <si>
+    <t>Cook, WA</t>
+  </si>
+  <si>
+    <t>$38.69 - $60.28 per hour</t>
+  </si>
+  <si>
+    <t>fisheries</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-computer-scientist---acoustic-telemetry-data-processing-cook-washington/5740401675</t>
+  </si>
+  <si>
+    <t>Cultural Resources Technician- Temporary</t>
+  </si>
+  <si>
+    <t>Phoenix, AZ</t>
+  </si>
+  <si>
+    <t>$19.31 - $25.49 per hour</t>
+  </si>
+  <si>
+    <t>general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-cultural-resources-technician--temporary-phoenix-arizona/3726541440</t>
+  </si>
+  <si>
+    <t>Customer Services Specialist (Office Specialist 1)</t>
+  </si>
+  <si>
+    <t>Oregon Dept. of State Lands</t>
+  </si>
+  <si>
+    <t>Salem, OR</t>
+  </si>
+  <si>
+    <t>$3,513 - $4,519 per month</t>
+  </si>
+  <si>
+    <t>admin-leadership</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-customer-services-specialist-office-specialist-1-salem-oregon/2582049953</t>
+  </si>
+  <si>
+    <t>Data Management Specialist 2- Natural Coordinated Assessments and StreamNet</t>
+  </si>
+  <si>
+    <t>Boise, ID</t>
+  </si>
+  <si>
+    <t>$24.26 - $38.58 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-data-management-specialist-2--natural-coordinated-assessments-and-streamnet-boise-idaho/5938322667</t>
+  </si>
+  <si>
+    <t>Director of Education</t>
+  </si>
+  <si>
+    <t>Boyce Thompson Arboretum</t>
+  </si>
+  <si>
+    <t>Superior, AZ</t>
+  </si>
+  <si>
+    <t>$75,000 - $80,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-environmental-education</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-director-of-education-superior-arizona/7564424769</t>
+  </si>
+  <si>
+    <t>Director of Land Conservation</t>
+  </si>
+  <si>
+    <t>Cibolo Center for Conservation</t>
+  </si>
+  <si>
+    <t>Boerne, TX</t>
+  </si>
+  <si>
+    <t>$75,000 - $100,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-director-of-land-conservation-boerne-texas/6005698582</t>
+  </si>
+  <si>
+    <t>Director of Land Protection</t>
+  </si>
+  <si>
+    <t>Big Waters Land Trust</t>
+  </si>
+  <si>
+    <t>Osprey, FL</t>
+  </si>
+  <si>
+    <t>admin-leadership-general-stewardship-land-trust</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-director-of-land-protection-osprey-florida/8387564011</t>
+  </si>
+  <si>
+    <t>District Technician</t>
+  </si>
+  <si>
+    <t>Burke Soil Conservation District</t>
+  </si>
+  <si>
+    <t>Bowbells, ND</t>
+  </si>
+  <si>
+    <t>$24/hr</t>
+  </si>
+  <si>
+    <t>general-stewardship-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-district-technician-bowbells-north-dakota/5704001239</t>
+  </si>
+  <si>
+    <t>Farmland Protection Specialist</t>
+  </si>
+  <si>
+    <t>Western New York Land Conservancy Inc.</t>
+  </si>
+  <si>
+    <t>East Aurora, NY</t>
+  </si>
+  <si>
+    <t>$58,500 - $68,500 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-farmland-protection-specialist-east-aurora-new-york/9330294883</t>
+  </si>
+  <si>
+    <t>Fish Hatchery Technician</t>
+  </si>
+  <si>
+    <t>Northern Southeast Regional Aquaculture Associaition</t>
+  </si>
+  <si>
+    <t>Sitka, AK</t>
+  </si>
+  <si>
+    <t>$17 - $21 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-fish-hatchery-technician-sitka-alaska/5547167224</t>
+  </si>
+  <si>
+    <t>Fishery Biologist 2- Snake River Monitoring</t>
+  </si>
+  <si>
+    <t>$66,505 - $104,610 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-fishery-biologist-2--snake-river-monitoring-cook-washington/7878693714</t>
+  </si>
+  <si>
+    <t>Forestry Specialist | St Petersburg, FL</t>
+  </si>
+  <si>
+    <t>ACRT Inc</t>
+  </si>
+  <si>
+    <t>St. Petersburg, FL</t>
+  </si>
+  <si>
+    <t>Based on Experience</t>
+  </si>
+  <si>
+    <t>forestry</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-forestry-specialist--st-petersburg-fl-st-petersburg-florida/3910452559</t>
+  </si>
+  <si>
+    <t>Great Lakes Communications Fellowship</t>
+  </si>
+  <si>
+    <t>Great Lakes Observing System (GLOS)</t>
+  </si>
+  <si>
+    <t>Ann Arbor, MI</t>
+  </si>
+  <si>
+    <t>$40,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-great-lakes-communications-fellowship-ann-arbor-michigan/7370221376</t>
+  </si>
+  <si>
+    <t>Great Lakes Engagement Fellowship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-great-lakes-engagement-fellowship-ann-arbor-michigan/6391675661</t>
+  </si>
+  <si>
+    <t>Intern - Naturalist (Summer)</t>
+  </si>
+  <si>
+    <t>Custer State Park</t>
+  </si>
+  <si>
+    <t>Custer, SD</t>
+  </si>
+  <si>
+    <t>$18.83 per hour</t>
+  </si>
+  <si>
+    <t>environmental-education</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-intern---naturalist-summer-custer-south-dakota/8589881425</t>
+  </si>
+  <si>
+    <t>K-12 Program Coordinator</t>
+  </si>
+  <si>
+    <t>Great Mountain Forest</t>
+  </si>
+  <si>
+    <t>Norfolk, CT</t>
+  </si>
+  <si>
+    <t>$26 per hour</t>
+  </si>
+  <si>
+    <t>admin-leadership-environmental-education-forestry</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-k-12-program-coordinator-norfolk-connecticut/3568752151</t>
+  </si>
+  <si>
+    <t>Office Manager</t>
+  </si>
+  <si>
+    <t>$25 - $30 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-office-manager-norfolk-connecticut/3679012372</t>
+  </si>
+  <si>
+    <t>Program Director</t>
+  </si>
+  <si>
+    <t>Freshwater Society</t>
+  </si>
+  <si>
+    <t>Saint Paul, MN</t>
+  </si>
+  <si>
+    <t>$90,000 - $107,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-hydrology-policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-program-director-saint-paul-minnesota/1396657586</t>
+  </si>
+  <si>
+    <t>Rare Carnivore Monitoring Field Technician</t>
+  </si>
+  <si>
+    <t>Swan Valley Connections</t>
+  </si>
+  <si>
+    <t>Condon, MT</t>
+  </si>
+  <si>
+    <t>$20 per hour</t>
+  </si>
+  <si>
+    <t>ecology-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-rare-carnivore-monitoring-field-technician-condon-montana/6004809425</t>
+  </si>
+  <si>
+    <t>Regional Manager, Southeast</t>
+  </si>
+  <si>
+    <t>Forest Stewardship Council</t>
+  </si>
+  <si>
+    <t>Atlanta, GA</t>
+  </si>
+  <si>
+    <t>$90,000 - $110,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-forestry-sustainability</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-regional-manager-southeast-atlanta-georgia/2998147833</t>
+  </si>
+  <si>
+    <t>Senior Preserve Manager</t>
+  </si>
+  <si>
+    <t>Westchester Land Trust</t>
+  </si>
+  <si>
+    <t>Bedford Hills, NY</t>
+  </si>
+  <si>
+    <t>$78,000 - $82,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-senior-preserve-manager-bedford-hills-new-york/3111688737</t>
+  </si>
+  <si>
+    <t>Senior Project Manager (Energy)</t>
+  </si>
+  <si>
+    <t>California Energy Commission</t>
+  </si>
+  <si>
+    <t>Sacramento, CA</t>
+  </si>
+  <si>
+    <t>$10,427 - $12,969 per month</t>
+  </si>
+  <si>
+    <t>policy-and-law-sustainability</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-senior-project-manager-energy-sacramento-ca-usa-california/1188421049</t>
+  </si>
+  <si>
+    <t>Service Forester</t>
+  </si>
+  <si>
+    <t>Washington State Department of Natural Resources</t>
+  </si>
+  <si>
+    <t>Deer Park, WA</t>
+  </si>
+  <si>
+    <t>$4,517 - $6,075 per month</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-service-forester-deer-park-washington/6082919198</t>
+  </si>
+  <si>
+    <t>Urban Forestry Manager</t>
+  </si>
+  <si>
+    <t>Louisville Grows</t>
+  </si>
+  <si>
+    <t>Louisville, KY</t>
+  </si>
+  <si>
+    <t>$45,000 - $60,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-forestry-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-urban-forestry-manager-louisville-kentucky/8703633457</t>
+  </si>
+  <si>
+    <t>Volunteer Field Assistants</t>
+  </si>
+  <si>
+    <t>Monash University</t>
+  </si>
+  <si>
+    <t>Derby, Australia</t>
+  </si>
+  <si>
+    <t>Unpaid</t>
+  </si>
+  <si>
+    <t>unpaid</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-volunteer-field-assistants-derby-australia/1467054766</t>
+  </si>
+  <si>
+    <t>Water Programs Manager</t>
+  </si>
+  <si>
+    <t>River Alliance of Wisconsin</t>
+  </si>
+  <si>
+    <t>Madison, WI</t>
+  </si>
+  <si>
+    <t>$60,000 - $65,000 per year</t>
+  </si>
+  <si>
+    <t>hydrology-policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-water-programs-manager-madison-wisconsin/8679601498</t>
+  </si>
+  <si>
+    <t>Water Resources Management Specialist</t>
+  </si>
+  <si>
+    <t>Jefferson County Land and Water Conservation Department</t>
+  </si>
+  <si>
+    <t>Jefferson, WI</t>
+  </si>
+  <si>
+    <t>$31.45 - $34.15 per hour</t>
+  </si>
+  <si>
+    <t>hydrology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-water-resources-management-specialist-jefferson-wisconsin/8324314975</t>
+  </si>
+  <si>
+    <t>Work Planner</t>
+  </si>
+  <si>
+    <t>ArborMetrics</t>
+  </si>
+  <si>
+    <t>Saginaw, MI</t>
+  </si>
+  <si>
+    <t>$23 - $26 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-work-planner-saginaw-michigan/8546048680</t>
+  </si>
+  <si>
+    <t>Senior Environmental Specialist (Tribal Brownfields)</t>
+  </si>
+  <si>
+    <t>Salt River Pima Maricopa Indian Community</t>
+  </si>
+  <si>
+    <t>Scottsdale, Arizona, United States</t>
+  </si>
+  <si>
+    <t>Full-Time</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Environmental</t>
+  </si>
+  <si>
+    <t>https://greenjobs.greenjobsearch.org/jobs/senior-environmental-specialist-tribal-brownfields/</t>
+  </si>
+  <si>
+    <t>🌍 Líder de Equipo F2F Vía Pública | Donantes Individuales | Turno Mañana o Tarde | CABA</t>
+  </si>
+  <si>
+    <t>Ingeniería Sin Fronteras Argentina</t>
+  </si>
+  <si>
+    <t>Buenos Aires, Ciudad Autónoma de Buenos Aires, AR</t>
+  </si>
+  <si>
+    <t>Contract</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/84bb675107d849af8da56e11af7cee41-lider-de-equipo-f2f-via-publica-donantes-individuales-turno-manana-o-tarde-caba-ingenieria-sin-fronteras-argentina-buenos-aires</t>
+  </si>
+  <si>
+    <t>Administrative Coordinator</t>
+  </si>
+  <si>
+    <t>Sisters of St. Joseph of Baden</t>
+  </si>
+  <si>
+    <t>Baden, Pennsylvania</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>USD 22.50/hour</t>
+  </si>
+  <si>
+    <t>Environment, Hunger Food Security, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/407b6ebbf9ba4cb0b56dffa8397e1178-administrative-coordinator-sisters-of-st-joseph-of-baden-baden</t>
+  </si>
+  <si>
+    <t>Administrative Support Supervisor (SHLA) – Eviction Defense Center Workgroup</t>
+  </si>
+  <si>
+    <t>Legal Aid Foundation of Los Angeles</t>
+  </si>
+  <si>
+    <t>Los Angeles, California</t>
+  </si>
+  <si>
+    <t>USD 73486.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8e581f659bee49818433c6f4948c3c93-administrative-support-supervisor-shla-eviction-defense-center-workgroup-legal-aid-foundation-of-los-angeles-los-angeles</t>
+  </si>
+  <si>
+    <t>Advancement Assistant</t>
+  </si>
+  <si>
+    <t>WildCare.Org</t>
+  </si>
+  <si>
+    <t>San Rafael, California</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 30.00/hour</t>
+  </si>
+  <si>
+    <t>Animals</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/21b3e6161e1e4eeba5046ae4f6116038-advancement-assistant-wildcareorg-san-rafael</t>
+  </si>
+  <si>
+    <t>APOYO ESCOLAR - CENTRO BARRIAL LA LUCILA</t>
+  </si>
+  <si>
+    <t>Centros Barriales - Municipalidad de Vicente López</t>
+  </si>
+  <si>
+    <t>Florida, Buenos Aires, AR</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/86183d9fc9ba4d929ce9035331668f19-apoyo-escolar-centro-barrial-la-lucila-centros-barriales-municipalidad-de-vicente-lopez-florida</t>
+  </si>
+  <si>
+    <t>Assistant Attorney General</t>
+  </si>
+  <si>
+    <t>Office of the Massachusetts Attorney General</t>
+  </si>
+  <si>
+    <t>Boston, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 90125.00 - 134513.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/e9aa3ba05a0a4f379f5c725ea5ac0b51-assistant-attorney-general-office-of-the-massachusetts-attorney-general-boston</t>
+  </si>
+  <si>
+    <t>Assistant Supervising Attorney</t>
+  </si>
+  <si>
+    <t>The Immigrant Law Center of Minnesota</t>
+  </si>
+  <si>
+    <t>USD 91984.00/year</t>
+  </si>
+  <si>
+    <t>Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ab10ae6c134340db95e0c7c46a099a82-assistant-supervising-attorney-the-immigrant-law-center-of-minnesota-saint-paul</t>
+  </si>
+  <si>
+    <t>Attorney – Eviction Defense Center (LB)</t>
+  </si>
+  <si>
+    <t>Long Beach, California</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 116328.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5149c76a72f241f4ab2f5726e6fdf261-attorney-eviction-defense-center-lb-legal-aid-foundation-of-los-angeles-long-beach</t>
+  </si>
+  <si>
+    <t>Attorney – Eviction Defense Center (Multiple Positions)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0e438ae7b88748e2b333300296639c3c-attorney-eviction-defense-center-multiple-positions-legal-aid-foundation-of-los-angeles-los-angeles</t>
+  </si>
+  <si>
+    <t>Attorney – Santa Monica Right to Counsel (Stay Housed LA)</t>
+  </si>
+  <si>
+    <t>Santa Monica, California</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 111854.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Poverty, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cad30cd9fc824f8a9e3fa1ef2b007b5e-attorney-santa-monica-right-to-counsel-stay-housed-la-legal-aid-foundation-of-los-angeles-santa-monica</t>
+  </si>
+  <si>
+    <t>Attorney – Survivor and Family Justice Workgroup</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 91936.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d2baf24c23814842bbd3cf574d8ee12c-attorney-survivor-and-family-justice-workgroup-legal-aid-foundation-of-los-angeles-los-angeles</t>
+  </si>
+  <si>
+    <t>Attorney (Housing) - Asian &amp; Pacific Islander Community Outreach Project workgroup</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 95613.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/52ef9e7f57eb4610b781d4665da6c7da-attorney-housing-asian-pacific-islander-community-outreach-project-workgroup-legal-aid-foundation-of-los-angeles-los-angeles</t>
+  </si>
+  <si>
+    <t>Attorney- Economic Stability Workgroup (3-5)</t>
+  </si>
+  <si>
+    <t>USD 88400.00 - 95613.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f31c09c437b5477b9bd0339b81e7640b-attorney-economic-stability-workgroup-3-5-legal-aid-foundation-of-los-angeles-los-angeles</t>
+  </si>
+  <si>
+    <t>Bilingual Intensive Case Manager (Social Worker)</t>
+  </si>
+  <si>
+    <t>Restore NYC</t>
+  </si>
+  <si>
+    <t>New York, New York</t>
+  </si>
+  <si>
+    <t>USD 67000.00 - 72000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Poverty, Victim Support</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/74fa805efd5748acb3819d3125e92a76-bilingual-intensive-case-manager-social-worker-restore-nyc-new-york</t>
+  </si>
+  <si>
+    <t>Case Manager (Stay Housed LA) - Eviction Defense Center Workgroup</t>
+  </si>
+  <si>
+    <t>USD 54080.00 - 71165.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a7871ec3bef64740baf44905418f49c3-case-manager-stay-housed-la-eviction-defense-center-workgroup-legal-aid-foundation-of-los-angeles-los-angeles</t>
+  </si>
+  <si>
+    <t>Chief Finance Officer</t>
+  </si>
+  <si>
+    <t>Center for Large Landscape Conservation</t>
+  </si>
+  <si>
+    <t>Bozeman, Montana</t>
+  </si>
+  <si>
+    <t>USD 128000.00 - 150000.00/year</t>
+  </si>
+  <si>
+    <t>Animals, Environment, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/71a20cf3002248a4bca6d30f71032f2d-chief-finance-officer-center-for-large-landscape-conservation-bozeman</t>
+  </si>
+  <si>
+    <t>Childcare Outreach and Enrollment Coordinator</t>
+  </si>
+  <si>
+    <t>La Colmena</t>
+  </si>
+  <si>
+    <t>Richmond County, New York</t>
+  </si>
+  <si>
+    <t>Full Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 45000.00 - 45000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b55fb1cc9f854b3c9d7e45994c6100e5-childcare-outreach-and-enrollment-coordinator-la-colmena-richmond-county</t>
+  </si>
+  <si>
+    <t>Climate Litigation Counsel</t>
+  </si>
+  <si>
+    <t>Climate Science Legal Defense Fund</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 105000.00/year</t>
+  </si>
+  <si>
+    <t>Climate Change, Environment, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2bc1903c6f974829822c0bf47b8bd6a5-climate-litigation-counsel-climate-science-legal-defense-fund-new-york</t>
+  </si>
+  <si>
+    <t>Communications &amp; Marketing Coordinator – Development/Administration Workgroup</t>
+  </si>
+  <si>
+    <t>USD 58576.00 - 73486.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4df2acb2501646ec996119ae43c4e727-communications-marketing-coordinator-developmentadministration-workgroup-legal-aid-foundation-of-los-angeles-los-angeles</t>
+  </si>
+  <si>
+    <t>Communications Manager</t>
+  </si>
+  <si>
+    <t>Cottonwood Gulch Expeditions</t>
+  </si>
+  <si>
+    <t>Albuquerque, New Mexico</t>
+  </si>
+  <si>
+    <t>USD 45000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0458dcd982ef41b2853fbf7d03a63aa7-communications-manager-cottonwood-gulch-expeditions-albuquerque</t>
+  </si>
+  <si>
+    <t>CHAI: Comprehensive Housing Assistance, Inc.</t>
+  </si>
+  <si>
+    <t>Baltimore, Maryland</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Education, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/dfbcc32a936643b0b02e71a809d091cd-community-engagement-manager-chai-comprehensive-housing-assistance-inc-baltimore</t>
+  </si>
+  <si>
+    <t>Community Roots Charter School, 7th Grade Humanities, Family Leave, 01/2027-06/2027</t>
+  </si>
+  <si>
+    <t>Community Roots Charter School</t>
+  </si>
+  <si>
+    <t>Kings County, New York</t>
+  </si>
+  <si>
+    <t>USD 65894.00 - 121360.00/year</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2015d67040d24d8cad6615b0f0de783d-community-roots-charter-school-7th-grade-humanities-family-leave-012027-062027-community-roots-charter-school-kings-county</t>
+  </si>
+  <si>
+    <t>Community Worker</t>
+  </si>
+  <si>
+    <t>Guru Shardha Welfare Charity</t>
+  </si>
+  <si>
+    <t>Calgary, Alberta, CA</t>
+  </si>
+  <si>
+    <t>CAD 18.00 - 24.00/hour</t>
+  </si>
+  <si>
+    <t>Community Development, Education, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8002eb9e01254ab7ba4294fd0051880c-community-worker-guru-shardha-welfare-charity-calgary</t>
+  </si>
+  <si>
+    <t>Coordinator, Public Health Initiatives – Hypertensive Disorders of Pregnancy (Grant-Funded Position)</t>
+  </si>
+  <si>
+    <t>Society for Maternal-Fetal Medicine</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/659872b44e5a4b2c8c108a6c946201d8-coordinator-public-health-initiatives-hypertensive-disorders-of-pregnancy-grant-funded-position-society-for-maternal-fetal-medicine-washington</t>
+  </si>
+  <si>
+    <t>Crest Runner</t>
+  </si>
+  <si>
+    <t>Pacific Crest Trail Association</t>
+  </si>
+  <si>
+    <t>Campo, California</t>
+  </si>
+  <si>
+    <t>USD 22.00 - 22.00/hour</t>
+  </si>
+  <si>
+    <t>Climate Change, Disaster Relief, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a7a945f63efe4e1aad18e6186f5b8f16-crest-runner-pacific-crest-trail-association-campo</t>
+  </si>
+  <si>
+    <t>Data &amp; Systems Specialist</t>
+  </si>
+  <si>
+    <t>Public Counsel</t>
+  </si>
+  <si>
+    <t>Los Angeles, CA</t>
+  </si>
+  <si>
+    <t>USD 62030.95 - 72834.94/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3e0ae515c62d46c9a318d8b0666f183c-data-systems-specialist-public-counsel-los-angeles</t>
+  </si>
+  <si>
+    <t>Delivery driver</t>
+  </si>
+  <si>
+    <t>CAD 15.00 - 20.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/252c4306195740a8b3c2aa486563c99e-delivery-driver-guru-shardha-welfare-charity-calgary</t>
+  </si>
+  <si>
+    <t>Delivery Driver</t>
+  </si>
+  <si>
+    <t>Mississauga, Ontario, CA</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5d3da0ab19414e8fb37af94c81783738-delivery-driver-guru-shardha-welfare-charity-mississauga</t>
+  </si>
+  <si>
+    <t>Development Coordinator</t>
+  </si>
+  <si>
+    <t>Lung Cancer Foundation of America</t>
+  </si>
+  <si>
+    <t>USD 45000.00 - 50000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Research Social Science, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4cf4c1c18fac4e96983ed960536284de-development-coordinator-lung-cancer-foundation-of-america-los-angeles</t>
+  </si>
+  <si>
+    <t>Careers In Nonprofits, Inc.</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 27.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/7167b7d504df4d5fa7dbf000e6a55f2b-development-coordinator-careers-in-nonprofits-inc-new-york</t>
+  </si>
+  <si>
+    <t>Digital Content Manager</t>
+  </si>
+  <si>
+    <t>American Association of State Highway &amp; Transportation Officials</t>
+  </si>
+  <si>
+    <t>Washington, District of Columbia</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Transportation</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ad015f151bf34fb990bd88360520681b-digital-content-manager-american-association-of-state-highway-transportation-officials-washington</t>
+  </si>
+  <si>
+    <t>Digital Marketing Manager</t>
+  </si>
+  <si>
+    <t>Points of Light</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c1b9968bedb5467f8e8cf8bfb319fc47-digital-marketing-manager-points-of-light-atlanta</t>
+  </si>
+  <si>
+    <t>Director of Finance</t>
+  </si>
+  <si>
+    <t>Bellwether</t>
+  </si>
+  <si>
+    <t>USD 121750.00 - 156875.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6ee6af448d2f43b892019dc8c265763e-director-of-finance-bellwether-washington</t>
+  </si>
+  <si>
+    <t>Director of Human Resources</t>
+  </si>
+  <si>
+    <t>Wissahickon Charter School</t>
+  </si>
+  <si>
+    <t>Philadelphia, Pennsylvania</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c5b55641020e4582b4e665bc35d5fb4d-director-of-human-resources-wissahickon-charter-school-philadelphia</t>
+  </si>
+  <si>
+    <t>Director of Pro Bono Programs</t>
+  </si>
+  <si>
+    <t>Inland Counties Legal Services, Inc.</t>
+  </si>
+  <si>
+    <t>Riverside, California</t>
+  </si>
+  <si>
+    <t>USD 127920.00 - 150800.00/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance, Disaster Relief, Lgbtq</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f5fd4025002b463d815e966ba8f25812-director-of-pro-bono-programs-inland-counties-legal-services-inc-riverside</t>
+  </si>
+  <si>
+    <t>Director of Programs</t>
+  </si>
+  <si>
+    <t>Climate Science Alliance</t>
+  </si>
+  <si>
+    <t>San Diego, California</t>
+  </si>
+  <si>
+    <t>USD 45.00 - 50.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Climate Change, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b9f93ebe24c34805990971cd6317e24c-director-of-programs-climate-science-alliance-san-diego</t>
+  </si>
+  <si>
+    <t>Director, Washington, DC</t>
+  </si>
+  <si>
+    <t>Human Rights Watch</t>
+  </si>
+  <si>
+    <t>USD 133000.00 - 157000.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3cd5ecc58b674327b9fd45204a7947f8-director-washington-dc-human-rights-watch-washington</t>
+  </si>
+  <si>
+    <t>Executive Director/Managing Agent -- Sudbury Housing Authority</t>
+  </si>
+  <si>
+    <t>Massachusetts NAHRO</t>
+  </si>
+  <si>
+    <t>Sudbury, Massachusetts</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>USD 62682.30 - 69547.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Housing Homelessness, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e83aa1a21a624426b6eb932a872a593a-executive-directormanaging-agent-sudbury-housing-authority-massachusetts-nahro-sudbury</t>
+  </si>
+  <si>
+    <t>Extra Special People (ESP)- Financial Controller</t>
+  </si>
+  <si>
+    <t>Extra Special People (ESP)</t>
+  </si>
+  <si>
+    <t>Athens, Georgia</t>
+  </si>
+  <si>
+    <t>USD 115000.00 - 135000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/043648ab38f64e13b74368af3123dcc8-extra-special-people-esp-financial-controller-extra-special-people-esp-athens</t>
+  </si>
+  <si>
+    <t>Facilitador/a Niño y Niña - Filial Mendoza</t>
+  </si>
+  <si>
+    <t>Aldeas Infantiles SOS Argentina</t>
+  </si>
+  <si>
+    <t>Mendoza, Mendoza, AR</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Children Youth, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f98c84aec406451ba4b05bc03583a862-facilitadora-nino-y-nina-filial-mendoza-aldeas-infantiles-sos-argentina-mendoza</t>
+  </si>
+  <si>
+    <t>Facilities &amp; Operations Manager</t>
+  </si>
+  <si>
+    <t>GrubStreet</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/79f08ce0c0c343b8adeeaaa4475f3374-facilities-operations-manager-grubstreet-boston</t>
+  </si>
+  <si>
+    <t>Facilities Coordinator</t>
+  </si>
+  <si>
+    <t>United Way of King County (WA State)</t>
+  </si>
+  <si>
+    <t>Seattle, Washington</t>
+  </si>
+  <si>
+    <t>USD 30.08 - 31.58/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b1deda0b658a4cdfb880cb2c61acbf7f-facilities-coordinator-united-way-of-king-county-wa-state-seattle</t>
+  </si>
+  <si>
+    <t>Fellowship Program Manager</t>
+  </si>
+  <si>
+    <t>College Visions</t>
+  </si>
+  <si>
+    <t>Providence, Rhode Island</t>
+  </si>
+  <si>
+    <t>USD 65000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3113d39b8c674d89b720285ee74ea943-fellowship-program-manager-college-visions-providence</t>
+  </si>
+  <si>
+    <t>FFLA Director of Legal Services</t>
+  </si>
+  <si>
+    <t>Americans for Immigrant Justice</t>
+  </si>
+  <si>
+    <t>Miami, FL</t>
+  </si>
+  <si>
+    <t>USD 106430.00 - 150000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c983d33e48084dd996edae540ea48d7d-ffla-director-of-legal-services-americans-for-immigrant-justice-miami</t>
+  </si>
+  <si>
+    <t>Foundation Relations Director</t>
+  </si>
+  <si>
+    <t>Meals on Wheels America</t>
+  </si>
+  <si>
+    <t>Arlington, Virginia</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Seniors Retirement, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9b0442db79de45b58816412275891120-foundation-relations-director-meals-on-wheels-america-arlington</t>
+  </si>
+  <si>
+    <t>Grants &amp; Contracts Coordinator – Development/Administration Workgroup</t>
+  </si>
+  <si>
+    <t>USD 70500.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bb196fe6f0a242cfbe8b337101b72f80-grants-contracts-coordinator-developmentadministration-workgroup-legal-aid-foundation-of-los-angeles-los-angeles</t>
+  </si>
+  <si>
+    <t>Grants Assistant</t>
+  </si>
+  <si>
+    <t>Myriad USA</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/493b5bddf7034dd593acb770a450e9da-grants-assistant-myriad-usa-new-york</t>
+  </si>
+  <si>
+    <t>Group Exercise Instructor I (Flatbush YMCA)</t>
+  </si>
+  <si>
+    <t>YMCA of Greater New York</t>
+  </si>
+  <si>
+    <t>USD 30.00 - 50.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Volunteering, Sports Recreation</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/35df706dae74441bb24cf05ae0f08eec-group-exercise-instructor-i-flatbush-ymca-ymca-of-greater-new-york-kings-county</t>
+  </si>
+  <si>
+    <t>Habeas Operations Senior Manager</t>
+  </si>
+  <si>
+    <t>Immigrant ARC</t>
+  </si>
+  <si>
+    <t>USD 74000.00 - 87000.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5db9620d583b48998fc8c245cb971cdc-habeas-operations-senior-manager-immigrant-arc-albany</t>
+  </si>
+  <si>
+    <t>Housing/Consumer Attorney (Disaster Legal Services) – Pro Bono Workgroup</t>
+  </si>
+  <si>
+    <t>USD 91936.00 - 107552.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2df631963fb04b35bee35db9bd5a1ef0-housingconsumer-attorney-disaster-legal-services-pro-bono-workgroup-legal-aid-foundation-of-los-angeles-los-angeles</t>
+  </si>
+  <si>
+    <t>HR Coordinator</t>
+  </si>
+  <si>
+    <t>Regina, Saskatchewan, CA</t>
+  </si>
+  <si>
+    <t>CAD 17.00 - 25.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6d7daec608bf4cb1a7d73de89ac7a45c-hr-coordinator-guru-shardha-welfare-charity-regina</t>
+  </si>
+  <si>
+    <t>Major Gifts Officer</t>
+  </si>
+  <si>
+    <t>United Way of Greater Los Angeles</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/26f318a26f324e888cbab9ca2cbb2c0b-major-gifts-officer-united-way-of-greater-los-angeles-los-angeles</t>
+  </si>
+  <si>
+    <t>Manager of Family Support Services</t>
+  </si>
+  <si>
+    <t>Literacy Partners, Inc.</t>
+  </si>
+  <si>
+    <t>USD 66300.00/year</t>
+  </si>
+  <si>
+    <t>Education, Family, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bd952b6e22e64945a10d710cf09af37d-manager-of-family-support-services-literacy-partners-inc-new-york</t>
+  </si>
+  <si>
+    <t>Manager, Public Health Initiatives &amp; Quality Improvement in Hypertensive Disorders of Pregnancy (Grant-Funded)</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/add9208a4abd4b77a481fb9cd12ebb7f-manager-public-health-initiatives-quality-improvement-in-hypertensive-disorders-of-pregnancy-grant-funded-society-for-maternal-fetal-medicine-washington</t>
+  </si>
+  <si>
+    <t>Managing Director, Gift Planning (Legacy Giving)</t>
+  </si>
+  <si>
+    <t>The Breast Cancer Research Foundation</t>
+  </si>
+  <si>
+    <t>USD 175000.00 - 190000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Job Workplace, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8a9019df92b3430ebb25e355c3060b3d-managing-director-gift-planning-legacy-giving-the-breast-cancer-research-foundation-new-york</t>
+  </si>
+  <si>
+    <t>Marketing Manager</t>
+  </si>
+  <si>
+    <t>Temple Beth Am Jupiter</t>
+  </si>
+  <si>
+    <t>Jupiter, Florida</t>
+  </si>
+  <si>
+    <t>Religion Spirituality, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/323238468af349088aa3754d2f98180b-marketing-manager-temple-beth-am-jupiter-jupiter</t>
+  </si>
+  <si>
+    <t>Membership Manager, Education Writers Association</t>
+  </si>
+  <si>
+    <t>Education Writers Association</t>
+  </si>
+  <si>
+    <t>USD 68000.00 - 76000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/485d9adac3d248f498acf68c57942d38-membership-manager-education-writers-association-education-writers-association-washington</t>
+  </si>
+  <si>
+    <t>Membership Recruitment Specialist</t>
+  </si>
+  <si>
+    <t>Girl Scout Council of the Nation's Capital</t>
+  </si>
+  <si>
+    <t>Manassas, Virginia</t>
+  </si>
+  <si>
+    <t>USD 52000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3ea7a527a61547f0bb21676e4c157632-membership-recruitment-specialist-girl-scout-council-of-the-nations-capital-manassas</t>
+  </si>
+  <si>
+    <t>Museum Math Fellow (Exponent Fellowship)</t>
+  </si>
+  <si>
+    <t>National Museum of Mathematics</t>
+  </si>
+  <si>
+    <t>USD 20.00 - 20.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f84fef5ca3b644e19d5f68013ae11c0d-museum-math-fellow-exponent-fellowship-national-museum-of-mathematics-new-york</t>
+  </si>
+  <si>
+    <t>Operations Manager</t>
+  </si>
+  <si>
+    <t>United Neighborhood Houses</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/70d9c4385503494db9c226425e5553e5-operations-manager-united-neighborhood-houses-new-york</t>
+  </si>
+  <si>
+    <t>Paralegal (Stay Housed LA/Right to Counsel) – Santa Monica Workgroup</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bcc06c0d31834578ad623771a6737326-paralegal-stay-housed-laright-to-counsel-santa-monica-workgroup-legal-aid-foundation-of-los-angeles-santa-monica</t>
+  </si>
+  <si>
+    <t>Post Graduate Fellow (Housing Justice) - Eviction Defense Center Workgroup</t>
+  </si>
+  <si>
+    <t>USD 74880.00 - 77875.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5a92f3e4f33d4121834fad5d8648ec27-post-graduate-fellow-housing-justice-eviction-defense-center-workgroup-legal-aid-foundation-of-los-angeles-los-angeles</t>
+  </si>
+  <si>
+    <t>Press Secretary</t>
+  </si>
+  <si>
+    <t>Groundwork Collaborative</t>
+  </si>
+  <si>
+    <t>USD 110000.00 - 140000.00/year</t>
+  </si>
+  <si>
+    <t>Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/3035b83e5b3d4347bc29493a24fd8dd9-press-secretary-groundwork-collaborative-washington</t>
+  </si>
+  <si>
+    <t>Program Assistant, Edie Windsor SAGE Center</t>
+  </si>
+  <si>
+    <t>SAGE | Advocacy and Services for LGBT Elders, Inc.</t>
+  </si>
+  <si>
+    <t>USD 46000.00 - 46000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Housing Homelessness, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/867ff82d990d48a7b8e76cb1b61e4d82-program-assistant-edie-windsor-sage-center-sage-advocacy-and-services-for-lgbt-elders-inc-new-york</t>
+  </si>
+  <si>
+    <t>Program Coordinator</t>
+  </si>
+  <si>
+    <t>Pachamama Alliance</t>
+  </si>
+  <si>
+    <t>San Francisco, California</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Climate Change, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c50bd93557e24e3ca41499d87f2665dd-program-coordinator-pachamama-alliance-san-francisco</t>
+  </si>
+  <si>
+    <t>Program Manager, Audience Reach and Communications</t>
+  </si>
+  <si>
+    <t>Jewish Story Partners</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Media, Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/95121b5d2d504beca8fd9d89f52ec761-program-manager-audience-reach-and-communications-jewish-story-partners-los-angeles</t>
+  </si>
+  <si>
+    <t>Program Manager, High-Performance Building Courses</t>
+  </si>
+  <si>
+    <t>Studio HPDC</t>
+  </si>
+  <si>
+    <t>Newton, Massachusetts</t>
+  </si>
+  <si>
+    <t>Climate Change, Education, Energy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/439b136b0fde4388919e325e23ce3628-program-manager-high-performance-building-courses-studio-hpdc-newton</t>
+  </si>
+  <si>
+    <t>Program Manager, Virtual Course and Alumni Programming, Stevens Digital Leaders</t>
+  </si>
+  <si>
+    <t>American Councils for International Education: ACTR/ACCELS</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Education, International Relations</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8bfef994f556421886fffad1a96dce02-program-manager-virtual-course-and-alumni-programming-stevens-digital-leaders-american-councils-for-international-education-actraccels-washington</t>
+  </si>
+  <si>
+    <t>Project Coordinator</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bc10a1b8364d47818f2807e2c1e61075-project-coordinator-lung-cancer-foundation-of-america-los-angeles</t>
+  </si>
+  <si>
+    <t>Project Onramp Manager</t>
+  </si>
+  <si>
+    <t>Life Science Cares</t>
+  </si>
+  <si>
+    <t>Education, Community Development, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/07cbaf77b3d84ad2b0c460e23ddb8d9c-project-onramp-manager-life-science-cares-new-york</t>
+  </si>
+  <si>
+    <t>Receptionist (Stay Housed L.A. Coalition) – Client Intake Workgroup (South)</t>
+  </si>
+  <si>
+    <t>South Gate, California</t>
+  </si>
+  <si>
+    <t>USD 52500.00 - 61417.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/53d49451d93e482d9ef3dedebf639607-receptionist-stay-housed-la-coalition-client-intake-workgroup-south-legal-aid-foundation-of-los-angeles-south-gate</t>
+  </si>
+  <si>
+    <t>Regional Director, Development &amp; Philanthropy (Rochester Region)</t>
+  </si>
+  <si>
+    <t>Make-A-Wish Metro NY and Western NY</t>
+  </si>
+  <si>
+    <t>Rochester, New York</t>
+  </si>
+  <si>
+    <t>USD 88000.00 - 94000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/30cce50bea1847a4b97b460b1bcc4f38-regional-director-development-philanthropy-rochester-region-make-a-wish-metro-ny-and-western-ny-rochester</t>
+  </si>
+  <si>
+    <t>Research Associate</t>
+  </si>
+  <si>
+    <t>CEA Consulting</t>
+  </si>
+  <si>
+    <t>Environment, Climate Change, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/26b5472515ed4b6cb12fe18572635f2b-research-associate-cea-consulting-san-francisco</t>
+  </si>
+  <si>
+    <t>Responsable de Desarrollo y Alianzas - CABA, Bs. As.</t>
+  </si>
+  <si>
+    <t>Asociación Civil Pata Pila</t>
+  </si>
+  <si>
+    <t>Buenos Aires, Buenos Aires, AR</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/80ec95dae98646658d7ec93793bf68be-responsable-de-desarrollo-y-alianzas-caba-bs-as-asociacion-civil-pata-pila-buenos-aires</t>
+  </si>
+  <si>
+    <t>Revenue Operations Coordinator</t>
+  </si>
+  <si>
+    <t>Partnership to End Addiction</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9cd2205d9e7b4d5f8c0054fcd1efc80a-revenue-operations-coordinator-partnership-to-end-addiction-new-york</t>
+  </si>
+  <si>
+    <t>Senior Attorney-Matrimonial Unit</t>
+  </si>
+  <si>
+    <t>District Council 37, Health &amp; Security Plan</t>
+  </si>
+  <si>
+    <t>USD 107515.00 - 130863.00/year</t>
+  </si>
+  <si>
+    <t>Job Workplace, Conflict Resolution, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e489c85929e6417d988b1be09ecb1f75-senior-attorney-matrimonial-unit-district-council-37-health-security-plan-new-york</t>
+  </si>
+  <si>
+    <t>Senior Fellow, Finance and Insurance</t>
+  </si>
+  <si>
+    <t>R Street Institute</t>
+  </si>
+  <si>
+    <t>USD 160000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2b35243f3b804168b0ea87959030c726-senior-fellow-finance-and-insurance-r-street-institute-washington</t>
+  </si>
+  <si>
+    <t>Senior Manager/Director, Communications</t>
+  </si>
+  <si>
+    <t>Omidyar Network</t>
+  </si>
+  <si>
+    <t>USD 195800.00 - 275400.00/year</t>
+  </si>
+  <si>
+    <t>Philanthropy, Science Technology, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/4860ea8c05944c4391d28ff9f156d6cc-senior-managerdirector-communications-omidyar-network-san-francisco</t>
+  </si>
+  <si>
+    <t>Site Safety Training (SST) Associate</t>
+  </si>
+  <si>
+    <t>USD 40000.00 - 45000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e367f59f7cc94286a53d8357e7bdd4c4-site-safety-training-sst-associate-la-colmena-richmond-county</t>
+  </si>
+  <si>
+    <t>Site Supervisor (Flatbush YMCA)</t>
+  </si>
+  <si>
+    <t>USD 66300.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7dd3494280c64b80a6e67e29d478c167-site-supervisor-flatbush-ymca-ymca-of-greater-new-york-kings-county</t>
+  </si>
+  <si>
+    <t>Social Media Manager - Ukrainian/English</t>
+  </si>
+  <si>
+    <t>American Coalition for Ukraine</t>
+  </si>
+  <si>
+    <t>USD 2500.00 - 2500.00/month</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Immigrants Or Refugees, International Relations</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/381ac49f2e794bf0bb0d6d5f715e5b0b-social-media-manager-ukrainianenglish-american-coalition-for-ukraine-washington</t>
+  </si>
+  <si>
+    <t>Social Worker, The Dorothy Ross Friedman Residence</t>
+  </si>
+  <si>
+    <t>ACTORS FUND OF AMERICA</t>
+  </si>
+  <si>
+    <t>Brooklyn, New York</t>
+  </si>
+  <si>
+    <t>USD 69000.00 - 78422.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/677c676303784ddbb4800bee350548af-social-worker-the-dorothy-ross-friedman-residence-actors-fund-of-america-brooklyn</t>
+  </si>
+  <si>
+    <t>Stay Housed LA Intake Supervisor – Client Intake Workgroup</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2997d538b4f84fffa1dbbee21bb3b849-stay-housed-la-intake-supervisor-client-intake-workgroup-legal-aid-foundation-of-los-angeles-los-angeles</t>
+  </si>
+  <si>
+    <t>Student Advisor</t>
+  </si>
+  <si>
+    <t>East Side House Settlement</t>
+  </si>
+  <si>
+    <t>Bronx County, New York</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4fb0265900ca4d4ead51fd08ad1e4092-student-advisor-east-side-house-settlement-bronx-county</t>
+  </si>
+  <si>
+    <t>Supervising Attorney (Domestic Violence and Immigration)</t>
+  </si>
+  <si>
+    <t>Volunteer Legal Advocates</t>
+  </si>
+  <si>
+    <t>Rockville, Maryland</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 88000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Immigrants Or Refugees, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4cd161959df445fea968c02b80603fd8-supervising-attorney-domestic-violence-and-immigration-volunteer-legal-advocates-rockville</t>
+  </si>
+  <si>
+    <t>TALLERISTA DE RECREACION</t>
+  </si>
+  <si>
+    <t>Villa Martelli, Provincia de Buenos Aires, AR</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/45f8c9e2ff0d426d8e2ac53440e37b4d-tallerista-de-recreacion-centros-barriales-municipalidad-de-vicente-lopez-villa-martelli</t>
+  </si>
+  <si>
+    <t>TALLERISTA PARA CENTRO BARRIAL DE INFANCIA - VILLA MARTELLI</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/4c6c7867eb6b4d1b8ba571031a3fafcd-tallerista-para-centro-barrial-de-infancia-villa-martelli-centros-barriales-municipalidad-de-vicente-lopez-villa-martelli</t>
+  </si>
+  <si>
+    <t>Teacher's Toolkit Curriculum Development Manager</t>
+  </si>
+  <si>
+    <t>Skeptoid Media Inc</t>
+  </si>
+  <si>
+    <t>USD 35.00/hour</t>
+  </si>
+  <si>
+    <t>Education, Media, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b1a3ac9daeb94912a260f87497e8aeed-teachers-toolkit-curriculum-development-manager-skeptoid-media-inc-bend</t>
+  </si>
+  <si>
+    <t>Temporary Bilingual Administrative Assistant</t>
+  </si>
+  <si>
+    <t>Immigration Center for Women and Children</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 28.00/hour</t>
+  </si>
+  <si>
+    <t>Immigrants Or Refugees, Children Youth, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d8735093a97649358e5f44868e4634f0-temporary-bilingual-administrative-assistant-immigration-center-for-women-and-children-san-francisco</t>
+  </si>
+  <si>
+    <t>Transport Dispatchers</t>
+  </si>
+  <si>
+    <t>CAD 22.00 - 25.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/31f9d856e90e4818829526633fd744a7-transport-dispatchers-guru-shardha-welfare-charity-mississauga</t>
+  </si>
+  <si>
+    <t>Transport Truck Driver</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c718d6722372489e90bacfb4553c4b17-transport-truck-driver-guru-shardha-welfare-charity-mississauga</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/274bfdf2918d4d1ca30c47bb9870fbfd-transport-truck-driver-guru-shardha-welfare-charity-calgary</t>
+  </si>
+  <si>
+    <t>Transportation Dispatcher</t>
+  </si>
+  <si>
+    <t>Community Development, Housing Homelessness, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a681aba7b6f44512ad3fa2bc6d94498d-transportation-dispatcher-guru-shardha-welfare-charity-calgary</t>
+  </si>
+  <si>
+    <t>Washington Transportation Policy Manager</t>
+  </si>
+  <si>
+    <t>Climate Solutions</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 105000.00/year</t>
+  </si>
+  <si>
+    <t>Climate Change, Energy, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ad9574cb212d48699910b63128d8bdf4-washington-transportation-policy-manager-climate-solutions-seattle</t>
+  </si>
+  <si>
+    <t>Zona: Mar del Plata - Lider de Equipo de Captadores/as de Fondos (F2F)</t>
+  </si>
+  <si>
+    <t>Mar del Plata, Provincia de Buenos Aires, AR</t>
+  </si>
+  <si>
+    <t>Children Youth, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e0e4108edc3d40aaa79cc05eebb397c6-zona-mar-del-plata-lider-de-equipo-de-captadoresas-de-fondos-f2f-aldeas-infantiles-sos-argentina-mar-del-plata</t>
+  </si>
+  <si>
+    <t>Zona: Rosario - Lider de Equipo de Captadores/as de Fondos (F2F)</t>
+  </si>
+  <si>
+    <t>Rosario, Santa Fe, AR</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/02ba65f035a64cc1b6695e319d51923a-zona-rosario-lider-de-equipo-de-captadoresas-de-fondos-f2f-aldeas-infantiles-sos-argentina-rosario</t>
+  </si>
+  <si>
+    <t>Zona: San Miguel de Tucumán - Lider de Equipo de Captadores/as de Fondos (F2F)</t>
+  </si>
+  <si>
+    <t>San Miguel de Tucumán, Tucumán, AR</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d3a18b54e52b4dfa9f4c85cbbf9b2336-zona-san-miguel-de-tucuman-lider-de-equipo-de-captadoresas-de-fondos-f2f-aldeas-infantiles-sos-argentina-san-miguel-de-tucuman</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -54,6 +1920,10 @@
     </font>
     <font>
       <b/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF1155CC"/>
     </font>
   </fonts>
   <fills count="2">
@@ -76,9 +1946,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -418,7 +2289,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -457,8 +2328,802 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" t="s">
+        <v>33</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" t="s">
+        <v>39</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>44</v>
+      </c>
+      <c r="F7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
+        <v>49</v>
+      </c>
+      <c r="F8" t="s">
+        <v>50</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C9" t="s">
+        <v>54</v>
+      </c>
+      <c r="D9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" t="s">
+        <v>55</v>
+      </c>
+      <c r="F9" t="s">
+        <v>56</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>58</v>
+      </c>
+      <c r="B10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" t="s">
+        <v>59</v>
+      </c>
+      <c r="D10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" t="s">
+        <v>60</v>
+      </c>
+      <c r="F10" t="s">
+        <v>45</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>62</v>
+      </c>
+      <c r="B11" t="s">
+        <v>63</v>
+      </c>
+      <c r="C11" t="s">
+        <v>64</v>
+      </c>
+      <c r="D11" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" t="s">
+        <v>65</v>
+      </c>
+      <c r="F11" t="s">
+        <v>66</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>68</v>
+      </c>
+      <c r="B12" t="s">
+        <v>69</v>
+      </c>
+      <c r="C12" t="s">
+        <v>70</v>
+      </c>
+      <c r="D12" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" t="s">
+        <v>71</v>
+      </c>
+      <c r="F12" t="s">
+        <v>33</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>73</v>
+      </c>
+      <c r="B13" t="s">
+        <v>74</v>
+      </c>
+      <c r="C13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D13" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" t="s">
+        <v>32</v>
+      </c>
+      <c r="F13" t="s">
+        <v>76</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>78</v>
+      </c>
+      <c r="B14" t="s">
+        <v>79</v>
+      </c>
+      <c r="C14" t="s">
+        <v>80</v>
+      </c>
+      <c r="D14" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F14" t="s">
+        <v>82</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>84</v>
+      </c>
+      <c r="B15" t="s">
+        <v>85</v>
+      </c>
+      <c r="C15" t="s">
+        <v>86</v>
+      </c>
+      <c r="D15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" t="s">
+        <v>87</v>
+      </c>
+      <c r="F15" t="s">
+        <v>76</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>89</v>
+      </c>
+      <c r="B16" t="s">
+        <v>90</v>
+      </c>
+      <c r="C16" t="s">
+        <v>91</v>
+      </c>
+      <c r="D16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" t="s">
+        <v>92</v>
+      </c>
+      <c r="F16" t="s">
+        <v>45</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>94</v>
+      </c>
+      <c r="B17" t="s">
+        <v>42</v>
+      </c>
+      <c r="C17" t="s">
+        <v>43</v>
+      </c>
+      <c r="D17" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" t="s">
+        <v>95</v>
+      </c>
+      <c r="F17" t="s">
+        <v>45</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>97</v>
+      </c>
+      <c r="B18" t="s">
+        <v>98</v>
+      </c>
+      <c r="C18" t="s">
+        <v>99</v>
+      </c>
+      <c r="D18" t="s">
+        <v>18</v>
+      </c>
+      <c r="E18" t="s">
+        <v>100</v>
+      </c>
+      <c r="F18" t="s">
+        <v>101</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>103</v>
+      </c>
+      <c r="B19" t="s">
+        <v>104</v>
+      </c>
+      <c r="C19" t="s">
+        <v>105</v>
+      </c>
+      <c r="D19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" t="s">
+        <v>106</v>
+      </c>
+      <c r="F19" t="s">
+        <v>56</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>108</v>
+      </c>
+      <c r="B20" t="s">
+        <v>104</v>
+      </c>
+      <c r="C20" t="s">
+        <v>105</v>
+      </c>
+      <c r="D20" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" t="s">
+        <v>106</v>
+      </c>
+      <c r="F20" t="s">
+        <v>56</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>110</v>
+      </c>
+      <c r="B21" t="s">
+        <v>111</v>
+      </c>
+      <c r="C21" t="s">
+        <v>112</v>
+      </c>
+      <c r="D21" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" t="s">
+        <v>113</v>
+      </c>
+      <c r="F21" t="s">
+        <v>114</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>116</v>
+      </c>
+      <c r="B22" t="s">
+        <v>117</v>
+      </c>
+      <c r="C22" t="s">
+        <v>118</v>
+      </c>
+      <c r="D22" t="s">
+        <v>18</v>
+      </c>
+      <c r="E22" t="s">
+        <v>119</v>
+      </c>
+      <c r="F22" t="s">
+        <v>120</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>122</v>
+      </c>
+      <c r="B23" t="s">
+        <v>117</v>
+      </c>
+      <c r="C23" t="s">
+        <v>118</v>
+      </c>
+      <c r="D23" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" t="s">
+        <v>123</v>
+      </c>
+      <c r="F23" t="s">
+        <v>56</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>125</v>
+      </c>
+      <c r="B24" t="s">
+        <v>126</v>
+      </c>
+      <c r="C24" t="s">
+        <v>127</v>
+      </c>
+      <c r="D24" t="s">
+        <v>18</v>
+      </c>
+      <c r="E24" t="s">
+        <v>128</v>
+      </c>
+      <c r="F24" t="s">
+        <v>129</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>131</v>
+      </c>
+      <c r="B25" t="s">
+        <v>132</v>
+      </c>
+      <c r="C25" t="s">
+        <v>133</v>
+      </c>
+      <c r="D25" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" t="s">
+        <v>134</v>
+      </c>
+      <c r="F25" t="s">
+        <v>135</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>137</v>
+      </c>
+      <c r="B26" t="s">
+        <v>138</v>
+      </c>
+      <c r="C26" t="s">
+        <v>139</v>
+      </c>
+      <c r="D26" t="s">
+        <v>18</v>
+      </c>
+      <c r="E26" t="s">
+        <v>140</v>
+      </c>
+      <c r="F26" t="s">
+        <v>141</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>143</v>
+      </c>
+      <c r="B27" t="s">
+        <v>144</v>
+      </c>
+      <c r="C27" t="s">
+        <v>145</v>
+      </c>
+      <c r="D27" t="s">
+        <v>18</v>
+      </c>
+      <c r="E27" t="s">
+        <v>146</v>
+      </c>
+      <c r="F27" t="s">
+        <v>76</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>148</v>
+      </c>
+      <c r="B28" t="s">
+        <v>149</v>
+      </c>
+      <c r="C28" t="s">
+        <v>150</v>
+      </c>
+      <c r="D28" t="s">
+        <v>18</v>
+      </c>
+      <c r="E28" t="s">
+        <v>151</v>
+      </c>
+      <c r="F28" t="s">
+        <v>152</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>154</v>
+      </c>
+      <c r="B29" t="s">
+        <v>155</v>
+      </c>
+      <c r="C29" t="s">
+        <v>156</v>
+      </c>
+      <c r="D29" t="s">
+        <v>11</v>
+      </c>
+      <c r="E29" t="s">
+        <v>157</v>
+      </c>
+      <c r="F29" t="s">
+        <v>101</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>159</v>
+      </c>
+      <c r="B30" t="s">
+        <v>160</v>
+      </c>
+      <c r="C30" t="s">
+        <v>161</v>
+      </c>
+      <c r="D30" t="s">
+        <v>18</v>
+      </c>
+      <c r="E30" t="s">
+        <v>162</v>
+      </c>
+      <c r="F30" t="s">
+        <v>163</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>165</v>
+      </c>
+      <c r="B31" t="s">
+        <v>166</v>
+      </c>
+      <c r="C31" t="s">
+        <v>167</v>
+      </c>
+      <c r="D31" t="s">
+        <v>168</v>
+      </c>
+      <c r="E31" t="s">
+        <v>169</v>
+      </c>
+      <c r="F31" t="s">
+        <v>135</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>171</v>
+      </c>
+      <c r="B32" t="s">
+        <v>172</v>
+      </c>
+      <c r="C32" t="s">
+        <v>173</v>
+      </c>
+      <c r="D32" t="s">
+        <v>18</v>
+      </c>
+      <c r="E32" t="s">
+        <v>174</v>
+      </c>
+      <c r="F32" t="s">
+        <v>175</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>177</v>
+      </c>
+      <c r="B33" t="s">
+        <v>178</v>
+      </c>
+      <c r="C33" t="s">
+        <v>179</v>
+      </c>
+      <c r="D33" t="s">
+        <v>18</v>
+      </c>
+      <c r="E33" t="s">
+        <v>180</v>
+      </c>
+      <c r="F33" t="s">
+        <v>181</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>183</v>
+      </c>
+      <c r="B34" t="s">
+        <v>184</v>
+      </c>
+      <c r="C34" t="s">
+        <v>185</v>
+      </c>
+      <c r="D34" t="s">
+        <v>18</v>
+      </c>
+      <c r="E34" t="s">
+        <v>186</v>
+      </c>
+      <c r="F34" t="s">
+        <v>101</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>187</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -466,7 +3131,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -505,8 +3170,34 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D2" t="s">
+        <v>191</v>
+      </c>
+      <c r="E2" t="s">
+        <v>192</v>
+      </c>
+      <c r="F2" t="s">
+        <v>193</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>194</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -514,7 +3205,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H98"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -553,8 +3244,2338 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C2" t="s">
+        <v>197</v>
+      </c>
+      <c r="D2" t="s">
+        <v>198</v>
+      </c>
+      <c r="E2" t="s">
+        <v>192</v>
+      </c>
+      <c r="F2" t="s">
+        <v>199</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>201</v>
+      </c>
+      <c r="B3" t="s">
+        <v>202</v>
+      </c>
+      <c r="C3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D3" t="s">
+        <v>204</v>
+      </c>
+      <c r="E3" t="s">
+        <v>205</v>
+      </c>
+      <c r="F3" t="s">
+        <v>206</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>208</v>
+      </c>
+      <c r="B4" t="s">
+        <v>209</v>
+      </c>
+      <c r="C4" t="s">
+        <v>210</v>
+      </c>
+      <c r="D4" t="s">
+        <v>204</v>
+      </c>
+      <c r="E4" t="s">
+        <v>211</v>
+      </c>
+      <c r="F4" t="s">
+        <v>212</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>214</v>
+      </c>
+      <c r="B5" t="s">
+        <v>215</v>
+      </c>
+      <c r="C5" t="s">
+        <v>216</v>
+      </c>
+      <c r="D5" t="s">
+        <v>204</v>
+      </c>
+      <c r="E5" t="s">
+        <v>217</v>
+      </c>
+      <c r="F5" t="s">
+        <v>218</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>220</v>
+      </c>
+      <c r="B6" t="s">
+        <v>221</v>
+      </c>
+      <c r="C6" t="s">
+        <v>222</v>
+      </c>
+      <c r="D6" t="s">
+        <v>204</v>
+      </c>
+      <c r="E6" t="s">
+        <v>192</v>
+      </c>
+      <c r="F6" t="s">
+        <v>223</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>225</v>
+      </c>
+      <c r="B7" t="s">
+        <v>226</v>
+      </c>
+      <c r="C7" t="s">
+        <v>227</v>
+      </c>
+      <c r="D7" t="s">
+        <v>204</v>
+      </c>
+      <c r="E7" t="s">
+        <v>228</v>
+      </c>
+      <c r="F7" t="s">
+        <v>192</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>230</v>
+      </c>
+      <c r="B8" t="s">
+        <v>231</v>
+      </c>
+      <c r="C8" t="s">
+        <v>127</v>
+      </c>
+      <c r="D8" t="s">
+        <v>204</v>
+      </c>
+      <c r="E8" t="s">
+        <v>232</v>
+      </c>
+      <c r="F8" t="s">
+        <v>233</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>235</v>
+      </c>
+      <c r="B9" t="s">
+        <v>209</v>
+      </c>
+      <c r="C9" t="s">
+        <v>236</v>
+      </c>
+      <c r="D9" t="s">
+        <v>204</v>
+      </c>
+      <c r="E9" t="s">
+        <v>237</v>
+      </c>
+      <c r="F9" t="s">
+        <v>212</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>239</v>
+      </c>
+      <c r="B10" t="s">
+        <v>209</v>
+      </c>
+      <c r="C10" t="s">
+        <v>210</v>
+      </c>
+      <c r="D10" t="s">
+        <v>204</v>
+      </c>
+      <c r="E10" t="s">
+        <v>237</v>
+      </c>
+      <c r="F10" t="s">
+        <v>212</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>241</v>
+      </c>
+      <c r="B11" t="s">
+        <v>209</v>
+      </c>
+      <c r="C11" t="s">
+        <v>242</v>
+      </c>
+      <c r="D11" t="s">
+        <v>204</v>
+      </c>
+      <c r="E11" t="s">
+        <v>243</v>
+      </c>
+      <c r="F11" t="s">
+        <v>244</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>246</v>
+      </c>
+      <c r="B12" t="s">
+        <v>209</v>
+      </c>
+      <c r="C12" t="s">
+        <v>210</v>
+      </c>
+      <c r="D12" t="s">
+        <v>204</v>
+      </c>
+      <c r="E12" t="s">
+        <v>247</v>
+      </c>
+      <c r="F12" t="s">
+        <v>212</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>249</v>
+      </c>
+      <c r="B13" t="s">
+        <v>209</v>
+      </c>
+      <c r="C13" t="s">
+        <v>210</v>
+      </c>
+      <c r="D13" t="s">
+        <v>204</v>
+      </c>
+      <c r="E13" t="s">
+        <v>250</v>
+      </c>
+      <c r="F13" t="s">
+        <v>192</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>252</v>
+      </c>
+      <c r="B14" t="s">
+        <v>209</v>
+      </c>
+      <c r="C14" t="s">
+        <v>210</v>
+      </c>
+      <c r="D14" t="s">
+        <v>204</v>
+      </c>
+      <c r="E14" t="s">
+        <v>253</v>
+      </c>
+      <c r="F14" t="s">
+        <v>212</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>255</v>
+      </c>
+      <c r="B15" t="s">
+        <v>256</v>
+      </c>
+      <c r="C15" t="s">
+        <v>257</v>
+      </c>
+      <c r="D15" t="s">
+        <v>204</v>
+      </c>
+      <c r="E15" t="s">
+        <v>258</v>
+      </c>
+      <c r="F15" t="s">
+        <v>259</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>261</v>
+      </c>
+      <c r="B16" t="s">
+        <v>209</v>
+      </c>
+      <c r="C16" t="s">
+        <v>210</v>
+      </c>
+      <c r="D16" t="s">
+        <v>204</v>
+      </c>
+      <c r="E16" t="s">
+        <v>262</v>
+      </c>
+      <c r="F16" t="s">
+        <v>212</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>264</v>
+      </c>
+      <c r="B17" t="s">
+        <v>265</v>
+      </c>
+      <c r="C17" t="s">
+        <v>266</v>
+      </c>
+      <c r="D17" t="s">
+        <v>204</v>
+      </c>
+      <c r="E17" t="s">
+        <v>267</v>
+      </c>
+      <c r="F17" t="s">
+        <v>268</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>270</v>
+      </c>
+      <c r="B18" t="s">
+        <v>271</v>
+      </c>
+      <c r="C18" t="s">
+        <v>272</v>
+      </c>
+      <c r="D18" t="s">
+        <v>273</v>
+      </c>
+      <c r="E18" t="s">
+        <v>274</v>
+      </c>
+      <c r="F18" t="s">
+        <v>233</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>276</v>
+      </c>
+      <c r="B19" t="s">
+        <v>277</v>
+      </c>
+      <c r="C19" t="s">
+        <v>278</v>
+      </c>
+      <c r="D19" t="s">
+        <v>204</v>
+      </c>
+      <c r="E19" t="s">
+        <v>279</v>
+      </c>
+      <c r="F19" t="s">
+        <v>280</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>282</v>
+      </c>
+      <c r="B20" t="s">
+        <v>209</v>
+      </c>
+      <c r="C20" t="s">
+        <v>210</v>
+      </c>
+      <c r="D20" t="s">
+        <v>204</v>
+      </c>
+      <c r="E20" t="s">
+        <v>283</v>
+      </c>
+      <c r="F20" t="s">
+        <v>212</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>285</v>
+      </c>
+      <c r="B21" t="s">
+        <v>286</v>
+      </c>
+      <c r="C21" t="s">
+        <v>287</v>
+      </c>
+      <c r="D21" t="s">
+        <v>204</v>
+      </c>
+      <c r="E21" t="s">
+        <v>288</v>
+      </c>
+      <c r="F21" t="s">
+        <v>289</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>35</v>
+      </c>
+      <c r="B22" t="s">
+        <v>291</v>
+      </c>
+      <c r="C22" t="s">
+        <v>292</v>
+      </c>
+      <c r="D22" t="s">
+        <v>204</v>
+      </c>
+      <c r="E22" t="s">
+        <v>293</v>
+      </c>
+      <c r="F22" t="s">
+        <v>294</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>296</v>
+      </c>
+      <c r="B23" t="s">
+        <v>297</v>
+      </c>
+      <c r="C23" t="s">
+        <v>298</v>
+      </c>
+      <c r="D23" t="s">
+        <v>273</v>
+      </c>
+      <c r="E23" t="s">
+        <v>299</v>
+      </c>
+      <c r="F23" t="s">
+        <v>300</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>302</v>
+      </c>
+      <c r="B24" t="s">
+        <v>303</v>
+      </c>
+      <c r="C24" t="s">
+        <v>304</v>
+      </c>
+      <c r="D24" t="s">
+        <v>204</v>
+      </c>
+      <c r="E24" t="s">
+        <v>305</v>
+      </c>
+      <c r="F24" t="s">
+        <v>306</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>308</v>
+      </c>
+      <c r="B25" t="s">
+        <v>309</v>
+      </c>
+      <c r="C25" t="s">
+        <v>278</v>
+      </c>
+      <c r="D25" t="s">
+        <v>204</v>
+      </c>
+      <c r="E25" t="s">
+        <v>310</v>
+      </c>
+      <c r="F25" t="s">
+        <v>311</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>313</v>
+      </c>
+      <c r="B26" t="s">
+        <v>314</v>
+      </c>
+      <c r="C26" t="s">
+        <v>315</v>
+      </c>
+      <c r="D26" t="s">
+        <v>273</v>
+      </c>
+      <c r="E26" t="s">
+        <v>316</v>
+      </c>
+      <c r="F26" t="s">
+        <v>317</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>319</v>
+      </c>
+      <c r="B27" t="s">
+        <v>320</v>
+      </c>
+      <c r="C27" t="s">
+        <v>321</v>
+      </c>
+      <c r="D27" t="s">
+        <v>204</v>
+      </c>
+      <c r="E27" t="s">
+        <v>322</v>
+      </c>
+      <c r="F27" t="s">
+        <v>212</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>324</v>
+      </c>
+      <c r="B28" t="s">
+        <v>303</v>
+      </c>
+      <c r="C28" t="s">
+        <v>304</v>
+      </c>
+      <c r="D28" t="s">
+        <v>204</v>
+      </c>
+      <c r="E28" t="s">
+        <v>325</v>
+      </c>
+      <c r="F28" t="s">
+        <v>306</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>327</v>
+      </c>
+      <c r="B29" t="s">
+        <v>303</v>
+      </c>
+      <c r="C29" t="s">
+        <v>328</v>
+      </c>
+      <c r="D29" t="s">
+        <v>204</v>
+      </c>
+      <c r="E29" t="s">
+        <v>325</v>
+      </c>
+      <c r="F29" t="s">
+        <v>306</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>330</v>
+      </c>
+      <c r="B30" t="s">
+        <v>331</v>
+      </c>
+      <c r="C30" t="s">
+        <v>278</v>
+      </c>
+      <c r="D30" t="s">
+        <v>204</v>
+      </c>
+      <c r="E30" t="s">
+        <v>332</v>
+      </c>
+      <c r="F30" t="s">
+        <v>333</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>330</v>
+      </c>
+      <c r="B31" t="s">
+        <v>335</v>
+      </c>
+      <c r="C31" t="s">
+        <v>257</v>
+      </c>
+      <c r="D31" t="s">
+        <v>273</v>
+      </c>
+      <c r="E31" t="s">
+        <v>336</v>
+      </c>
+      <c r="F31" t="s">
+        <v>192</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>338</v>
+      </c>
+      <c r="B32" t="s">
+        <v>339</v>
+      </c>
+      <c r="C32" t="s">
+        <v>340</v>
+      </c>
+      <c r="D32" t="s">
+        <v>204</v>
+      </c>
+      <c r="E32" t="s">
+        <v>341</v>
+      </c>
+      <c r="F32" t="s">
+        <v>342</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>344</v>
+      </c>
+      <c r="B33" t="s">
+        <v>345</v>
+      </c>
+      <c r="C33" t="s">
+        <v>278</v>
+      </c>
+      <c r="D33" t="s">
+        <v>204</v>
+      </c>
+      <c r="E33" t="s">
+        <v>346</v>
+      </c>
+      <c r="F33" t="s">
+        <v>347</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>349</v>
+      </c>
+      <c r="B34" t="s">
+        <v>350</v>
+      </c>
+      <c r="C34" t="s">
+        <v>278</v>
+      </c>
+      <c r="D34" t="s">
+        <v>204</v>
+      </c>
+      <c r="E34" t="s">
+        <v>351</v>
+      </c>
+      <c r="F34" t="s">
+        <v>300</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>353</v>
+      </c>
+      <c r="B35" t="s">
+        <v>354</v>
+      </c>
+      <c r="C35" t="s">
+        <v>355</v>
+      </c>
+      <c r="D35" t="s">
+        <v>204</v>
+      </c>
+      <c r="E35" t="s">
+        <v>192</v>
+      </c>
+      <c r="F35" t="s">
+        <v>356</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>358</v>
+      </c>
+      <c r="B36" t="s">
+        <v>359</v>
+      </c>
+      <c r="C36" t="s">
+        <v>360</v>
+      </c>
+      <c r="D36" t="s">
+        <v>204</v>
+      </c>
+      <c r="E36" t="s">
+        <v>361</v>
+      </c>
+      <c r="F36" t="s">
+        <v>362</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>364</v>
+      </c>
+      <c r="B37" t="s">
+        <v>365</v>
+      </c>
+      <c r="C37" t="s">
+        <v>366</v>
+      </c>
+      <c r="D37" t="s">
+        <v>204</v>
+      </c>
+      <c r="E37" t="s">
+        <v>367</v>
+      </c>
+      <c r="F37" t="s">
+        <v>368</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>370</v>
+      </c>
+      <c r="B38" t="s">
+        <v>371</v>
+      </c>
+      <c r="C38" t="s">
+        <v>340</v>
+      </c>
+      <c r="D38" t="s">
+        <v>204</v>
+      </c>
+      <c r="E38" t="s">
+        <v>372</v>
+      </c>
+      <c r="F38" t="s">
+        <v>373</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>375</v>
+      </c>
+      <c r="B39" t="s">
+        <v>376</v>
+      </c>
+      <c r="C39" t="s">
+        <v>377</v>
+      </c>
+      <c r="D39" t="s">
+        <v>378</v>
+      </c>
+      <c r="E39" t="s">
+        <v>379</v>
+      </c>
+      <c r="F39" t="s">
+        <v>380</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>382</v>
+      </c>
+      <c r="B40" t="s">
+        <v>383</v>
+      </c>
+      <c r="C40" t="s">
+        <v>384</v>
+      </c>
+      <c r="D40" t="s">
+        <v>204</v>
+      </c>
+      <c r="E40" t="s">
+        <v>385</v>
+      </c>
+      <c r="F40" t="s">
+        <v>192</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>387</v>
+      </c>
+      <c r="B41" t="s">
+        <v>388</v>
+      </c>
+      <c r="C41" t="s">
+        <v>389</v>
+      </c>
+      <c r="D41" t="s">
+        <v>204</v>
+      </c>
+      <c r="E41" t="s">
+        <v>192</v>
+      </c>
+      <c r="F41" t="s">
+        <v>390</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>392</v>
+      </c>
+      <c r="B42" t="s">
+        <v>393</v>
+      </c>
+      <c r="C42" t="s">
+        <v>227</v>
+      </c>
+      <c r="D42" t="s">
+        <v>204</v>
+      </c>
+      <c r="E42" t="s">
+        <v>394</v>
+      </c>
+      <c r="F42" t="s">
+        <v>395</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>397</v>
+      </c>
+      <c r="B43" t="s">
+        <v>398</v>
+      </c>
+      <c r="C43" t="s">
+        <v>399</v>
+      </c>
+      <c r="D43" t="s">
+        <v>204</v>
+      </c>
+      <c r="E43" t="s">
+        <v>400</v>
+      </c>
+      <c r="F43" t="s">
+        <v>192</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>402</v>
+      </c>
+      <c r="B44" t="s">
+        <v>403</v>
+      </c>
+      <c r="C44" t="s">
+        <v>404</v>
+      </c>
+      <c r="D44" t="s">
+        <v>204</v>
+      </c>
+      <c r="E44" t="s">
+        <v>405</v>
+      </c>
+      <c r="F44" t="s">
+        <v>289</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>407</v>
+      </c>
+      <c r="B45" t="s">
+        <v>408</v>
+      </c>
+      <c r="C45" t="s">
+        <v>409</v>
+      </c>
+      <c r="D45" t="s">
+        <v>273</v>
+      </c>
+      <c r="E45" t="s">
+        <v>410</v>
+      </c>
+      <c r="F45" t="s">
+        <v>411</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>413</v>
+      </c>
+      <c r="B46" t="s">
+        <v>414</v>
+      </c>
+      <c r="C46" t="s">
+        <v>415</v>
+      </c>
+      <c r="D46" t="s">
+        <v>204</v>
+      </c>
+      <c r="E46" t="s">
+        <v>416</v>
+      </c>
+      <c r="F46" t="s">
+        <v>417</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>419</v>
+      </c>
+      <c r="B47" t="s">
+        <v>209</v>
+      </c>
+      <c r="C47" t="s">
+        <v>210</v>
+      </c>
+      <c r="D47" t="s">
+        <v>204</v>
+      </c>
+      <c r="E47" t="s">
+        <v>420</v>
+      </c>
+      <c r="F47" t="s">
+        <v>212</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>422</v>
+      </c>
+      <c r="B48" t="s">
+        <v>423</v>
+      </c>
+      <c r="C48" t="s">
+        <v>257</v>
+      </c>
+      <c r="D48" t="s">
+        <v>204</v>
+      </c>
+      <c r="E48" t="s">
+        <v>424</v>
+      </c>
+      <c r="F48" t="s">
+        <v>425</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>427</v>
+      </c>
+      <c r="B49" t="s">
+        <v>428</v>
+      </c>
+      <c r="C49" t="s">
+        <v>298</v>
+      </c>
+      <c r="D49" t="s">
+        <v>378</v>
+      </c>
+      <c r="E49" t="s">
+        <v>429</v>
+      </c>
+      <c r="F49" t="s">
+        <v>430</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>432</v>
+      </c>
+      <c r="B50" t="s">
+        <v>433</v>
+      </c>
+      <c r="C50" t="s">
+        <v>278</v>
+      </c>
+      <c r="D50" t="s">
+        <v>273</v>
+      </c>
+      <c r="E50" t="s">
+        <v>434</v>
+      </c>
+      <c r="F50" t="s">
+        <v>435</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>437</v>
+      </c>
+      <c r="B51" t="s">
+        <v>209</v>
+      </c>
+      <c r="C51" t="s">
+        <v>210</v>
+      </c>
+      <c r="D51" t="s">
+        <v>204</v>
+      </c>
+      <c r="E51" t="s">
+        <v>438</v>
+      </c>
+      <c r="F51" t="s">
+        <v>212</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>440</v>
+      </c>
+      <c r="B52" t="s">
+        <v>303</v>
+      </c>
+      <c r="C52" t="s">
+        <v>441</v>
+      </c>
+      <c r="D52" t="s">
+        <v>204</v>
+      </c>
+      <c r="E52" t="s">
+        <v>442</v>
+      </c>
+      <c r="F52" t="s">
+        <v>306</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>444</v>
+      </c>
+      <c r="B53" t="s">
+        <v>445</v>
+      </c>
+      <c r="C53" t="s">
+        <v>210</v>
+      </c>
+      <c r="D53" t="s">
+        <v>204</v>
+      </c>
+      <c r="E53" t="s">
+        <v>446</v>
+      </c>
+      <c r="F53" t="s">
+        <v>447</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>449</v>
+      </c>
+      <c r="B54" t="s">
+        <v>450</v>
+      </c>
+      <c r="C54" t="s">
+        <v>257</v>
+      </c>
+      <c r="D54" t="s">
+        <v>204</v>
+      </c>
+      <c r="E54" t="s">
+        <v>451</v>
+      </c>
+      <c r="F54" t="s">
+        <v>452</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>454</v>
+      </c>
+      <c r="B55" t="s">
+        <v>309</v>
+      </c>
+      <c r="C55" t="s">
+        <v>278</v>
+      </c>
+      <c r="D55" t="s">
+        <v>204</v>
+      </c>
+      <c r="E55" t="s">
+        <v>455</v>
+      </c>
+      <c r="F55" t="s">
+        <v>311</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>457</v>
+      </c>
+      <c r="B56" t="s">
+        <v>458</v>
+      </c>
+      <c r="C56" t="s">
+        <v>257</v>
+      </c>
+      <c r="D56" t="s">
+        <v>204</v>
+      </c>
+      <c r="E56" t="s">
+        <v>459</v>
+      </c>
+      <c r="F56" t="s">
+        <v>460</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>462</v>
+      </c>
+      <c r="B57" t="s">
+        <v>463</v>
+      </c>
+      <c r="C57" t="s">
+        <v>464</v>
+      </c>
+      <c r="D57" t="s">
+        <v>204</v>
+      </c>
+      <c r="E57" t="s">
+        <v>310</v>
+      </c>
+      <c r="F57" t="s">
+        <v>465</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>467</v>
+      </c>
+      <c r="B58" t="s">
+        <v>468</v>
+      </c>
+      <c r="C58" t="s">
+        <v>278</v>
+      </c>
+      <c r="D58" t="s">
+        <v>204</v>
+      </c>
+      <c r="E58" t="s">
+        <v>469</v>
+      </c>
+      <c r="F58" t="s">
+        <v>192</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>471</v>
+      </c>
+      <c r="B59" t="s">
+        <v>472</v>
+      </c>
+      <c r="C59" t="s">
+        <v>473</v>
+      </c>
+      <c r="D59" t="s">
+        <v>204</v>
+      </c>
+      <c r="E59" t="s">
+        <v>474</v>
+      </c>
+      <c r="F59" t="s">
+        <v>475</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>477</v>
+      </c>
+      <c r="B60" t="s">
+        <v>478</v>
+      </c>
+      <c r="C60" t="s">
+        <v>257</v>
+      </c>
+      <c r="D60" t="s">
+        <v>273</v>
+      </c>
+      <c r="E60" t="s">
+        <v>479</v>
+      </c>
+      <c r="F60" t="s">
+        <v>289</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>481</v>
+      </c>
+      <c r="B61" t="s">
+        <v>482</v>
+      </c>
+      <c r="C61" t="s">
+        <v>257</v>
+      </c>
+      <c r="D61" t="s">
+        <v>204</v>
+      </c>
+      <c r="E61" t="s">
+        <v>455</v>
+      </c>
+      <c r="F61" t="s">
+        <v>192</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>484</v>
+      </c>
+      <c r="B62" t="s">
+        <v>209</v>
+      </c>
+      <c r="C62" t="s">
+        <v>242</v>
+      </c>
+      <c r="D62" t="s">
+        <v>204</v>
+      </c>
+      <c r="E62" t="s">
+        <v>262</v>
+      </c>
+      <c r="F62" t="s">
+        <v>212</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>486</v>
+      </c>
+      <c r="B63" t="s">
+        <v>209</v>
+      </c>
+      <c r="C63" t="s">
+        <v>210</v>
+      </c>
+      <c r="D63" t="s">
+        <v>204</v>
+      </c>
+      <c r="E63" t="s">
+        <v>487</v>
+      </c>
+      <c r="F63" t="s">
+        <v>212</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>489</v>
+      </c>
+      <c r="B64" t="s">
+        <v>490</v>
+      </c>
+      <c r="C64" t="s">
+        <v>340</v>
+      </c>
+      <c r="D64" t="s">
+        <v>204</v>
+      </c>
+      <c r="E64" t="s">
+        <v>491</v>
+      </c>
+      <c r="F64" t="s">
+        <v>492</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>494</v>
+      </c>
+      <c r="B65" t="s">
+        <v>495</v>
+      </c>
+      <c r="C65" t="s">
+        <v>257</v>
+      </c>
+      <c r="D65" t="s">
+        <v>204</v>
+      </c>
+      <c r="E65" t="s">
+        <v>496</v>
+      </c>
+      <c r="F65" t="s">
+        <v>497</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>499</v>
+      </c>
+      <c r="B66" t="s">
+        <v>500</v>
+      </c>
+      <c r="C66" t="s">
+        <v>501</v>
+      </c>
+      <c r="D66" t="s">
+        <v>204</v>
+      </c>
+      <c r="E66" t="s">
+        <v>502</v>
+      </c>
+      <c r="F66" t="s">
+        <v>503</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>505</v>
+      </c>
+      <c r="B67" t="s">
+        <v>506</v>
+      </c>
+      <c r="C67" t="s">
+        <v>321</v>
+      </c>
+      <c r="D67" t="s">
+        <v>204</v>
+      </c>
+      <c r="E67" t="s">
+        <v>507</v>
+      </c>
+      <c r="F67" t="s">
+        <v>508</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>510</v>
+      </c>
+      <c r="B68" t="s">
+        <v>511</v>
+      </c>
+      <c r="C68" t="s">
+        <v>512</v>
+      </c>
+      <c r="D68" t="s">
+        <v>204</v>
+      </c>
+      <c r="E68" t="s">
+        <v>502</v>
+      </c>
+      <c r="F68" t="s">
+        <v>513</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>515</v>
+      </c>
+      <c r="B69" t="s">
+        <v>516</v>
+      </c>
+      <c r="C69" t="s">
+        <v>340</v>
+      </c>
+      <c r="D69" t="s">
+        <v>204</v>
+      </c>
+      <c r="E69" t="s">
+        <v>341</v>
+      </c>
+      <c r="F69" t="s">
+        <v>517</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>519</v>
+      </c>
+      <c r="B70" t="s">
+        <v>331</v>
+      </c>
+      <c r="C70" t="s">
+        <v>278</v>
+      </c>
+      <c r="D70" t="s">
+        <v>204</v>
+      </c>
+      <c r="E70" t="s">
+        <v>332</v>
+      </c>
+      <c r="F70" t="s">
+        <v>333</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>521</v>
+      </c>
+      <c r="B71" t="s">
+        <v>522</v>
+      </c>
+      <c r="C71" t="s">
+        <v>257</v>
+      </c>
+      <c r="D71" t="s">
+        <v>204</v>
+      </c>
+      <c r="E71" t="s">
+        <v>341</v>
+      </c>
+      <c r="F71" t="s">
+        <v>523</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>525</v>
+      </c>
+      <c r="B72" t="s">
+        <v>209</v>
+      </c>
+      <c r="C72" t="s">
+        <v>526</v>
+      </c>
+      <c r="D72" t="s">
+        <v>204</v>
+      </c>
+      <c r="E72" t="s">
+        <v>527</v>
+      </c>
+      <c r="F72" t="s">
+        <v>212</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>529</v>
+      </c>
+      <c r="B73" t="s">
+        <v>530</v>
+      </c>
+      <c r="C73" t="s">
+        <v>531</v>
+      </c>
+      <c r="D73" t="s">
+        <v>204</v>
+      </c>
+      <c r="E73" t="s">
+        <v>532</v>
+      </c>
+      <c r="F73" t="s">
+        <v>533</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>535</v>
+      </c>
+      <c r="B74" t="s">
+        <v>536</v>
+      </c>
+      <c r="C74" t="s">
+        <v>501</v>
+      </c>
+      <c r="D74" t="s">
+        <v>204</v>
+      </c>
+      <c r="E74" t="s">
+        <v>455</v>
+      </c>
+      <c r="F74" t="s">
+        <v>537</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>539</v>
+      </c>
+      <c r="B75" t="s">
+        <v>540</v>
+      </c>
+      <c r="C75" t="s">
+        <v>541</v>
+      </c>
+      <c r="D75" t="s">
+        <v>204</v>
+      </c>
+      <c r="E75" t="s">
+        <v>192</v>
+      </c>
+      <c r="F75" t="s">
+        <v>192</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>543</v>
+      </c>
+      <c r="B76" t="s">
+        <v>544</v>
+      </c>
+      <c r="C76" t="s">
+        <v>257</v>
+      </c>
+      <c r="D76" t="s">
+        <v>204</v>
+      </c>
+      <c r="E76" t="s">
+        <v>424</v>
+      </c>
+      <c r="F76" t="s">
+        <v>545</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>547</v>
+      </c>
+      <c r="B77" t="s">
+        <v>548</v>
+      </c>
+      <c r="C77" t="s">
+        <v>257</v>
+      </c>
+      <c r="D77" t="s">
+        <v>204</v>
+      </c>
+      <c r="E77" t="s">
+        <v>549</v>
+      </c>
+      <c r="F77" t="s">
+        <v>550</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>552</v>
+      </c>
+      <c r="B78" t="s">
+        <v>553</v>
+      </c>
+      <c r="C78" t="s">
+        <v>278</v>
+      </c>
+      <c r="D78" t="s">
+        <v>204</v>
+      </c>
+      <c r="E78" t="s">
+        <v>554</v>
+      </c>
+      <c r="F78" t="s">
+        <v>492</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>556</v>
+      </c>
+      <c r="B79" t="s">
+        <v>557</v>
+      </c>
+      <c r="C79" t="s">
+        <v>501</v>
+      </c>
+      <c r="D79" t="s">
+        <v>204</v>
+      </c>
+      <c r="E79" t="s">
+        <v>558</v>
+      </c>
+      <c r="F79" t="s">
+        <v>559</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>561</v>
+      </c>
+      <c r="B80" t="s">
+        <v>271</v>
+      </c>
+      <c r="C80" t="s">
+        <v>272</v>
+      </c>
+      <c r="D80" t="s">
+        <v>204</v>
+      </c>
+      <c r="E80" t="s">
+        <v>562</v>
+      </c>
+      <c r="F80" t="s">
+        <v>233</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>564</v>
+      </c>
+      <c r="B81" t="s">
+        <v>428</v>
+      </c>
+      <c r="C81" t="s">
+        <v>298</v>
+      </c>
+      <c r="D81" t="s">
+        <v>204</v>
+      </c>
+      <c r="E81" t="s">
+        <v>565</v>
+      </c>
+      <c r="F81" t="s">
+        <v>566</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>568</v>
+      </c>
+      <c r="B82" t="s">
+        <v>569</v>
+      </c>
+      <c r="C82" t="s">
+        <v>278</v>
+      </c>
+      <c r="D82" t="s">
+        <v>198</v>
+      </c>
+      <c r="E82" t="s">
+        <v>570</v>
+      </c>
+      <c r="F82" t="s">
+        <v>571</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>573</v>
+      </c>
+      <c r="B83" t="s">
+        <v>574</v>
+      </c>
+      <c r="C83" t="s">
+        <v>575</v>
+      </c>
+      <c r="D83" t="s">
+        <v>204</v>
+      </c>
+      <c r="E83" t="s">
+        <v>576</v>
+      </c>
+      <c r="F83" t="s">
+        <v>192</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>578</v>
+      </c>
+      <c r="B84" t="s">
+        <v>209</v>
+      </c>
+      <c r="C84" t="s">
+        <v>210</v>
+      </c>
+      <c r="D84" t="s">
+        <v>204</v>
+      </c>
+      <c r="E84" t="s">
+        <v>420</v>
+      </c>
+      <c r="F84" t="s">
+        <v>212</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>580</v>
+      </c>
+      <c r="B85" t="s">
+        <v>581</v>
+      </c>
+      <c r="C85" t="s">
+        <v>582</v>
+      </c>
+      <c r="D85" t="s">
+        <v>204</v>
+      </c>
+      <c r="E85" t="s">
+        <v>274</v>
+      </c>
+      <c r="F85" t="s">
+        <v>583</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>585</v>
+      </c>
+      <c r="B86" t="s">
+        <v>586</v>
+      </c>
+      <c r="C86" t="s">
+        <v>587</v>
+      </c>
+      <c r="D86" t="s">
+        <v>204</v>
+      </c>
+      <c r="E86" t="s">
+        <v>588</v>
+      </c>
+      <c r="F86" t="s">
+        <v>589</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>591</v>
+      </c>
+      <c r="B87" t="s">
+        <v>221</v>
+      </c>
+      <c r="C87" t="s">
+        <v>592</v>
+      </c>
+      <c r="D87" t="s">
+        <v>204</v>
+      </c>
+      <c r="E87" t="s">
+        <v>192</v>
+      </c>
+      <c r="F87" t="s">
+        <v>223</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>594</v>
+      </c>
+      <c r="B88" t="s">
+        <v>221</v>
+      </c>
+      <c r="C88" t="s">
+        <v>592</v>
+      </c>
+      <c r="D88" t="s">
+        <v>204</v>
+      </c>
+      <c r="E88" t="s">
+        <v>192</v>
+      </c>
+      <c r="F88" t="s">
+        <v>223</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>596</v>
+      </c>
+      <c r="B89" t="s">
+        <v>597</v>
+      </c>
+      <c r="C89" t="s">
+        <v>278</v>
+      </c>
+      <c r="D89" t="s">
+        <v>198</v>
+      </c>
+      <c r="E89" t="s">
+        <v>598</v>
+      </c>
+      <c r="F89" t="s">
+        <v>599</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>601</v>
+      </c>
+      <c r="B90" t="s">
+        <v>602</v>
+      </c>
+      <c r="C90" t="s">
+        <v>501</v>
+      </c>
+      <c r="D90" t="s">
+        <v>198</v>
+      </c>
+      <c r="E90" t="s">
+        <v>603</v>
+      </c>
+      <c r="F90" t="s">
+        <v>604</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>606</v>
+      </c>
+      <c r="B91" t="s">
+        <v>303</v>
+      </c>
+      <c r="C91" t="s">
+        <v>328</v>
+      </c>
+      <c r="D91" t="s">
+        <v>204</v>
+      </c>
+      <c r="E91" t="s">
+        <v>607</v>
+      </c>
+      <c r="F91" t="s">
+        <v>306</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>609</v>
+      </c>
+      <c r="B92" t="s">
+        <v>303</v>
+      </c>
+      <c r="C92" t="s">
+        <v>328</v>
+      </c>
+      <c r="D92" t="s">
+        <v>204</v>
+      </c>
+      <c r="E92" t="s">
+        <v>607</v>
+      </c>
+      <c r="F92" t="s">
+        <v>342</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>609</v>
+      </c>
+      <c r="B93" t="s">
+        <v>303</v>
+      </c>
+      <c r="C93" t="s">
+        <v>304</v>
+      </c>
+      <c r="D93" t="s">
+        <v>204</v>
+      </c>
+      <c r="E93" t="s">
+        <v>607</v>
+      </c>
+      <c r="F93" t="s">
+        <v>342</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>612</v>
+      </c>
+      <c r="B94" t="s">
+        <v>303</v>
+      </c>
+      <c r="C94" t="s">
+        <v>304</v>
+      </c>
+      <c r="D94" t="s">
+        <v>204</v>
+      </c>
+      <c r="E94" t="s">
+        <v>607</v>
+      </c>
+      <c r="F94" t="s">
+        <v>613</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>615</v>
+      </c>
+      <c r="B95" t="s">
+        <v>616</v>
+      </c>
+      <c r="C95" t="s">
+        <v>399</v>
+      </c>
+      <c r="D95" t="s">
+        <v>204</v>
+      </c>
+      <c r="E95" t="s">
+        <v>617</v>
+      </c>
+      <c r="F95" t="s">
+        <v>618</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>620</v>
+      </c>
+      <c r="B96" t="s">
+        <v>388</v>
+      </c>
+      <c r="C96" t="s">
+        <v>621</v>
+      </c>
+      <c r="D96" t="s">
+        <v>378</v>
+      </c>
+      <c r="E96" t="s">
+        <v>192</v>
+      </c>
+      <c r="F96" t="s">
+        <v>622</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>624</v>
+      </c>
+      <c r="B97" t="s">
+        <v>388</v>
+      </c>
+      <c r="C97" t="s">
+        <v>625</v>
+      </c>
+      <c r="D97" t="s">
+        <v>378</v>
+      </c>
+      <c r="E97" t="s">
+        <v>192</v>
+      </c>
+      <c r="F97" t="s">
+        <v>622</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>627</v>
+      </c>
+      <c r="B98" t="s">
+        <v>388</v>
+      </c>
+      <c r="C98" t="s">
+        <v>628</v>
+      </c>
+      <c r="D98" t="s">
+        <v>378</v>
+      </c>
+      <c r="E98" t="s">
+        <v>192</v>
+      </c>
+      <c r="F98" t="s">
+        <v>622</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>629</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+    <hyperlink ref="H43" r:id="rId42"/>
+    <hyperlink ref="H44" r:id="rId43"/>
+    <hyperlink ref="H45" r:id="rId44"/>
+    <hyperlink ref="H46" r:id="rId45"/>
+    <hyperlink ref="H47" r:id="rId46"/>
+    <hyperlink ref="H48" r:id="rId47"/>
+    <hyperlink ref="H49" r:id="rId48"/>
+    <hyperlink ref="H50" r:id="rId49"/>
+    <hyperlink ref="H51" r:id="rId50"/>
+    <hyperlink ref="H52" r:id="rId51"/>
+    <hyperlink ref="H53" r:id="rId52"/>
+    <hyperlink ref="H54" r:id="rId53"/>
+    <hyperlink ref="H55" r:id="rId54"/>
+    <hyperlink ref="H56" r:id="rId55"/>
+    <hyperlink ref="H57" r:id="rId56"/>
+    <hyperlink ref="H58" r:id="rId57"/>
+    <hyperlink ref="H59" r:id="rId58"/>
+    <hyperlink ref="H60" r:id="rId59"/>
+    <hyperlink ref="H61" r:id="rId60"/>
+    <hyperlink ref="H62" r:id="rId61"/>
+    <hyperlink ref="H63" r:id="rId62"/>
+    <hyperlink ref="H64" r:id="rId63"/>
+    <hyperlink ref="H65" r:id="rId64"/>
+    <hyperlink ref="H66" r:id="rId65"/>
+    <hyperlink ref="H67" r:id="rId66"/>
+    <hyperlink ref="H68" r:id="rId67"/>
+    <hyperlink ref="H69" r:id="rId68"/>
+    <hyperlink ref="H70" r:id="rId69"/>
+    <hyperlink ref="H71" r:id="rId70"/>
+    <hyperlink ref="H72" r:id="rId71"/>
+    <hyperlink ref="H73" r:id="rId72"/>
+    <hyperlink ref="H74" r:id="rId73"/>
+    <hyperlink ref="H75" r:id="rId74"/>
+    <hyperlink ref="H76" r:id="rId75"/>
+    <hyperlink ref="H77" r:id="rId76"/>
+    <hyperlink ref="H78" r:id="rId77"/>
+    <hyperlink ref="H79" r:id="rId78"/>
+    <hyperlink ref="H80" r:id="rId79"/>
+    <hyperlink ref="H81" r:id="rId80"/>
+    <hyperlink ref="H82" r:id="rId81"/>
+    <hyperlink ref="H83" r:id="rId82"/>
+    <hyperlink ref="H84" r:id="rId83"/>
+    <hyperlink ref="H85" r:id="rId84"/>
+    <hyperlink ref="H86" r:id="rId85"/>
+    <hyperlink ref="H87" r:id="rId86"/>
+    <hyperlink ref="H88" r:id="rId87"/>
+    <hyperlink ref="H89" r:id="rId88"/>
+    <hyperlink ref="H90" r:id="rId89"/>
+    <hyperlink ref="H91" r:id="rId90"/>
+    <hyperlink ref="H92" r:id="rId91"/>
+    <hyperlink ref="H93" r:id="rId92"/>
+    <hyperlink ref="H94" r:id="rId93"/>
+    <hyperlink ref="H95" r:id="rId94"/>
+    <hyperlink ref="H96" r:id="rId95"/>
+    <hyperlink ref="H97" r:id="rId96"/>
+    <hyperlink ref="H98" r:id="rId97"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/docs/xlsx/jobs-2026-10-09.xlsx
+++ b/docs/xlsx/jobs-2026-10-09.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="949" uniqueCount="630">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1292" uniqueCount="854">
   <si>
     <t>Title</t>
   </si>
@@ -601,6 +601,27 @@
     <t>https://greenjobs.greenjobsearch.org/jobs/senior-environmental-specialist-tribal-brownfields/</t>
   </si>
   <si>
+    <t>Volunteer Intern Coordinator – UNPAID</t>
+  </si>
+  <si>
+    <t>Climate Steps</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>Part-Time</t>
+  </si>
+  <si>
+    <t>Less than 20,000</t>
+  </si>
+  <si>
+    <t>Climate Change</t>
+  </si>
+  <si>
+    <t>https://greenjobs.greenjobsearch.org/jobs/volunteer-intern-coordinator-unpaid/</t>
+  </si>
+  <si>
     <t>🌍 Líder de Equipo F2F Vía Pública | Donantes Individuales | Turno Mañana o Tarde | CABA</t>
   </si>
   <si>
@@ -619,6 +640,27 @@
     <t>https://www.idealist.org/en/nonprofit-job/84bb675107d849af8da56e11af7cee41-lider-de-equipo-f2f-via-publica-donantes-individuales-turno-manana-o-tarde-caba-ingenieria-sin-fronteras-argentina-buenos-aires</t>
   </si>
   <si>
+    <t>Administrative Associate</t>
+  </si>
+  <si>
+    <t>Center for Gender &amp; Refugee Studies (CGRS)</t>
+  </si>
+  <si>
+    <t>San Francisco, California</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>USD 28.41 - 32.00/hour</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Immigrants Or Refugees, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/75812aa1ac764715b56f985b73918782-administrative-associate-center-for-gender-refugee-studies-cgrs-san-francisco</t>
+  </si>
+  <si>
     <t>Administrative Coordinator</t>
   </si>
   <si>
@@ -628,9 +670,6 @@
     <t>Baden, Pennsylvania</t>
   </si>
   <si>
-    <t>Full Time</t>
-  </si>
-  <si>
     <t>USD 22.50/hour</t>
   </si>
   <si>
@@ -676,6 +715,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/21b3e6161e1e4eeba5046ae4f6116038-advancement-assistant-wildcareorg-san-rafael</t>
   </si>
   <si>
+    <t>Advancement Coordinator</t>
+  </si>
+  <si>
+    <t>Tudor Place Historic House &amp; Garden</t>
+  </si>
+  <si>
+    <t>Washington, District of Columbia</t>
+  </si>
+  <si>
+    <t>USD 45000.00 - 48000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Education, Travel Hospitality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/333324961bda41f9b0763d1c9cabcd47-advancement-coordinator-tudor-place-historic-house-garden-washington</t>
+  </si>
+  <si>
     <t>APOYO ESCOLAR - CENTRO BARRIAL LA LUCILA</t>
   </si>
   <si>
@@ -799,6 +856,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/74fa805efd5748acb3819d3125e92a76-bilingual-intensive-case-manager-social-worker-restore-nyc-new-york</t>
   </si>
   <si>
+    <t>Bilingual Receptionist</t>
+  </si>
+  <si>
+    <t>Hadsell Stormer Renick &amp; Dai LLP</t>
+  </si>
+  <si>
+    <t>Part Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 20.00 - 25.00/hour</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/32234cc8bf32417fa98a3ee216f1c8c9-bilingual-receptionist-hadsell-stormer-renick-dai-llp-los-angeles</t>
+  </si>
+  <si>
     <t>Case Manager (Stay Housed LA) - Eviction Defense Center Workgroup</t>
   </si>
   <si>
@@ -826,6 +901,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/71a20cf3002248a4bca6d30f71032f2d-chief-finance-officer-center-for-large-landscape-conservation-bozeman</t>
   </si>
   <si>
+    <t>The 19th</t>
+  </si>
+  <si>
+    <t>USD 190000.00 - 215000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Lgbtq, Media</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/773446128b7b4c28b4cd2a1e8bdf0188-chief-product-officer-the-19th-austin</t>
+  </si>
+  <si>
     <t>Childcare Outreach and Enrollment Coordinator</t>
   </si>
   <si>
@@ -850,9 +937,6 @@
     <t>Climate Science Legal Defense Fund</t>
   </si>
   <si>
-    <t>Remote</t>
-  </si>
-  <si>
     <t>USD 95000.00 - 105000.00/year</t>
   </si>
   <si>
@@ -904,6 +988,36 @@
     <t>https://www.idealist.org/en/nonprofit-job/dfbcc32a936643b0b02e71a809d091cd-community-engagement-manager-chai-comprehensive-housing-assistance-inc-baltimore</t>
   </si>
   <si>
+    <t>Community Fundraising &amp; Campaigns Coordinator</t>
+  </si>
+  <si>
+    <t>Kesem National</t>
+  </si>
+  <si>
+    <t>USD 58000.00 - 63000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0e3feb900d3040e49c918ddeef27f660-community-fundraising-campaigns-coordinator-kesem-national-covina</t>
+  </si>
+  <si>
+    <t>Community Outreach &amp; Referral Partnerships Coordinator</t>
+  </si>
+  <si>
+    <t>Concerned Home Managers for the Elderly, Inc.</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>USD 35.00 - 40.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ef172b4396c44041967f8eadac539b6e-community-outreach-referral-partnerships-coordinator-concerned-home-managers-for-the-elderly-inc-new-york</t>
+  </si>
+  <si>
     <t>Community Roots Charter School, 7th Grade Humanities, Family Leave, 01/2027-06/2027</t>
   </si>
   <si>
@@ -940,6 +1054,39 @@
     <t>https://www.idealist.org/en/nonprofit-job/8002eb9e01254ab7ba4294fd0051880c-community-worker-guru-shardha-welfare-charity-calgary</t>
   </si>
   <si>
+    <t>Contract Art Therapist in Bronx Schools (2 full days per week)</t>
+  </si>
+  <si>
+    <t>ART THERAPY PROJECT CORPORATION (TATP)., THE</t>
+  </si>
+  <si>
+    <t>Bronx County, New York</t>
+  </si>
+  <si>
+    <t>USD 600.00 - 600.00/day</t>
+  </si>
+  <si>
+    <t>Children Youth, Mental Health, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c23a9bcf12484d3f89d5aafc33352023-contract-art-therapist-in-bronx-schools-2-full-days-per-week-art-therapy-project-corporation-tatp-the-bronx-county</t>
+  </si>
+  <si>
+    <t>Conversation Class Instructor –Adults</t>
+  </si>
+  <si>
+    <t>Kandelia</t>
+  </si>
+  <si>
+    <t>USD 7440.00 - 11640.00/year</t>
+  </si>
+  <si>
+    <t>Education, Family, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c20bbd3029694945a6922613468188d3-conversation-class-instructor-adults-kandelia-seattle</t>
+  </si>
+  <si>
     <t>Coordinator, Public Health Initiatives – Hypertensive Disorders of Pregnancy (Grant-Funded Position)</t>
   </si>
   <si>
@@ -1006,6 +1153,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/5d3da0ab19414e8fb37af94c81783738-delivery-driver-guru-shardha-welfare-charity-mississauga</t>
   </si>
   <si>
+    <t>Development &amp; Operations Co-Director</t>
+  </si>
+  <si>
+    <t>"We Always Swing"® Jazz Series</t>
+  </si>
+  <si>
+    <t>Columbia, Missouri</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f0d47fcb54bf45fb820f6517ca17172f-development-operations-co-director-we-always-swing-jazz-series-columbia</t>
+  </si>
+  <si>
     <t>Development Coordinator</t>
   </si>
   <si>
@@ -1030,15 +1195,27 @@
     <t>https://www.idealist.org/en/job/7167b7d504df4d5fa7dbf000e6a55f2b-development-coordinator-careers-in-nonprofits-inc-new-york</t>
   </si>
   <si>
+    <t>Development Operations Specialist</t>
+  </si>
+  <si>
+    <t>Pratt Fine Arts Center, Seattle WA</t>
+  </si>
+  <si>
+    <t>Seattle, WA</t>
+  </si>
+  <si>
+    <t>USD 28.00 - 34.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c9fcd4abe9c7402783070f8a82ac7755-development-operations-specialist-pratt-fine-arts-center-seattle-wa-seattle</t>
+  </si>
+  <si>
     <t>Digital Content Manager</t>
   </si>
   <si>
     <t>American Association of State Highway &amp; Transportation Officials</t>
   </si>
   <si>
-    <t>Washington, District of Columbia</t>
-  </si>
-  <si>
     <t>USD 80000.00 - 90000.00/year</t>
   </si>
   <si>
@@ -1063,6 +1240,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/c1b9968bedb5467f8e8cf8bfb319fc47-digital-marketing-manager-points-of-light-atlanta</t>
   </si>
   <si>
+    <t>Director of Family and Youth</t>
+  </si>
+  <si>
+    <t>Comunidad VA</t>
+  </si>
+  <si>
+    <t>Seven Corners, Virginia</t>
+  </si>
+  <si>
+    <t>USD 73000.00 - 91000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/de3b67896da748fa9688eb5f2c77d704-director-of-family-and-youth-comunidad-va-seven-corners</t>
+  </si>
+  <si>
     <t>Director of Finance</t>
   </si>
   <si>
@@ -1090,6 +1285,33 @@
     <t>https://www.idealist.org/en/nonprofit-job/c5b55641020e4582b4e665bc35d5fb4d-director-of-human-resources-wissahickon-charter-school-philadelphia</t>
   </si>
   <si>
+    <t>Director of People &amp; Culture</t>
+  </si>
+  <si>
+    <t>Chimp Haven, Inc.</t>
+  </si>
+  <si>
+    <t>Shreveport, Louisiana</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e39206381e8c4abfadea1bbb92d9b465-director-of-people-culture-chimp-haven-inc-shreveport</t>
+  </si>
+  <si>
+    <t>Director of Policy, Food, Agriculture &amp; Rural Economies</t>
+  </si>
+  <si>
+    <t>State Innovation Exchange</t>
+  </si>
+  <si>
+    <t>USD 110000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c9a3fbfa5e754664ac868cd03ada359f-director-of-policy-food-agriculture-rural-economies-state-innovation-exchange-denver</t>
+  </si>
+  <si>
     <t>Director of Pro Bono Programs</t>
   </si>
   <si>
@@ -1126,6 +1348,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/b9f93ebe24c34805990971cd6317e24c-director-of-programs-climate-science-alliance-san-diego</t>
   </si>
   <si>
+    <t>Director, Meeting Operations</t>
+  </si>
+  <si>
+    <t>American Association for Justice</t>
+  </si>
+  <si>
+    <t>USD 130000.00 - 150000.00/year</t>
+  </si>
+  <si>
+    <t>Crime Safety, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/be1ae1346f5f4d60ab7dbc73436d41cd-director-meeting-operations-american-association-for-justice-washington</t>
+  </si>
+  <si>
     <t>Director, Washington, DC</t>
   </si>
   <si>
@@ -1135,12 +1372,78 @@
     <t>USD 133000.00 - 157000.00/year</t>
   </si>
   <si>
-    <t>Human Rights Civil Liberties</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/3cd5ecc58b674327b9fd45204a7947f8-director-washington-dc-human-rights-watch-washington</t>
   </si>
   <si>
+    <t>Executive Director</t>
+  </si>
+  <si>
+    <t>Colorado Doula Project</t>
+  </si>
+  <si>
+    <t>Remote (Colorado)</t>
+  </si>
+  <si>
+    <t>USD 88000.00 - 98000.00/year</t>
+  </si>
+  <si>
+    <t>Lgbtq, Reproductive Health Rights, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8afd261d7bcb4d95956cb1f91a0dff0c-executive-director-colorado-doula-project-denver</t>
+  </si>
+  <si>
+    <t>National Speleological Society</t>
+  </si>
+  <si>
+    <t>Huntsville, Alabama</t>
+  </si>
+  <si>
+    <t>Education, Environment, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/35c30c58188f4db0a7f36bd4b4e34824-executive-director-national-speleological-society-huntsville</t>
+  </si>
+  <si>
+    <t>SAJ</t>
+  </si>
+  <si>
+    <t>USD 135000.00 - 155000.00/year</t>
+  </si>
+  <si>
+    <t>Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bd93f3c3413a47a09d2d5b41aba84091-executive-director-saj-new-york</t>
+  </si>
+  <si>
+    <t>Kitty Bungalow Charm School for Wayward Cats</t>
+  </si>
+  <si>
+    <t>USD 75000.00/year</t>
+  </si>
+  <si>
+    <t>Animals, Conflict Resolution, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/be44f81615f2492cbb45e5077a7fb164-executive-director-kitty-bungalow-charm-school-for-wayward-cats-los-angeles</t>
+  </si>
+  <si>
+    <t>Executive Director – Revitalize San Pedro Partnership (RSPP)</t>
+  </si>
+  <si>
+    <t>Revitalize San Pedro Partnership</t>
+  </si>
+  <si>
+    <t>USD 65000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Entrepreneurship</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/46133297bd80473787f65704bf2284ea-executive-director-revitalize-san-pedro-partnership-rspp-revitalize-san-pedro-partnership-albuquerque</t>
+  </si>
+  <si>
     <t>Executive Director/Managing Agent -- Sudbury Housing Authority</t>
   </si>
   <si>
@@ -1150,9 +1453,6 @@
     <t>Sudbury, Massachusetts</t>
   </si>
   <si>
-    <t>Part Time</t>
-  </si>
-  <si>
     <t>USD 62682.30 - 69547.00/year</t>
   </si>
   <si>
@@ -1231,9 +1531,6 @@
     <t>Providence, Rhode Island</t>
   </si>
   <si>
-    <t>USD 65000.00/year</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/3113d39b8c674d89b720285ee74ea943-fellowship-program-manager-college-visions-providence</t>
   </si>
   <si>
@@ -1327,6 +1624,42 @@
     <t>https://www.idealist.org/en/nonprofit-job/5db9620d583b48998fc8c245cb971cdc-habeas-operations-senior-manager-immigrant-arc-albany</t>
   </si>
   <si>
+    <t>Home Tutors – Hyderabad &amp; Telangana</t>
+  </si>
+  <si>
+    <t>Shiva's Tutorial</t>
+  </si>
+  <si>
+    <t>Hyderabad, Telangana, IN</t>
+  </si>
+  <si>
+    <t>USD 5.00 - 20.00/hour</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/60aa8d108d02438e85226925ad5158d2-home-tutors-hyderabad-telangana-shivas-tutorial-hyderabad</t>
+  </si>
+  <si>
+    <t>Housing Attorney (NO Eviction Defense) (Hybrid)</t>
+  </si>
+  <si>
+    <t>Mental Health Advocacy Services, Inc.</t>
+  </si>
+  <si>
+    <t>Glendale, California</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 105000.00/year</t>
+  </si>
+  <si>
+    <t>Disability, Human Rights Civil Liberties, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e3fba1b9f66941339f4704afac1daf97-housing-attorney-no-eviction-defense-hybrid-mental-health-advocacy-services-inc-glendale</t>
+  </si>
+  <si>
     <t>Housing/Consumer Attorney (Disaster Legal Services) – Pro Bono Workgroup</t>
   </si>
   <si>
@@ -1348,6 +1681,51 @@
     <t>https://www.idealist.org/en/nonprofit-job/6d7daec608bf4cb1a7d73de89ac7a45c-hr-coordinator-guru-shardha-welfare-charity-regina</t>
   </si>
   <si>
+    <t>Immigration Staff Attorney - Hybrid/Remote - Eastern Massachusetts</t>
+  </si>
+  <si>
+    <t>New England Justice for Our Neighbors</t>
+  </si>
+  <si>
+    <t>Belmont, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Victim Support, Immigrants Or Refugees, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4af0f064f2d34d9da82dd68a03d50ef0-immigration-staff-attorney-hybridremote-eastern-massachusetts-new-england-justice-for-our-neighbors-belmont</t>
+  </si>
+  <si>
+    <t>Individual Giving and Donor Engagement Manager</t>
+  </si>
+  <si>
+    <t>Together for Girls</t>
+  </si>
+  <si>
+    <t>USD 72000.00 - 84000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cbc0fef0d76346029b931847ea9be087-individual-giving-and-donor-engagement-manager-together-for-girls-washington</t>
+  </si>
+  <si>
+    <t>Litigation Assistant</t>
+  </si>
+  <si>
+    <t>Neighborhood Defender Service of Harlem, New York</t>
+  </si>
+  <si>
+    <t>USD 68500.00 - 80650.00/year</t>
+  </si>
+  <si>
+    <t>Crime Safety, Human Rights Civil Liberties, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/35d0466389f8408490eb202ab924abae-litigation-assistant-neighborhood-defender-service-of-harlem-new-york-new-york</t>
+  </si>
+  <si>
     <t>Major Gifts Officer</t>
   </si>
   <si>
@@ -1357,9 +1735,6 @@
     <t>USD 80000.00 - 95000.00/year</t>
   </si>
   <si>
-    <t>Community Development, Economic Development, Education</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/26f318a26f324e888cbab9ca2cbb2c0b-major-gifts-officer-united-way-of-greater-los-angeles-los-angeles</t>
   </si>
   <si>
@@ -1402,6 +1777,12 @@
     <t>https://www.idealist.org/en/nonprofit-job/8a9019df92b3430ebb25e355c3060b3d-managing-director-gift-planning-legacy-giving-the-breast-cancer-research-foundation-new-york</t>
   </si>
   <si>
+    <t>Marketing Coordinator</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/326e0c377e6f4df0a458d3cb0beddcf4-marketing-coordinator-tudor-place-historic-house-garden-washington</t>
+  </si>
+  <si>
     <t>Marketing Manager</t>
   </si>
   <si>
@@ -1417,6 +1798,51 @@
     <t>https://www.idealist.org/en/nonprofit-job/323238468af349088aa3754d2f98180b-marketing-manager-temple-beth-am-jupiter-jupiter</t>
   </si>
   <si>
+    <t>MCLE Program Assistant</t>
+  </si>
+  <si>
+    <t>Oregon State Bar</t>
+  </si>
+  <si>
+    <t>Tigard, OR</t>
+  </si>
+  <si>
+    <t>USD 22.61 - 28.26/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a57a2ab879594a4289852aa5cb3705d4-mcle-program-assistant-oregon-state-bar-tigard</t>
+  </si>
+  <si>
+    <t>Meals on Wheels Driver</t>
+  </si>
+  <si>
+    <t>Union Settlement Association</t>
+  </si>
+  <si>
+    <t>new york, ny, NY</t>
+  </si>
+  <si>
+    <t>USD 17.00 - 17.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ce690cf3133f47d9ad7032c07ec1902e-meals-on-wheels-driver-union-settlement-association-new-york-ny</t>
+  </si>
+  <si>
+    <t>Membership Coordinator, Contractor</t>
+  </si>
+  <si>
+    <t>Virtual Executives</t>
+  </si>
+  <si>
+    <t>USD 40.00 - 50.00/hour</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Education, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/8b798d1a8d6b465f80f3380e8d2dcba7-membership-coordinator-contractor-virtual-executives-new-york</t>
+  </si>
+  <si>
     <t>Membership Manager, Education Writers Association</t>
   </si>
   <si>
@@ -1468,12 +1894,57 @@
     <t>https://www.idealist.org/en/nonprofit-job/70d9c4385503494db9c226425e5553e5-operations-manager-united-neighborhood-houses-new-york</t>
   </si>
   <si>
+    <t>Paralegal - Domestic Violence Project (FJC)</t>
+  </si>
+  <si>
+    <t>Counsel for Justice</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 35.00/hour</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Immigrants Or Refugees, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/37f7cb7b1b02487cbd12a5692a91dc54-paralegal-domestic-violence-project-fjc-counsel-for-justice-los-angeles</t>
+  </si>
+  <si>
     <t>Paralegal (Stay Housed LA/Right to Counsel) – Santa Monica Workgroup</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/bcc06c0d31834578ad623771a6737326-paralegal-stay-housed-laright-to-counsel-santa-monica-workgroup-legal-aid-foundation-of-los-angeles-santa-monica</t>
   </si>
   <si>
+    <t>Paralegal, ACLU of Vermont</t>
+  </si>
+  <si>
+    <t>ACLU of Vermont</t>
+  </si>
+  <si>
+    <t>Montpelier, VT</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/72f84243edf64b758f43d1b13d2013d6-paralegal-aclu-of-vermont-aclu-of-vermont-montpelier</t>
+  </si>
+  <si>
+    <t>PART-TIME PROGRAM ASSISTANT</t>
+  </si>
+  <si>
+    <t>Open Path Psychotherapy Collective</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 25.00/hour</t>
+  </si>
+  <si>
+    <t>Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0931b2fb37a74ebaa440042a146e1f06-part-time-program-assistant-open-path-psychotherapy-collective-asheville</t>
+  </si>
+  <si>
     <t>Post Graduate Fellow (Housing Justice) - Eviction Defense Center Workgroup</t>
   </si>
   <si>
@@ -1492,9 +1963,6 @@
     <t>USD 110000.00 - 140000.00/year</t>
   </si>
   <si>
-    <t>Policy</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/job/3035b83e5b3d4347bc29493a24fd8dd9-press-secretary-groundwork-collaborative-washington</t>
   </si>
   <si>
@@ -1519,27 +1987,42 @@
     <t>Pachamama Alliance</t>
   </si>
   <si>
-    <t>San Francisco, California</t>
-  </si>
-  <si>
-    <t>USD 75000.00 - 85000.00/year</t>
-  </si>
-  <si>
     <t>Environment, Climate Change, Community Development</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/c50bd93557e24e3ca41499d87f2665dd-program-coordinator-pachamama-alliance-san-francisco</t>
   </si>
   <si>
+    <t>Our Minds Matter</t>
+  </si>
+  <si>
+    <t>USD 64789.00 - 77248.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b0d8cf2dc5f14404acce0b11a073ff80-program-coordinator-our-minds-matter-washington</t>
+  </si>
+  <si>
+    <t>Creator Accountability Network</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Conflict Resolution, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fc905570889d488d8645a0e48f6c59a3-program-director-creator-accountability-network-philadelphia</t>
+  </si>
+  <si>
     <t>Program Manager, Audience Reach and Communications</t>
   </si>
   <si>
     <t>Jewish Story Partners</t>
   </si>
   <si>
-    <t>USD 70000.00 - 80000.00/year</t>
-  </si>
-  <si>
     <t>Arts Music, Media, Religion Spirituality</t>
   </si>
   <si>
@@ -1645,6 +2128,30 @@
     <t>https://www.idealist.org/en/nonprofit-job/80ec95dae98646658d7ec93793bf68be-responsable-de-desarrollo-y-alianzas-caba-bs-as-asociacion-civil-pata-pila-buenos-aires</t>
   </si>
   <si>
+    <t>Retreat Support Associate (RSA) - Extra Hire</t>
+  </si>
+  <si>
+    <t>Spirit Rock Meditation Center</t>
+  </si>
+  <si>
+    <t>Woodacre, CA</t>
+  </si>
+  <si>
+    <t>USD 240.00 - 240.00/day</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/77ea9169373d47a1acda18f31801c120-retreat-support-associate-rsa-extra-hire-spirit-rock-meditation-center-woodacre</t>
+  </si>
+  <si>
+    <t>Retreat Support Associate (RSA) - Residential</t>
+  </si>
+  <si>
+    <t>USD 174.00 - 174.00/day</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2bd06e373f174d6998161e991d65bceb-retreat-support-associate-rsa-residential-spirit-rock-meditation-center-woodacre</t>
+  </si>
+  <si>
     <t>Revenue Operations Coordinator</t>
   </si>
   <si>
@@ -1657,6 +2164,48 @@
     <t>https://www.idealist.org/en/nonprofit-job/9cd2205d9e7b4d5f8c0054fcd1efc80a-revenue-operations-coordinator-partnership-to-end-addiction-new-york</t>
   </si>
   <si>
+    <t>RLC Field Sales Representative (Boston, MA)</t>
+  </si>
+  <si>
+    <t>Rescuing Leftover Cuisine</t>
+  </si>
+  <si>
+    <t>Community Development, Housing Homelessness, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d2a84d7e64a34594994f5d2681bdc1f9-rlc-field-sales-representative-boston-ma-rescuing-leftover-cuisine-boston</t>
+  </si>
+  <si>
+    <t>Seasonal Program Facilitator</t>
+  </si>
+  <si>
+    <t>Latinas On the Verge of Excellence - LOVE, Inc</t>
+  </si>
+  <si>
+    <t>USD 21.00 - 21.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/27885f285f0144cb9eebe6779b638ce3-seasonal-program-facilitator-latinas-on-the-verge-of-excellence-love-inc-new-york</t>
+  </si>
+  <si>
+    <t>Senior Associate, Atlanta Civic Site</t>
+  </si>
+  <si>
+    <t>The Annie E. Casey Foundation</t>
+  </si>
+  <si>
+    <t>Atlanta, Georgia</t>
+  </si>
+  <si>
+    <t>USD 120000.00 - 130000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Economic Development, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/916deb4510494661b72c0cc848bd7688-senior-associate-atlanta-civic-site-the-annie-e-casey-foundation-atlanta</t>
+  </si>
+  <si>
     <t>Senior Attorney-Matrimonial Unit</t>
   </si>
   <si>
@@ -1672,6 +2221,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/e489c85929e6417d988b1be09ecb1f75-senior-attorney-matrimonial-unit-district-council-37-health-security-plan-new-york</t>
   </si>
   <si>
+    <t>Senior Civil Rights Attorney (Health and Immigration)</t>
+  </si>
+  <si>
+    <t>New York Lawyers for the Public Interest</t>
+  </si>
+  <si>
+    <t>New York, NY</t>
+  </si>
+  <si>
+    <t>USD 115000.00 - 130000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Health Medicine, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/472fb8e429c04bedbde48823b43d63eb-senior-civil-rights-attorney-health-and-immigration-new-york-lawyers-for-the-public-interest-new-york</t>
+  </si>
+  <si>
     <t>Senior Fellow, Finance and Insurance</t>
   </si>
   <si>
@@ -1699,6 +2266,36 @@
     <t>https://www.idealist.org/en/business-job/4860ea8c05944c4391d28ff9f156d6cc-senior-managerdirector-communications-omidyar-network-san-francisco</t>
   </si>
   <si>
+    <t>Senior Program Officer, Virtual Course Development, Stevens Digital Leaders</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5378b1f858e94a07bfa1bd4c10be3dad-senior-program-officer-virtual-course-development-stevens-digital-leaders-american-councils-for-international-education-actraccels-washington</t>
+  </si>
+  <si>
+    <t>Senior Research Associate</t>
+  </si>
+  <si>
+    <t>Equity Research Cooperative</t>
+  </si>
+  <si>
+    <t>USD 95000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cad8f74248f04227bc81601fb63ab9cd-senior-research-associate-equity-research-cooperative-philadelphia</t>
+  </si>
+  <si>
+    <t>Senior Strategy Officer, US Program (three openings)</t>
+  </si>
+  <si>
+    <t>Gates Foundation</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/d5a26f420be64ba189d5dda3ddf42913-senior-strategy-officer-us-program-three-openings-gates-foundation-seattle</t>
+  </si>
+  <si>
     <t>Site Safety Training (SST) Associate</t>
   </si>
   <si>
@@ -1762,9 +2359,6 @@
     <t>East Side House Settlement</t>
   </si>
   <si>
-    <t>Bronx County, New York</t>
-  </si>
-  <si>
     <t>Children Youth, Education, Science Technology</t>
   </si>
   <si>
@@ -1804,6 +2398,21 @@
     <t>https://www.idealist.org/en/government-job/4c6c7867eb6b4d1b8ba571031a3fafcd-tallerista-para-centro-barrial-de-infancia-villa-martelli-centros-barriales-municipalidad-de-vicente-lopez-villa-martelli</t>
   </si>
   <si>
+    <t>Teach English Abroad with the English Language Fellow Program</t>
+  </si>
+  <si>
+    <t>U.S. Department of State English Language Programs</t>
+  </si>
+  <si>
+    <t>USD 40000.00 - 40000.00/year</t>
+  </si>
+  <si>
+    <t>Education, International Relations</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/28354b2d7c994650a8678afe54b01b20-teach-english-abroad-with-the-english-language-fellow-program-us-department-of-state-english-language-programs-washington</t>
+  </si>
+  <si>
     <t>Teacher's Toolkit Curriculum Development Manager</t>
   </si>
   <si>
@@ -1834,6 +2443,27 @@
     <t>https://www.idealist.org/en/nonprofit-job/d8735093a97649358e5f44868e4634f0-temporary-bilingual-administrative-assistant-immigration-center-for-women-and-children-san-francisco</t>
   </si>
   <si>
+    <t>Trainer - Arts + Puerto Rico Programs</t>
+  </si>
+  <si>
+    <t>The Posse Foundation, Inc. - Arts+ Puerto Rico</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/634fdf66f34b47f6a33ef20361ea05cf-trainer-arts-puerto-rico-programs-the-posse-foundation-inc-arts-puerto-rico-new-york</t>
+  </si>
+  <si>
+    <t>Training &amp; Resources Coordinator</t>
+  </si>
+  <si>
+    <t>USD 51000.00 - 56000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8f72f8b05b5a4494b4cf451fb81c8c8e-training-resources-coordinator-kesem-national-covina</t>
+  </si>
+  <si>
     <t>Transport Dispatchers</t>
   </si>
   <si>
@@ -1861,6 +2491,33 @@
     <t>https://www.idealist.org/en/nonprofit-job/a681aba7b6f44512ad3fa2bc6d94498d-transportation-dispatcher-guru-shardha-welfare-charity-calgary</t>
   </si>
   <si>
+    <t>Vice President, Membership and Policy</t>
+  </si>
+  <si>
+    <t>American Public Human Services Association</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e11c400438294891a516c457cd4ca653-vice-president-membership-and-policy-american-public-human-services-association-arlington</t>
+  </si>
+  <si>
+    <t>Voter Engagement Canvasser - West Michigan</t>
+  </si>
+  <si>
+    <t>Civic Empowerment Coalition</t>
+  </si>
+  <si>
+    <t>Remote (Michigan)</t>
+  </si>
+  <si>
+    <t>USD 18.00 - 20.00/hour</t>
+  </si>
+  <si>
+    <t>Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/81d8fdd0263f4eaead6a61cb10d9b67a-voter-engagement-canvasser-west-michigan-civic-empowerment-coalition-los-angeles</t>
+  </si>
+  <si>
     <t>Washington Transportation Policy Manager</t>
   </si>
   <si>
@@ -1874,6 +2531,21 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/ad9574cb212d48699910b63128d8bdf4-washington-transportation-policy-manager-climate-solutions-seattle</t>
+  </si>
+  <si>
+    <t>Youth Employment Specialist</t>
+  </si>
+  <si>
+    <t>Bridges From School to Work Inc.</t>
+  </si>
+  <si>
+    <t>USD 70304.00 - 70304.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Disability, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a0927eb928874a6fbcfc32538d2b23e0-youth-employment-specialist-bridges-from-school-to-work-inc-los-angeles</t>
   </si>
   <si>
     <t>Zona: Mar del Plata - Lider de Equipo de Captadores/as de Fondos (F2F)</t>
@@ -3131,7 +3803,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -3193,10 +3865,34 @@
         <v>194</v>
       </c>
     </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>195</v>
+      </c>
+      <c r="B3" t="s">
+        <v>196</v>
+      </c>
+      <c r="C3" t="s">
+        <v>197</v>
+      </c>
+      <c r="D3" t="s">
+        <v>198</v>
+      </c>
+      <c r="E3" t="s">
+        <v>199</v>
+      </c>
+      <c r="F3" t="s">
+        <v>200</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -3205,7 +3901,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H98"/>
+  <dimension ref="A1:H146"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -3246,2233 +3942,3337 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="B2" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="C2" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="D2" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="E2" t="s">
         <v>192</v>
       </c>
       <c r="F2" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="B3" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="C3" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="D3" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="E3" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="F3" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="B4" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="C4" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="D4" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="E4" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="F4" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="B5" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="C5" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="D5" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="E5" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="F5" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="B6" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="C6" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="D6" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="E6" t="s">
-        <v>192</v>
+        <v>230</v>
       </c>
       <c r="F6" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="B7" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="C7" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="D7" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="E7" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="F7" t="s">
-        <v>192</v>
+        <v>237</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="B8" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="C8" t="s">
-        <v>127</v>
+        <v>241</v>
       </c>
       <c r="D8" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="E8" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="F8" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="B9" t="s">
-        <v>209</v>
+        <v>245</v>
       </c>
       <c r="C9" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="D9" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="E9" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="F9" t="s">
-        <v>212</v>
+        <v>192</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="B10" t="s">
-        <v>209</v>
+        <v>250</v>
       </c>
       <c r="C10" t="s">
-        <v>210</v>
+        <v>127</v>
       </c>
       <c r="D10" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="E10" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="F10" t="s">
-        <v>212</v>
+        <v>252</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="B11" t="s">
-        <v>209</v>
+        <v>222</v>
       </c>
       <c r="C11" t="s">
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="D11" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="E11" t="s">
-        <v>243</v>
+        <v>256</v>
       </c>
       <c r="F11" t="s">
-        <v>244</v>
+        <v>225</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="B12" t="s">
-        <v>209</v>
+        <v>222</v>
       </c>
       <c r="C12" t="s">
-        <v>210</v>
+        <v>223</v>
       </c>
       <c r="D12" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="E12" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="F12" t="s">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>248</v>
+        <v>259</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="B13" t="s">
-        <v>209</v>
+        <v>222</v>
       </c>
       <c r="C13" t="s">
-        <v>210</v>
+        <v>261</v>
       </c>
       <c r="D13" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="E13" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="F13" t="s">
-        <v>192</v>
+        <v>263</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>251</v>
+        <v>264</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>252</v>
+        <v>265</v>
       </c>
       <c r="B14" t="s">
-        <v>209</v>
+        <v>222</v>
       </c>
       <c r="C14" t="s">
-        <v>210</v>
+        <v>223</v>
       </c>
       <c r="D14" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="E14" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="F14" t="s">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>255</v>
+        <v>268</v>
       </c>
       <c r="B15" t="s">
-        <v>256</v>
+        <v>222</v>
       </c>
       <c r="C15" t="s">
-        <v>257</v>
+        <v>223</v>
       </c>
       <c r="D15" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="E15" t="s">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="F15" t="s">
-        <v>259</v>
+        <v>192</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="B16" t="s">
-        <v>209</v>
+        <v>222</v>
       </c>
       <c r="C16" t="s">
-        <v>210</v>
+        <v>223</v>
       </c>
       <c r="D16" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="E16" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="F16" t="s">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="B17" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="C17" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="D17" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="E17" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="F17" t="s">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="B18" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="C18" t="s">
-        <v>272</v>
+        <v>223</v>
       </c>
       <c r="D18" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="E18" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="F18" t="s">
-        <v>233</v>
+        <v>284</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="B19" t="s">
-        <v>277</v>
+        <v>222</v>
       </c>
       <c r="C19" t="s">
-        <v>278</v>
+        <v>223</v>
       </c>
       <c r="D19" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="E19" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="F19" t="s">
-        <v>280</v>
+        <v>225</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="B20" t="s">
-        <v>209</v>
+        <v>290</v>
       </c>
       <c r="C20" t="s">
-        <v>210</v>
+        <v>291</v>
       </c>
       <c r="D20" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="E20" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="F20" t="s">
-        <v>212</v>
+        <v>293</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>285</v>
+        <v>29</v>
       </c>
       <c r="B21" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="C21" t="s">
-        <v>287</v>
+        <v>197</v>
       </c>
       <c r="D21" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="E21" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="F21" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>35</v>
+        <v>299</v>
       </c>
       <c r="B22" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="C22" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="D22" t="s">
-        <v>204</v>
+        <v>302</v>
       </c>
       <c r="E22" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="F22" t="s">
-        <v>294</v>
+        <v>252</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>295</v>
+        <v>304</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="B23" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="C23" t="s">
-        <v>298</v>
+        <v>197</v>
       </c>
       <c r="D23" t="s">
-        <v>273</v>
+        <v>211</v>
       </c>
       <c r="E23" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="F23" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="B24" t="s">
-        <v>303</v>
+        <v>222</v>
       </c>
       <c r="C24" t="s">
-        <v>304</v>
+        <v>223</v>
       </c>
       <c r="D24" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="E24" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="F24" t="s">
-        <v>306</v>
+        <v>225</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="B25" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="C25" t="s">
-        <v>278</v>
+        <v>315</v>
       </c>
       <c r="D25" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="E25" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="F25" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>313</v>
+        <v>35</v>
       </c>
       <c r="B26" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="C26" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="D26" t="s">
-        <v>273</v>
+        <v>211</v>
       </c>
       <c r="E26" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="F26" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="B27" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="C27" t="s">
-        <v>321</v>
+        <v>197</v>
       </c>
       <c r="D27" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="E27" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="F27" t="s">
-        <v>212</v>
+        <v>327</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="B28" t="s">
-        <v>303</v>
+        <v>330</v>
       </c>
       <c r="C28" t="s">
-        <v>304</v>
+        <v>276</v>
       </c>
       <c r="D28" t="s">
-        <v>204</v>
+        <v>331</v>
       </c>
       <c r="E28" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="F28" t="s">
-        <v>306</v>
+        <v>192</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="B29" t="s">
-        <v>303</v>
+        <v>335</v>
       </c>
       <c r="C29" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="D29" t="s">
-        <v>204</v>
+        <v>302</v>
       </c>
       <c r="E29" t="s">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="F29" t="s">
-        <v>306</v>
+        <v>338</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>329</v>
+        <v>339</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="B30" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="C30" t="s">
-        <v>278</v>
+        <v>342</v>
       </c>
       <c r="D30" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="E30" t="s">
-        <v>332</v>
+        <v>343</v>
       </c>
       <c r="F30" t="s">
-        <v>333</v>
+        <v>344</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>334</v>
+        <v>345</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>330</v>
+        <v>346</v>
       </c>
       <c r="B31" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="C31" t="s">
-        <v>257</v>
+        <v>348</v>
       </c>
       <c r="D31" t="s">
-        <v>273</v>
+        <v>205</v>
       </c>
       <c r="E31" t="s">
-        <v>336</v>
+        <v>349</v>
       </c>
       <c r="F31" t="s">
-        <v>192</v>
+        <v>350</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>337</v>
+        <v>351</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>338</v>
+        <v>352</v>
       </c>
       <c r="B32" t="s">
-        <v>339</v>
+        <v>353</v>
       </c>
       <c r="C32" t="s">
-        <v>340</v>
+        <v>197</v>
       </c>
       <c r="D32" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E32" t="s">
-        <v>341</v>
+        <v>354</v>
       </c>
       <c r="F32" t="s">
-        <v>342</v>
+        <v>355</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>343</v>
+        <v>356</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>344</v>
+        <v>357</v>
       </c>
       <c r="B33" t="s">
-        <v>345</v>
+        <v>358</v>
       </c>
       <c r="C33" t="s">
-        <v>278</v>
+        <v>197</v>
       </c>
       <c r="D33" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="E33" t="s">
-        <v>346</v>
+        <v>359</v>
       </c>
       <c r="F33" t="s">
-        <v>347</v>
+        <v>360</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>348</v>
+        <v>361</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>349</v>
+        <v>362</v>
       </c>
       <c r="B34" t="s">
-        <v>350</v>
+        <v>363</v>
       </c>
       <c r="C34" t="s">
-        <v>278</v>
+        <v>364</v>
       </c>
       <c r="D34" t="s">
-        <v>204</v>
+        <v>302</v>
       </c>
       <c r="E34" t="s">
-        <v>351</v>
+        <v>365</v>
       </c>
       <c r="F34" t="s">
-        <v>300</v>
+        <v>366</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>352</v>
+        <v>367</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>353</v>
+        <v>368</v>
       </c>
       <c r="B35" t="s">
-        <v>354</v>
+        <v>369</v>
       </c>
       <c r="C35" t="s">
-        <v>355</v>
+        <v>370</v>
       </c>
       <c r="D35" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="E35" t="s">
-        <v>192</v>
+        <v>371</v>
       </c>
       <c r="F35" t="s">
-        <v>356</v>
+        <v>225</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>357</v>
+        <v>372</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>358</v>
+        <v>373</v>
       </c>
       <c r="B36" t="s">
-        <v>359</v>
+        <v>341</v>
       </c>
       <c r="C36" t="s">
-        <v>360</v>
+        <v>342</v>
       </c>
       <c r="D36" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="E36" t="s">
-        <v>361</v>
+        <v>374</v>
       </c>
       <c r="F36" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>363</v>
+        <v>375</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>364</v>
+        <v>376</v>
       </c>
       <c r="B37" t="s">
-        <v>365</v>
+        <v>341</v>
       </c>
       <c r="C37" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="D37" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="E37" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="F37" t="s">
-        <v>368</v>
+        <v>344</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>369</v>
+        <v>378</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="B38" t="s">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="C38" t="s">
-        <v>340</v>
+        <v>381</v>
       </c>
       <c r="D38" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="E38" t="s">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="F38" t="s">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>374</v>
+        <v>384</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>375</v>
+        <v>385</v>
       </c>
       <c r="B39" t="s">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="C39" t="s">
-        <v>377</v>
+        <v>197</v>
       </c>
       <c r="D39" t="s">
-        <v>378</v>
+        <v>211</v>
       </c>
       <c r="E39" t="s">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="F39" t="s">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>381</v>
+        <v>389</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="B40" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="C40" t="s">
-        <v>384</v>
+        <v>276</v>
       </c>
       <c r="D40" t="s">
-        <v>204</v>
+        <v>302</v>
       </c>
       <c r="E40" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="F40" t="s">
         <v>192</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="B41" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="C41" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="D41" t="s">
-        <v>204</v>
+        <v>331</v>
       </c>
       <c r="E41" t="s">
-        <v>192</v>
+        <v>396</v>
       </c>
       <c r="F41" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="B42" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="C42" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="D42" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="E42" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="F42" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="B43" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="C43" t="s">
-        <v>399</v>
+        <v>197</v>
       </c>
       <c r="D43" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="E43" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="F43" t="s">
-        <v>192</v>
+        <v>406</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="B44" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="C44" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="D44" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="E44" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="F44" t="s">
-        <v>289</v>
+        <v>412</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>406</v>
+        <v>413</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="B45" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="C45" t="s">
-        <v>409</v>
+        <v>197</v>
       </c>
       <c r="D45" t="s">
-        <v>273</v>
+        <v>211</v>
       </c>
       <c r="E45" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F45" t="s">
-        <v>411</v>
+        <v>338</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="B46" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="C46" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="D46" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="E46" t="s">
-        <v>416</v>
+        <v>192</v>
       </c>
       <c r="F46" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="B47" t="s">
-        <v>209</v>
+        <v>424</v>
       </c>
       <c r="C47" t="s">
-        <v>210</v>
+        <v>425</v>
       </c>
       <c r="D47" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="E47" t="s">
-        <v>420</v>
+        <v>192</v>
       </c>
       <c r="F47" t="s">
-        <v>212</v>
+        <v>192</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="B48" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="C48" t="s">
-        <v>257</v>
+        <v>197</v>
       </c>
       <c r="D48" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="E48" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="F48" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="B49" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="C49" t="s">
-        <v>298</v>
+        <v>434</v>
       </c>
       <c r="D49" t="s">
-        <v>378</v>
+        <v>211</v>
       </c>
       <c r="E49" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="F49" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="B50" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="C50" t="s">
-        <v>278</v>
+        <v>440</v>
       </c>
       <c r="D50" t="s">
-        <v>273</v>
+        <v>211</v>
       </c>
       <c r="E50" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="F50" t="s">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>436</v>
+        <v>443</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="B51" t="s">
-        <v>209</v>
+        <v>445</v>
       </c>
       <c r="C51" t="s">
-        <v>210</v>
+        <v>235</v>
       </c>
       <c r="D51" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="E51" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="F51" t="s">
-        <v>212</v>
+        <v>447</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>439</v>
+        <v>448</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>440</v>
+        <v>449</v>
       </c>
       <c r="B52" t="s">
-        <v>303</v>
+        <v>450</v>
       </c>
       <c r="C52" t="s">
-        <v>441</v>
+        <v>235</v>
       </c>
       <c r="D52" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="E52" t="s">
-        <v>442</v>
+        <v>451</v>
       </c>
       <c r="F52" t="s">
-        <v>306</v>
+        <v>284</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>443</v>
+        <v>452</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>444</v>
+        <v>453</v>
       </c>
       <c r="B53" t="s">
-        <v>445</v>
+        <v>454</v>
       </c>
       <c r="C53" t="s">
-        <v>210</v>
+        <v>455</v>
       </c>
       <c r="D53" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="E53" t="s">
-        <v>446</v>
+        <v>456</v>
       </c>
       <c r="F53" t="s">
-        <v>447</v>
+        <v>457</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>448</v>
+        <v>458</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="B54" t="s">
-        <v>450</v>
+        <v>459</v>
       </c>
       <c r="C54" t="s">
-        <v>257</v>
+        <v>460</v>
       </c>
       <c r="D54" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="E54" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="F54" t="s">
-        <v>452</v>
+        <v>461</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>453</v>
+        <v>462</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B55" t="s">
-        <v>309</v>
+        <v>463</v>
       </c>
       <c r="C55" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D55" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="E55" t="s">
-        <v>455</v>
+        <v>464</v>
       </c>
       <c r="F55" t="s">
-        <v>311</v>
+        <v>465</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>456</v>
+        <v>466</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="B56" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
       <c r="C56" t="s">
-        <v>257</v>
+        <v>223</v>
       </c>
       <c r="D56" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="E56" t="s">
-        <v>459</v>
+        <v>468</v>
       </c>
       <c r="F56" t="s">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>461</v>
+        <v>470</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>462</v>
+        <v>471</v>
       </c>
       <c r="B57" t="s">
-        <v>463</v>
+        <v>472</v>
       </c>
       <c r="C57" t="s">
-        <v>464</v>
+        <v>315</v>
       </c>
       <c r="D57" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="E57" t="s">
-        <v>310</v>
+        <v>473</v>
       </c>
       <c r="F57" t="s">
-        <v>465</v>
+        <v>474</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>466</v>
+        <v>475</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>467</v>
+        <v>476</v>
       </c>
       <c r="B58" t="s">
-        <v>468</v>
+        <v>477</v>
       </c>
       <c r="C58" t="s">
-        <v>278</v>
+        <v>478</v>
       </c>
       <c r="D58" t="s">
-        <v>204</v>
+        <v>331</v>
       </c>
       <c r="E58" t="s">
-        <v>469</v>
+        <v>479</v>
       </c>
       <c r="F58" t="s">
-        <v>192</v>
+        <v>480</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>470</v>
+        <v>481</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>471</v>
+        <v>482</v>
       </c>
       <c r="B59" t="s">
-        <v>472</v>
+        <v>483</v>
       </c>
       <c r="C59" t="s">
-        <v>473</v>
+        <v>484</v>
       </c>
       <c r="D59" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="E59" t="s">
-        <v>474</v>
+        <v>485</v>
       </c>
       <c r="F59" t="s">
-        <v>475</v>
+        <v>192</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>476</v>
+        <v>486</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>477</v>
+        <v>487</v>
       </c>
       <c r="B60" t="s">
-        <v>478</v>
+        <v>488</v>
       </c>
       <c r="C60" t="s">
-        <v>257</v>
+        <v>489</v>
       </c>
       <c r="D60" t="s">
-        <v>273</v>
+        <v>211</v>
       </c>
       <c r="E60" t="s">
-        <v>479</v>
+        <v>192</v>
       </c>
       <c r="F60" t="s">
-        <v>289</v>
+        <v>490</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>480</v>
+        <v>491</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>481</v>
+        <v>492</v>
       </c>
       <c r="B61" t="s">
-        <v>482</v>
+        <v>493</v>
       </c>
       <c r="C61" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="D61" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="E61" t="s">
-        <v>455</v>
+        <v>494</v>
       </c>
       <c r="F61" t="s">
-        <v>192</v>
+        <v>495</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>483</v>
+        <v>496</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>484</v>
+        <v>497</v>
       </c>
       <c r="B62" t="s">
-        <v>209</v>
+        <v>498</v>
       </c>
       <c r="C62" t="s">
-        <v>242</v>
+        <v>499</v>
       </c>
       <c r="D62" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="E62" t="s">
-        <v>262</v>
+        <v>500</v>
       </c>
       <c r="F62" t="s">
-        <v>212</v>
+        <v>192</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>485</v>
+        <v>501</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>486</v>
+        <v>502</v>
       </c>
       <c r="B63" t="s">
-        <v>209</v>
+        <v>503</v>
       </c>
       <c r="C63" t="s">
-        <v>210</v>
+        <v>504</v>
       </c>
       <c r="D63" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="E63" t="s">
-        <v>487</v>
+        <v>473</v>
       </c>
       <c r="F63" t="s">
-        <v>212</v>
+        <v>317</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>488</v>
+        <v>505</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>489</v>
+        <v>506</v>
       </c>
       <c r="B64" t="s">
-        <v>490</v>
+        <v>507</v>
       </c>
       <c r="C64" t="s">
-        <v>340</v>
+        <v>508</v>
       </c>
       <c r="D64" t="s">
-        <v>204</v>
+        <v>302</v>
       </c>
       <c r="E64" t="s">
-        <v>491</v>
+        <v>509</v>
       </c>
       <c r="F64" t="s">
-        <v>492</v>
+        <v>510</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>493</v>
+        <v>511</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>494</v>
+        <v>512</v>
       </c>
       <c r="B65" t="s">
-        <v>495</v>
+        <v>513</v>
       </c>
       <c r="C65" t="s">
-        <v>257</v>
+        <v>514</v>
       </c>
       <c r="D65" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="E65" t="s">
-        <v>496</v>
+        <v>515</v>
       </c>
       <c r="F65" t="s">
-        <v>497</v>
+        <v>516</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>498</v>
+        <v>517</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>499</v>
+        <v>518</v>
       </c>
       <c r="B66" t="s">
-        <v>500</v>
+        <v>222</v>
       </c>
       <c r="C66" t="s">
-        <v>501</v>
+        <v>223</v>
       </c>
       <c r="D66" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="E66" t="s">
-        <v>502</v>
+        <v>519</v>
       </c>
       <c r="F66" t="s">
-        <v>503</v>
+        <v>225</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>504</v>
+        <v>520</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>505</v>
+        <v>521</v>
       </c>
       <c r="B67" t="s">
-        <v>506</v>
+        <v>522</v>
       </c>
       <c r="C67" t="s">
-        <v>321</v>
+        <v>276</v>
       </c>
       <c r="D67" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="E67" t="s">
-        <v>507</v>
+        <v>523</v>
       </c>
       <c r="F67" t="s">
-        <v>508</v>
+        <v>524</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>509</v>
+        <v>525</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>510</v>
+        <v>526</v>
       </c>
       <c r="B68" t="s">
-        <v>511</v>
+        <v>527</v>
       </c>
       <c r="C68" t="s">
-        <v>512</v>
+        <v>336</v>
       </c>
       <c r="D68" t="s">
-        <v>204</v>
+        <v>331</v>
       </c>
       <c r="E68" t="s">
-        <v>502</v>
+        <v>528</v>
       </c>
       <c r="F68" t="s">
-        <v>513</v>
+        <v>529</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>514</v>
+        <v>530</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>515</v>
+        <v>531</v>
       </c>
       <c r="B69" t="s">
-        <v>516</v>
+        <v>532</v>
       </c>
       <c r="C69" t="s">
-        <v>340</v>
+        <v>197</v>
       </c>
       <c r="D69" t="s">
-        <v>204</v>
+        <v>302</v>
       </c>
       <c r="E69" t="s">
-        <v>341</v>
+        <v>533</v>
       </c>
       <c r="F69" t="s">
-        <v>517</v>
+        <v>534</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>518</v>
+        <v>535</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>519</v>
+        <v>536</v>
       </c>
       <c r="B70" t="s">
-        <v>331</v>
+        <v>537</v>
       </c>
       <c r="C70" t="s">
-        <v>278</v>
+        <v>538</v>
       </c>
       <c r="D70" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E70" t="s">
-        <v>332</v>
+        <v>539</v>
       </c>
       <c r="F70" t="s">
-        <v>333</v>
+        <v>540</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>520</v>
+        <v>541</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>521</v>
+        <v>542</v>
       </c>
       <c r="B71" t="s">
-        <v>522</v>
+        <v>543</v>
       </c>
       <c r="C71" t="s">
-        <v>257</v>
+        <v>544</v>
       </c>
       <c r="D71" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="E71" t="s">
-        <v>341</v>
+        <v>545</v>
       </c>
       <c r="F71" t="s">
-        <v>523</v>
+        <v>546</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>524</v>
+        <v>547</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>525</v>
+        <v>548</v>
       </c>
       <c r="B72" t="s">
-        <v>209</v>
+        <v>222</v>
       </c>
       <c r="C72" t="s">
-        <v>526</v>
+        <v>223</v>
       </c>
       <c r="D72" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="E72" t="s">
-        <v>527</v>
+        <v>549</v>
       </c>
       <c r="F72" t="s">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>528</v>
+        <v>550</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>529</v>
+        <v>551</v>
       </c>
       <c r="B73" t="s">
-        <v>530</v>
+        <v>341</v>
       </c>
       <c r="C73" t="s">
-        <v>531</v>
+        <v>552</v>
       </c>
       <c r="D73" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="E73" t="s">
-        <v>532</v>
+        <v>553</v>
       </c>
       <c r="F73" t="s">
-        <v>533</v>
+        <v>344</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>534</v>
+        <v>554</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>535</v>
+        <v>555</v>
       </c>
       <c r="B74" t="s">
-        <v>536</v>
+        <v>556</v>
       </c>
       <c r="C74" t="s">
-        <v>501</v>
+        <v>557</v>
       </c>
       <c r="D74" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="E74" t="s">
-        <v>455</v>
+        <v>558</v>
       </c>
       <c r="F74" t="s">
-        <v>537</v>
+        <v>559</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>538</v>
+        <v>560</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>539</v>
+        <v>561</v>
       </c>
       <c r="B75" t="s">
-        <v>540</v>
+        <v>562</v>
       </c>
       <c r="C75" t="s">
-        <v>541</v>
+        <v>197</v>
       </c>
       <c r="D75" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="E75" t="s">
-        <v>192</v>
+        <v>563</v>
       </c>
       <c r="F75" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>542</v>
+        <v>564</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>543</v>
+        <v>565</v>
       </c>
       <c r="B76" t="s">
-        <v>544</v>
+        <v>566</v>
       </c>
       <c r="C76" t="s">
-        <v>257</v>
+        <v>276</v>
       </c>
       <c r="D76" t="s">
-        <v>204</v>
+        <v>302</v>
       </c>
       <c r="E76" t="s">
-        <v>424</v>
+        <v>567</v>
       </c>
       <c r="F76" t="s">
-        <v>545</v>
+        <v>568</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>546</v>
+        <v>569</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>547</v>
+        <v>570</v>
       </c>
       <c r="B77" t="s">
-        <v>548</v>
+        <v>571</v>
       </c>
       <c r="C77" t="s">
-        <v>257</v>
+        <v>223</v>
       </c>
       <c r="D77" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="E77" t="s">
-        <v>549</v>
+        <v>572</v>
       </c>
       <c r="F77" t="s">
-        <v>550</v>
+        <v>540</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>551</v>
+        <v>573</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>552</v>
+        <v>574</v>
       </c>
       <c r="B78" t="s">
-        <v>553</v>
+        <v>575</v>
       </c>
       <c r="C78" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D78" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="E78" t="s">
-        <v>554</v>
+        <v>576</v>
       </c>
       <c r="F78" t="s">
-        <v>492</v>
+        <v>577</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>555</v>
+        <v>578</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>556</v>
+        <v>579</v>
       </c>
       <c r="B79" t="s">
-        <v>557</v>
+        <v>358</v>
       </c>
       <c r="C79" t="s">
-        <v>501</v>
+        <v>197</v>
       </c>
       <c r="D79" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="E79" t="s">
-        <v>558</v>
+        <v>580</v>
       </c>
       <c r="F79" t="s">
-        <v>559</v>
+        <v>360</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>560</v>
+        <v>581</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>561</v>
+        <v>582</v>
       </c>
       <c r="B80" t="s">
-        <v>271</v>
+        <v>583</v>
       </c>
       <c r="C80" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="D80" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="E80" t="s">
-        <v>562</v>
+        <v>584</v>
       </c>
       <c r="F80" t="s">
-        <v>233</v>
+        <v>585</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>563</v>
+        <v>586</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>564</v>
+        <v>587</v>
       </c>
       <c r="B81" t="s">
-        <v>428</v>
+        <v>234</v>
       </c>
       <c r="C81" t="s">
-        <v>298</v>
+        <v>235</v>
       </c>
       <c r="D81" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="E81" t="s">
-        <v>565</v>
+        <v>236</v>
       </c>
       <c r="F81" t="s">
-        <v>566</v>
+        <v>237</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>567</v>
+        <v>588</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>568</v>
+        <v>589</v>
       </c>
       <c r="B82" t="s">
-        <v>569</v>
+        <v>590</v>
       </c>
       <c r="C82" t="s">
-        <v>278</v>
+        <v>591</v>
       </c>
       <c r="D82" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="E82" t="s">
-        <v>570</v>
+        <v>359</v>
       </c>
       <c r="F82" t="s">
-        <v>571</v>
+        <v>592</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>572</v>
+        <v>593</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>573</v>
+        <v>594</v>
       </c>
       <c r="B83" t="s">
-        <v>574</v>
+        <v>595</v>
       </c>
       <c r="C83" t="s">
-        <v>575</v>
+        <v>596</v>
       </c>
       <c r="D83" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="E83" t="s">
-        <v>576</v>
+        <v>597</v>
       </c>
       <c r="F83" t="s">
-        <v>192</v>
+        <v>225</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>577</v>
+        <v>598</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>578</v>
+        <v>599</v>
       </c>
       <c r="B84" t="s">
-        <v>209</v>
+        <v>600</v>
       </c>
       <c r="C84" t="s">
-        <v>210</v>
+        <v>601</v>
       </c>
       <c r="D84" t="s">
-        <v>204</v>
+        <v>331</v>
       </c>
       <c r="E84" t="s">
-        <v>420</v>
+        <v>602</v>
       </c>
       <c r="F84" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>579</v>
+        <v>603</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>580</v>
+        <v>604</v>
       </c>
       <c r="B85" t="s">
-        <v>581</v>
+        <v>605</v>
       </c>
       <c r="C85" t="s">
-        <v>582</v>
+        <v>197</v>
       </c>
       <c r="D85" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E85" t="s">
-        <v>274</v>
+        <v>606</v>
       </c>
       <c r="F85" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>584</v>
+        <v>608</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>585</v>
+        <v>609</v>
       </c>
       <c r="B86" t="s">
-        <v>586</v>
+        <v>610</v>
       </c>
       <c r="C86" t="s">
-        <v>587</v>
+        <v>197</v>
       </c>
       <c r="D86" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="E86" t="s">
-        <v>588</v>
+        <v>611</v>
       </c>
       <c r="F86" t="s">
-        <v>589</v>
+        <v>192</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>590</v>
+        <v>612</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>591</v>
+        <v>613</v>
       </c>
       <c r="B87" t="s">
-        <v>221</v>
+        <v>614</v>
       </c>
       <c r="C87" t="s">
-        <v>592</v>
+        <v>615</v>
       </c>
       <c r="D87" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="E87" t="s">
-        <v>192</v>
+        <v>616</v>
       </c>
       <c r="F87" t="s">
-        <v>223</v>
+        <v>617</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>593</v>
+        <v>618</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>594</v>
+        <v>619</v>
       </c>
       <c r="B88" t="s">
-        <v>221</v>
+        <v>620</v>
       </c>
       <c r="C88" t="s">
-        <v>592</v>
+        <v>276</v>
       </c>
       <c r="D88" t="s">
-        <v>204</v>
+        <v>302</v>
       </c>
       <c r="E88" t="s">
-        <v>192</v>
+        <v>621</v>
       </c>
       <c r="F88" t="s">
-        <v>223</v>
+        <v>317</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>595</v>
+        <v>622</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>596</v>
+        <v>623</v>
       </c>
       <c r="B89" t="s">
-        <v>597</v>
+        <v>624</v>
       </c>
       <c r="C89" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D89" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="E89" t="s">
-        <v>598</v>
+        <v>580</v>
       </c>
       <c r="F89" t="s">
-        <v>599</v>
+        <v>192</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>600</v>
+        <v>625</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>601</v>
+        <v>626</v>
       </c>
       <c r="B90" t="s">
-        <v>602</v>
+        <v>627</v>
       </c>
       <c r="C90" t="s">
-        <v>501</v>
+        <v>223</v>
       </c>
       <c r="D90" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="E90" t="s">
-        <v>603</v>
+        <v>628</v>
       </c>
       <c r="F90" t="s">
-        <v>604</v>
+        <v>629</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>605</v>
+        <v>630</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>606</v>
+        <v>631</v>
       </c>
       <c r="B91" t="s">
-        <v>303</v>
+        <v>222</v>
       </c>
       <c r="C91" t="s">
-        <v>328</v>
+        <v>261</v>
       </c>
       <c r="D91" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="E91" t="s">
-        <v>607</v>
+        <v>287</v>
       </c>
       <c r="F91" t="s">
-        <v>306</v>
+        <v>225</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>608</v>
+        <v>632</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>609</v>
+        <v>633</v>
       </c>
       <c r="B92" t="s">
-        <v>303</v>
+        <v>634</v>
       </c>
       <c r="C92" t="s">
-        <v>328</v>
+        <v>635</v>
       </c>
       <c r="D92" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="E92" t="s">
-        <v>607</v>
+        <v>636</v>
       </c>
       <c r="F92" t="s">
-        <v>342</v>
+        <v>284</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>610</v>
+        <v>637</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>609</v>
+        <v>638</v>
       </c>
       <c r="B93" t="s">
-        <v>303</v>
+        <v>639</v>
       </c>
       <c r="C93" t="s">
-        <v>304</v>
+        <v>197</v>
       </c>
       <c r="D93" t="s">
-        <v>204</v>
+        <v>331</v>
       </c>
       <c r="E93" t="s">
-        <v>607</v>
+        <v>640</v>
       </c>
       <c r="F93" t="s">
-        <v>342</v>
+        <v>641</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>611</v>
+        <v>642</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>612</v>
+        <v>643</v>
       </c>
       <c r="B94" t="s">
-        <v>303</v>
+        <v>222</v>
       </c>
       <c r="C94" t="s">
-        <v>304</v>
+        <v>223</v>
       </c>
       <c r="D94" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="E94" t="s">
-        <v>607</v>
+        <v>644</v>
       </c>
       <c r="F94" t="s">
-        <v>613</v>
+        <v>225</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>614</v>
+        <v>645</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>615</v>
+        <v>646</v>
       </c>
       <c r="B95" t="s">
-        <v>616</v>
+        <v>647</v>
       </c>
       <c r="C95" t="s">
-        <v>399</v>
+        <v>235</v>
       </c>
       <c r="D95" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="E95" t="s">
-        <v>617</v>
+        <v>648</v>
       </c>
       <c r="F95" t="s">
-        <v>618</v>
+        <v>430</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>619</v>
+        <v>649</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>620</v>
+        <v>650</v>
       </c>
       <c r="B96" t="s">
-        <v>388</v>
+        <v>651</v>
       </c>
       <c r="C96" t="s">
-        <v>621</v>
+        <v>276</v>
       </c>
       <c r="D96" t="s">
-        <v>378</v>
+        <v>211</v>
       </c>
       <c r="E96" t="s">
-        <v>192</v>
+        <v>652</v>
       </c>
       <c r="F96" t="s">
-        <v>622</v>
+        <v>653</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>623</v>
+        <v>654</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>624</v>
+        <v>655</v>
       </c>
       <c r="B97" t="s">
-        <v>388</v>
+        <v>656</v>
       </c>
       <c r="C97" t="s">
-        <v>625</v>
+        <v>210</v>
       </c>
       <c r="D97" t="s">
-        <v>378</v>
+        <v>211</v>
       </c>
       <c r="E97" t="s">
-        <v>192</v>
+        <v>558</v>
       </c>
       <c r="F97" t="s">
-        <v>622</v>
+        <v>657</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>626</v>
+        <v>658</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>627</v>
+        <v>655</v>
       </c>
       <c r="B98" t="s">
+        <v>659</v>
+      </c>
+      <c r="C98" t="s">
+        <v>235</v>
+      </c>
+      <c r="D98" t="s">
+        <v>211</v>
+      </c>
+      <c r="E98" t="s">
+        <v>660</v>
+      </c>
+      <c r="F98" t="s">
+        <v>661</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>125</v>
+      </c>
+      <c r="B99" t="s">
+        <v>663</v>
+      </c>
+      <c r="C99" t="s">
+        <v>197</v>
+      </c>
+      <c r="D99" t="s">
+        <v>211</v>
+      </c>
+      <c r="E99" t="s">
+        <v>664</v>
+      </c>
+      <c r="F99" t="s">
+        <v>665</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>667</v>
+      </c>
+      <c r="B100" t="s">
+        <v>668</v>
+      </c>
+      <c r="C100" t="s">
+        <v>370</v>
+      </c>
+      <c r="D100" t="s">
+        <v>211</v>
+      </c>
+      <c r="E100" t="s">
+        <v>636</v>
+      </c>
+      <c r="F100" t="s">
+        <v>669</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>671</v>
+      </c>
+      <c r="B101" t="s">
+        <v>672</v>
+      </c>
+      <c r="C101" t="s">
+        <v>673</v>
+      </c>
+      <c r="D101" t="s">
+        <v>211</v>
+      </c>
+      <c r="E101" t="s">
+        <v>558</v>
+      </c>
+      <c r="F101" t="s">
+        <v>674</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>676</v>
+      </c>
+      <c r="B102" t="s">
+        <v>677</v>
+      </c>
+      <c r="C102" t="s">
+        <v>235</v>
+      </c>
+      <c r="D102" t="s">
+        <v>211</v>
+      </c>
+      <c r="E102" t="s">
+        <v>400</v>
+      </c>
+      <c r="F102" t="s">
+        <v>678</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>680</v>
+      </c>
+      <c r="B103" t="s">
+        <v>386</v>
+      </c>
+      <c r="C103" t="s">
+        <v>197</v>
+      </c>
+      <c r="D103" t="s">
+        <v>211</v>
+      </c>
+      <c r="E103" t="s">
+        <v>387</v>
+      </c>
+      <c r="F103" t="s">
         <v>388</v>
       </c>
-      <c r="C98" t="s">
-        <v>628</v>
-      </c>
-      <c r="D98" t="s">
-        <v>378</v>
-      </c>
-      <c r="E98" t="s">
+      <c r="H103" s="2" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>682</v>
+      </c>
+      <c r="B104" t="s">
+        <v>683</v>
+      </c>
+      <c r="C104" t="s">
+        <v>276</v>
+      </c>
+      <c r="D104" t="s">
+        <v>211</v>
+      </c>
+      <c r="E104" t="s">
+        <v>400</v>
+      </c>
+      <c r="F104" t="s">
+        <v>684</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>686</v>
+      </c>
+      <c r="B105" t="s">
+        <v>222</v>
+      </c>
+      <c r="C105" t="s">
+        <v>687</v>
+      </c>
+      <c r="D105" t="s">
+        <v>211</v>
+      </c>
+      <c r="E105" t="s">
+        <v>688</v>
+      </c>
+      <c r="F105" t="s">
+        <v>225</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>690</v>
+      </c>
+      <c r="B106" t="s">
+        <v>691</v>
+      </c>
+      <c r="C106" t="s">
+        <v>692</v>
+      </c>
+      <c r="D106" t="s">
+        <v>211</v>
+      </c>
+      <c r="E106" t="s">
+        <v>693</v>
+      </c>
+      <c r="F106" t="s">
+        <v>694</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>696</v>
+      </c>
+      <c r="B107" t="s">
+        <v>697</v>
+      </c>
+      <c r="C107" t="s">
+        <v>210</v>
+      </c>
+      <c r="D107" t="s">
+        <v>211</v>
+      </c>
+      <c r="E107" t="s">
+        <v>580</v>
+      </c>
+      <c r="F107" t="s">
+        <v>698</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>700</v>
+      </c>
+      <c r="B108" t="s">
+        <v>701</v>
+      </c>
+      <c r="C108" t="s">
+        <v>702</v>
+      </c>
+      <c r="D108" t="s">
+        <v>211</v>
+      </c>
+      <c r="E108" t="s">
         <v>192</v>
       </c>
-      <c r="F98" t="s">
-        <v>622</v>
-      </c>
-      <c r="H98" s="2" t="s">
-        <v>629</v>
+      <c r="F108" t="s">
+        <v>192</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>704</v>
+      </c>
+      <c r="B109" t="s">
+        <v>705</v>
+      </c>
+      <c r="C109" t="s">
+        <v>706</v>
+      </c>
+      <c r="D109" t="s">
+        <v>282</v>
+      </c>
+      <c r="E109" t="s">
+        <v>707</v>
+      </c>
+      <c r="F109" t="s">
+        <v>465</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>709</v>
+      </c>
+      <c r="B110" t="s">
+        <v>705</v>
+      </c>
+      <c r="C110" t="s">
+        <v>706</v>
+      </c>
+      <c r="D110" t="s">
+        <v>211</v>
+      </c>
+      <c r="E110" t="s">
+        <v>710</v>
+      </c>
+      <c r="F110" t="s">
+        <v>465</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>712</v>
+      </c>
+      <c r="B111" t="s">
+        <v>713</v>
+      </c>
+      <c r="C111" t="s">
+        <v>276</v>
+      </c>
+      <c r="D111" t="s">
+        <v>211</v>
+      </c>
+      <c r="E111" t="s">
+        <v>523</v>
+      </c>
+      <c r="F111" t="s">
+        <v>714</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>716</v>
+      </c>
+      <c r="B112" t="s">
+        <v>717</v>
+      </c>
+      <c r="C112" t="s">
+        <v>246</v>
+      </c>
+      <c r="D112" t="s">
+        <v>205</v>
+      </c>
+      <c r="E112" t="s">
+        <v>365</v>
+      </c>
+      <c r="F112" t="s">
+        <v>718</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>720</v>
+      </c>
+      <c r="B113" t="s">
+        <v>721</v>
+      </c>
+      <c r="C113" t="s">
+        <v>276</v>
+      </c>
+      <c r="D113" t="s">
+        <v>282</v>
+      </c>
+      <c r="E113" t="s">
+        <v>722</v>
+      </c>
+      <c r="F113" t="s">
+        <v>206</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>724</v>
+      </c>
+      <c r="B114" t="s">
+        <v>725</v>
+      </c>
+      <c r="C114" t="s">
+        <v>726</v>
+      </c>
+      <c r="D114" t="s">
+        <v>211</v>
+      </c>
+      <c r="E114" t="s">
+        <v>727</v>
+      </c>
+      <c r="F114" t="s">
+        <v>728</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>730</v>
+      </c>
+      <c r="B115" t="s">
+        <v>731</v>
+      </c>
+      <c r="C115" t="s">
+        <v>276</v>
+      </c>
+      <c r="D115" t="s">
+        <v>211</v>
+      </c>
+      <c r="E115" t="s">
+        <v>732</v>
+      </c>
+      <c r="F115" t="s">
+        <v>733</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>735</v>
+      </c>
+      <c r="B116" t="s">
+        <v>736</v>
+      </c>
+      <c r="C116" t="s">
+        <v>737</v>
+      </c>
+      <c r="D116" t="s">
+        <v>211</v>
+      </c>
+      <c r="E116" t="s">
+        <v>738</v>
+      </c>
+      <c r="F116" t="s">
+        <v>739</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>741</v>
+      </c>
+      <c r="B117" t="s">
+        <v>742</v>
+      </c>
+      <c r="C117" t="s">
+        <v>197</v>
+      </c>
+      <c r="D117" t="s">
+        <v>211</v>
+      </c>
+      <c r="E117" t="s">
+        <v>743</v>
+      </c>
+      <c r="F117" t="s">
+        <v>430</v>
+      </c>
+      <c r="H117" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>745</v>
+      </c>
+      <c r="B118" t="s">
+        <v>746</v>
+      </c>
+      <c r="C118" t="s">
+        <v>210</v>
+      </c>
+      <c r="D118" t="s">
+        <v>211</v>
+      </c>
+      <c r="E118" t="s">
+        <v>747</v>
+      </c>
+      <c r="F118" t="s">
+        <v>748</v>
+      </c>
+      <c r="H118" s="2" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>750</v>
+      </c>
+      <c r="B119" t="s">
+        <v>677</v>
+      </c>
+      <c r="C119" t="s">
+        <v>235</v>
+      </c>
+      <c r="D119" t="s">
+        <v>211</v>
+      </c>
+      <c r="E119" t="s">
+        <v>523</v>
+      </c>
+      <c r="F119" t="s">
+        <v>678</v>
+      </c>
+      <c r="H119" s="2" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>752</v>
+      </c>
+      <c r="B120" t="s">
+        <v>753</v>
+      </c>
+      <c r="C120" t="s">
+        <v>197</v>
+      </c>
+      <c r="D120" t="s">
+        <v>211</v>
+      </c>
+      <c r="E120" t="s">
+        <v>754</v>
+      </c>
+      <c r="F120" t="s">
+        <v>755</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>757</v>
+      </c>
+      <c r="B121" t="s">
+        <v>758</v>
+      </c>
+      <c r="C121" t="s">
+        <v>499</v>
+      </c>
+      <c r="D121" t="s">
+        <v>211</v>
+      </c>
+      <c r="E121" t="s">
+        <v>192</v>
+      </c>
+      <c r="F121" t="s">
+        <v>192</v>
+      </c>
+      <c r="H121" s="2" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>760</v>
+      </c>
+      <c r="B122" t="s">
+        <v>300</v>
+      </c>
+      <c r="C122" t="s">
+        <v>301</v>
+      </c>
+      <c r="D122" t="s">
+        <v>211</v>
+      </c>
+      <c r="E122" t="s">
+        <v>761</v>
+      </c>
+      <c r="F122" t="s">
+        <v>252</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>763</v>
+      </c>
+      <c r="B123" t="s">
+        <v>527</v>
+      </c>
+      <c r="C123" t="s">
+        <v>336</v>
+      </c>
+      <c r="D123" t="s">
+        <v>211</v>
+      </c>
+      <c r="E123" t="s">
+        <v>764</v>
+      </c>
+      <c r="F123" t="s">
+        <v>765</v>
+      </c>
+      <c r="H123" s="2" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>767</v>
+      </c>
+      <c r="B124" t="s">
+        <v>768</v>
+      </c>
+      <c r="C124" t="s">
+        <v>197</v>
+      </c>
+      <c r="D124" t="s">
+        <v>205</v>
+      </c>
+      <c r="E124" t="s">
+        <v>769</v>
+      </c>
+      <c r="F124" t="s">
+        <v>770</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>772</v>
+      </c>
+      <c r="B125" t="s">
+        <v>773</v>
+      </c>
+      <c r="C125" t="s">
+        <v>774</v>
+      </c>
+      <c r="D125" t="s">
+        <v>211</v>
+      </c>
+      <c r="E125" t="s">
+        <v>775</v>
+      </c>
+      <c r="F125" t="s">
+        <v>192</v>
+      </c>
+      <c r="H125" s="2" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>777</v>
+      </c>
+      <c r="B126" t="s">
+        <v>222</v>
+      </c>
+      <c r="C126" t="s">
+        <v>223</v>
+      </c>
+      <c r="D126" t="s">
+        <v>211</v>
+      </c>
+      <c r="E126" t="s">
+        <v>519</v>
+      </c>
+      <c r="F126" t="s">
+        <v>225</v>
+      </c>
+      <c r="H126" s="2" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>779</v>
+      </c>
+      <c r="B127" t="s">
+        <v>780</v>
+      </c>
+      <c r="C127" t="s">
+        <v>348</v>
+      </c>
+      <c r="D127" t="s">
+        <v>211</v>
+      </c>
+      <c r="E127" t="s">
+        <v>303</v>
+      </c>
+      <c r="F127" t="s">
+        <v>781</v>
+      </c>
+      <c r="H127" s="2" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>783</v>
+      </c>
+      <c r="B128" t="s">
+        <v>784</v>
+      </c>
+      <c r="C128" t="s">
+        <v>785</v>
+      </c>
+      <c r="D128" t="s">
+        <v>211</v>
+      </c>
+      <c r="E128" t="s">
+        <v>786</v>
+      </c>
+      <c r="F128" t="s">
+        <v>787</v>
+      </c>
+      <c r="H128" s="2" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>789</v>
+      </c>
+      <c r="B129" t="s">
+        <v>240</v>
+      </c>
+      <c r="C129" t="s">
+        <v>790</v>
+      </c>
+      <c r="D129" t="s">
+        <v>211</v>
+      </c>
+      <c r="E129" t="s">
+        <v>192</v>
+      </c>
+      <c r="F129" t="s">
+        <v>242</v>
+      </c>
+      <c r="H129" s="2" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>792</v>
+      </c>
+      <c r="B130" t="s">
+        <v>240</v>
+      </c>
+      <c r="C130" t="s">
+        <v>790</v>
+      </c>
+      <c r="D130" t="s">
+        <v>211</v>
+      </c>
+      <c r="E130" t="s">
+        <v>192</v>
+      </c>
+      <c r="F130" t="s">
+        <v>242</v>
+      </c>
+      <c r="H130" s="2" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>794</v>
+      </c>
+      <c r="B131" t="s">
+        <v>795</v>
+      </c>
+      <c r="C131" t="s">
+        <v>235</v>
+      </c>
+      <c r="D131" t="s">
+        <v>205</v>
+      </c>
+      <c r="E131" t="s">
+        <v>796</v>
+      </c>
+      <c r="F131" t="s">
+        <v>797</v>
+      </c>
+      <c r="H131" s="2" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>799</v>
+      </c>
+      <c r="B132" t="s">
+        <v>800</v>
+      </c>
+      <c r="C132" t="s">
+        <v>197</v>
+      </c>
+      <c r="D132" t="s">
+        <v>205</v>
+      </c>
+      <c r="E132" t="s">
+        <v>801</v>
+      </c>
+      <c r="F132" t="s">
+        <v>802</v>
+      </c>
+      <c r="H132" s="2" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>804</v>
+      </c>
+      <c r="B133" t="s">
+        <v>805</v>
+      </c>
+      <c r="C133" t="s">
+        <v>210</v>
+      </c>
+      <c r="D133" t="s">
+        <v>205</v>
+      </c>
+      <c r="E133" t="s">
+        <v>806</v>
+      </c>
+      <c r="F133" t="s">
+        <v>807</v>
+      </c>
+      <c r="H133" s="2" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>809</v>
+      </c>
+      <c r="B134" t="s">
+        <v>810</v>
+      </c>
+      <c r="C134" t="s">
+        <v>276</v>
+      </c>
+      <c r="D134" t="s">
+        <v>211</v>
+      </c>
+      <c r="E134" t="s">
+        <v>811</v>
+      </c>
+      <c r="F134" t="s">
+        <v>317</v>
+      </c>
+      <c r="H134" s="2" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>813</v>
+      </c>
+      <c r="B135" t="s">
+        <v>325</v>
+      </c>
+      <c r="C135" t="s">
+        <v>197</v>
+      </c>
+      <c r="D135" t="s">
+        <v>211</v>
+      </c>
+      <c r="E135" t="s">
+        <v>814</v>
+      </c>
+      <c r="F135" t="s">
+        <v>327</v>
+      </c>
+      <c r="H135" s="2" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>816</v>
+      </c>
+      <c r="B136" t="s">
+        <v>341</v>
+      </c>
+      <c r="C136" t="s">
+        <v>377</v>
+      </c>
+      <c r="D136" t="s">
+        <v>211</v>
+      </c>
+      <c r="E136" t="s">
+        <v>817</v>
+      </c>
+      <c r="F136" t="s">
+        <v>344</v>
+      </c>
+      <c r="H136" s="2" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>819</v>
+      </c>
+      <c r="B137" t="s">
+        <v>341</v>
+      </c>
+      <c r="C137" t="s">
+        <v>377</v>
+      </c>
+      <c r="D137" t="s">
+        <v>211</v>
+      </c>
+      <c r="E137" t="s">
+        <v>817</v>
+      </c>
+      <c r="F137" t="s">
+        <v>401</v>
+      </c>
+      <c r="H137" s="2" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>819</v>
+      </c>
+      <c r="B138" t="s">
+        <v>341</v>
+      </c>
+      <c r="C138" t="s">
+        <v>342</v>
+      </c>
+      <c r="D138" t="s">
+        <v>211</v>
+      </c>
+      <c r="E138" t="s">
+        <v>817</v>
+      </c>
+      <c r="F138" t="s">
+        <v>401</v>
+      </c>
+      <c r="H138" s="2" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>822</v>
+      </c>
+      <c r="B139" t="s">
+        <v>341</v>
+      </c>
+      <c r="C139" t="s">
+        <v>342</v>
+      </c>
+      <c r="D139" t="s">
+        <v>211</v>
+      </c>
+      <c r="E139" t="s">
+        <v>817</v>
+      </c>
+      <c r="F139" t="s">
+        <v>823</v>
+      </c>
+      <c r="H139" s="2" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>825</v>
+      </c>
+      <c r="B140" t="s">
+        <v>826</v>
+      </c>
+      <c r="C140" t="s">
+        <v>197</v>
+      </c>
+      <c r="D140" t="s">
+        <v>211</v>
+      </c>
+      <c r="E140" t="s">
+        <v>192</v>
+      </c>
+      <c r="F140" t="s">
+        <v>192</v>
+      </c>
+      <c r="H140" s="2" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>828</v>
+      </c>
+      <c r="B141" t="s">
+        <v>829</v>
+      </c>
+      <c r="C141" t="s">
+        <v>830</v>
+      </c>
+      <c r="D141" t="s">
+        <v>302</v>
+      </c>
+      <c r="E141" t="s">
+        <v>831</v>
+      </c>
+      <c r="F141" t="s">
+        <v>832</v>
+      </c>
+      <c r="H141" s="2" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>834</v>
+      </c>
+      <c r="B142" t="s">
+        <v>835</v>
+      </c>
+      <c r="C142" t="s">
+        <v>499</v>
+      </c>
+      <c r="D142" t="s">
+        <v>211</v>
+      </c>
+      <c r="E142" t="s">
+        <v>836</v>
+      </c>
+      <c r="F142" t="s">
+        <v>837</v>
+      </c>
+      <c r="H142" s="2" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>839</v>
+      </c>
+      <c r="B143" t="s">
+        <v>840</v>
+      </c>
+      <c r="C143" t="s">
+        <v>223</v>
+      </c>
+      <c r="D143" t="s">
+        <v>211</v>
+      </c>
+      <c r="E143" t="s">
+        <v>841</v>
+      </c>
+      <c r="F143" t="s">
+        <v>842</v>
+      </c>
+      <c r="H143" s="2" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>844</v>
+      </c>
+      <c r="B144" t="s">
+        <v>488</v>
+      </c>
+      <c r="C144" t="s">
+        <v>845</v>
+      </c>
+      <c r="D144" t="s">
+        <v>331</v>
+      </c>
+      <c r="E144" t="s">
+        <v>192</v>
+      </c>
+      <c r="F144" t="s">
+        <v>846</v>
+      </c>
+      <c r="H144" s="2" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>848</v>
+      </c>
+      <c r="B145" t="s">
+        <v>488</v>
+      </c>
+      <c r="C145" t="s">
+        <v>849</v>
+      </c>
+      <c r="D145" t="s">
+        <v>331</v>
+      </c>
+      <c r="E145" t="s">
+        <v>192</v>
+      </c>
+      <c r="F145" t="s">
+        <v>846</v>
+      </c>
+      <c r="H145" s="2" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>851</v>
+      </c>
+      <c r="B146" t="s">
+        <v>488</v>
+      </c>
+      <c r="C146" t="s">
+        <v>852</v>
+      </c>
+      <c r="D146" t="s">
+        <v>331</v>
+      </c>
+      <c r="E146" t="s">
+        <v>192</v>
+      </c>
+      <c r="F146" t="s">
+        <v>846</v>
+      </c>
+      <c r="H146" s="2" t="s">
+        <v>853</v>
       </c>
     </row>
   </sheetData>
@@ -5575,6 +7375,54 @@
     <hyperlink ref="H96" r:id="rId95"/>
     <hyperlink ref="H97" r:id="rId96"/>
     <hyperlink ref="H98" r:id="rId97"/>
+    <hyperlink ref="H99" r:id="rId98"/>
+    <hyperlink ref="H100" r:id="rId99"/>
+    <hyperlink ref="H101" r:id="rId100"/>
+    <hyperlink ref="H102" r:id="rId101"/>
+    <hyperlink ref="H103" r:id="rId102"/>
+    <hyperlink ref="H104" r:id="rId103"/>
+    <hyperlink ref="H105" r:id="rId104"/>
+    <hyperlink ref="H106" r:id="rId105"/>
+    <hyperlink ref="H107" r:id="rId106"/>
+    <hyperlink ref="H108" r:id="rId107"/>
+    <hyperlink ref="H109" r:id="rId108"/>
+    <hyperlink ref="H110" r:id="rId109"/>
+    <hyperlink ref="H111" r:id="rId110"/>
+    <hyperlink ref="H112" r:id="rId111"/>
+    <hyperlink ref="H113" r:id="rId112"/>
+    <hyperlink ref="H114" r:id="rId113"/>
+    <hyperlink ref="H115" r:id="rId114"/>
+    <hyperlink ref="H116" r:id="rId115"/>
+    <hyperlink ref="H117" r:id="rId116"/>
+    <hyperlink ref="H118" r:id="rId117"/>
+    <hyperlink ref="H119" r:id="rId118"/>
+    <hyperlink ref="H120" r:id="rId119"/>
+    <hyperlink ref="H121" r:id="rId120"/>
+    <hyperlink ref="H122" r:id="rId121"/>
+    <hyperlink ref="H123" r:id="rId122"/>
+    <hyperlink ref="H124" r:id="rId123"/>
+    <hyperlink ref="H125" r:id="rId124"/>
+    <hyperlink ref="H126" r:id="rId125"/>
+    <hyperlink ref="H127" r:id="rId126"/>
+    <hyperlink ref="H128" r:id="rId127"/>
+    <hyperlink ref="H129" r:id="rId128"/>
+    <hyperlink ref="H130" r:id="rId129"/>
+    <hyperlink ref="H131" r:id="rId130"/>
+    <hyperlink ref="H132" r:id="rId131"/>
+    <hyperlink ref="H133" r:id="rId132"/>
+    <hyperlink ref="H134" r:id="rId133"/>
+    <hyperlink ref="H135" r:id="rId134"/>
+    <hyperlink ref="H136" r:id="rId135"/>
+    <hyperlink ref="H137" r:id="rId136"/>
+    <hyperlink ref="H138" r:id="rId137"/>
+    <hyperlink ref="H139" r:id="rId138"/>
+    <hyperlink ref="H140" r:id="rId139"/>
+    <hyperlink ref="H141" r:id="rId140"/>
+    <hyperlink ref="H142" r:id="rId141"/>
+    <hyperlink ref="H143" r:id="rId142"/>
+    <hyperlink ref="H144" r:id="rId143"/>
+    <hyperlink ref="H145" r:id="rId144"/>
+    <hyperlink ref="H146" r:id="rId145"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/docs/xlsx/jobs-2026-10-09.xlsx
+++ b/docs/xlsx/jobs-2026-10-09.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1292" uniqueCount="854">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1306" uniqueCount="858">
   <si>
     <t>Title</t>
   </si>
@@ -1072,6 +1072,12 @@
     <t>https://www.idealist.org/en/nonprofit-job/c23a9bcf12484d3f89d5aafc33352023-contract-art-therapist-in-bronx-schools-2-full-days-per-week-art-therapy-project-corporation-tatp-the-bronx-county</t>
   </si>
   <si>
+    <t>The Art Therapy Project</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c23a9bcf12484d3f89d5aafc33352023-contract-art-therapist-in-bronx-schools-2-full-days-per-week-the-art-therapy-project-bronx-county</t>
+  </si>
+  <si>
     <t>Conversation Class Instructor –Adults</t>
   </si>
   <si>
@@ -2453,6 +2459,12 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/634fdf66f34b47f6a33ef20361ea05cf-trainer-arts-puerto-rico-programs-the-posse-foundation-inc-arts-puerto-rico-new-york</t>
+  </si>
+  <si>
+    <t>The Posse Foundation, Inc. - Arts + Puerto Rico Programs</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/634fdf66f34b47f6a33ef20361ea05cf-trainer-arts-puerto-rico-programs-the-posse-foundation-inc-arts-puerto-rico-programs-new-york</t>
   </si>
   <si>
     <t>Training &amp; Resources Coordinator</t>
@@ -3901,7 +3913,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H146"/>
+  <dimension ref="A1:H148"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -4632,358 +4644,358 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>346</v>
+      </c>
+      <c r="B32" t="s">
         <v>352</v>
       </c>
-      <c r="B32" t="s">
-        <v>353</v>
-      </c>
       <c r="C32" t="s">
-        <v>197</v>
+        <v>348</v>
       </c>
       <c r="D32" t="s">
         <v>205</v>
       </c>
       <c r="E32" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="F32" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="B33" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="C33" t="s">
         <v>197</v>
       </c>
       <c r="D33" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="E33" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="F33" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>359</v>
+      </c>
+      <c r="B34" t="s">
+        <v>360</v>
+      </c>
+      <c r="C34" t="s">
+        <v>197</v>
+      </c>
+      <c r="D34" t="s">
+        <v>211</v>
+      </c>
+      <c r="E34" t="s">
+        <v>361</v>
+      </c>
+      <c r="F34" t="s">
         <v>362</v>
       </c>
-      <c r="B34" t="s">
+      <c r="H34" s="2" t="s">
         <v>363</v>
-      </c>
-      <c r="C34" t="s">
-        <v>364</v>
-      </c>
-      <c r="D34" t="s">
-        <v>302</v>
-      </c>
-      <c r="E34" t="s">
-        <v>365</v>
-      </c>
-      <c r="F34" t="s">
-        <v>366</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>364</v>
+      </c>
+      <c r="B35" t="s">
+        <v>365</v>
+      </c>
+      <c r="C35" t="s">
+        <v>366</v>
+      </c>
+      <c r="D35" t="s">
+        <v>302</v>
+      </c>
+      <c r="E35" t="s">
+        <v>367</v>
+      </c>
+      <c r="F35" t="s">
         <v>368</v>
       </c>
-      <c r="B35" t="s">
+      <c r="H35" s="2" t="s">
         <v>369</v>
-      </c>
-      <c r="C35" t="s">
-        <v>370</v>
-      </c>
-      <c r="D35" t="s">
-        <v>211</v>
-      </c>
-      <c r="E35" t="s">
-        <v>371</v>
-      </c>
-      <c r="F35" t="s">
-        <v>225</v>
-      </c>
-      <c r="H35" s="2" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>370</v>
+      </c>
+      <c r="B36" t="s">
+        <v>371</v>
+      </c>
+      <c r="C36" t="s">
+        <v>372</v>
+      </c>
+      <c r="D36" t="s">
+        <v>211</v>
+      </c>
+      <c r="E36" t="s">
         <v>373</v>
       </c>
-      <c r="B36" t="s">
-        <v>341</v>
-      </c>
-      <c r="C36" t="s">
-        <v>342</v>
-      </c>
-      <c r="D36" t="s">
-        <v>211</v>
-      </c>
-      <c r="E36" t="s">
+      <c r="F36" t="s">
+        <v>225</v>
+      </c>
+      <c r="H36" s="2" t="s">
         <v>374</v>
-      </c>
-      <c r="F36" t="s">
-        <v>344</v>
-      </c>
-      <c r="H36" s="2" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B37" t="s">
         <v>341</v>
       </c>
       <c r="C37" t="s">
-        <v>377</v>
+        <v>342</v>
       </c>
       <c r="D37" t="s">
         <v>211</v>
       </c>
       <c r="E37" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="F37" t="s">
         <v>344</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>378</v>
+      </c>
+      <c r="B38" t="s">
+        <v>341</v>
+      </c>
+      <c r="C38" t="s">
         <v>379</v>
       </c>
-      <c r="B38" t="s">
+      <c r="D38" t="s">
+        <v>211</v>
+      </c>
+      <c r="E38" t="s">
+        <v>376</v>
+      </c>
+      <c r="F38" t="s">
+        <v>344</v>
+      </c>
+      <c r="H38" s="2" t="s">
         <v>380</v>
-      </c>
-      <c r="C38" t="s">
-        <v>381</v>
-      </c>
-      <c r="D38" t="s">
-        <v>211</v>
-      </c>
-      <c r="E38" t="s">
-        <v>382</v>
-      </c>
-      <c r="F38" t="s">
-        <v>383</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>381</v>
+      </c>
+      <c r="B39" t="s">
+        <v>382</v>
+      </c>
+      <c r="C39" t="s">
+        <v>383</v>
+      </c>
+      <c r="D39" t="s">
+        <v>211</v>
+      </c>
+      <c r="E39" t="s">
+        <v>384</v>
+      </c>
+      <c r="F39" t="s">
         <v>385</v>
       </c>
-      <c r="B39" t="s">
+      <c r="H39" s="2" t="s">
         <v>386</v>
-      </c>
-      <c r="C39" t="s">
-        <v>197</v>
-      </c>
-      <c r="D39" t="s">
-        <v>211</v>
-      </c>
-      <c r="E39" t="s">
-        <v>387</v>
-      </c>
-      <c r="F39" t="s">
-        <v>388</v>
-      </c>
-      <c r="H39" s="2" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B40" t="s">
+        <v>388</v>
+      </c>
+      <c r="C40" t="s">
+        <v>197</v>
+      </c>
+      <c r="D40" t="s">
+        <v>211</v>
+      </c>
+      <c r="E40" t="s">
+        <v>389</v>
+      </c>
+      <c r="F40" t="s">
         <v>390</v>
       </c>
-      <c r="C40" t="s">
-        <v>276</v>
-      </c>
-      <c r="D40" t="s">
-        <v>302</v>
-      </c>
-      <c r="E40" t="s">
+      <c r="H40" s="2" t="s">
         <v>391</v>
-      </c>
-      <c r="F40" t="s">
-        <v>192</v>
-      </c>
-      <c r="H40" s="2" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>387</v>
+      </c>
+      <c r="B41" t="s">
+        <v>392</v>
+      </c>
+      <c r="C41" t="s">
+        <v>276</v>
+      </c>
+      <c r="D41" t="s">
+        <v>302</v>
+      </c>
+      <c r="E41" t="s">
         <v>393</v>
       </c>
-      <c r="B41" t="s">
+      <c r="F41" t="s">
+        <v>192</v>
+      </c>
+      <c r="H41" s="2" t="s">
         <v>394</v>
-      </c>
-      <c r="C41" t="s">
-        <v>395</v>
-      </c>
-      <c r="D41" t="s">
-        <v>331</v>
-      </c>
-      <c r="E41" t="s">
-        <v>396</v>
-      </c>
-      <c r="F41" t="s">
-        <v>383</v>
-      </c>
-      <c r="H41" s="2" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>395</v>
+      </c>
+      <c r="B42" t="s">
+        <v>396</v>
+      </c>
+      <c r="C42" t="s">
+        <v>397</v>
+      </c>
+      <c r="D42" t="s">
+        <v>331</v>
+      </c>
+      <c r="E42" t="s">
         <v>398</v>
       </c>
-      <c r="B42" t="s">
+      <c r="F42" t="s">
+        <v>385</v>
+      </c>
+      <c r="H42" s="2" t="s">
         <v>399</v>
-      </c>
-      <c r="C42" t="s">
-        <v>235</v>
-      </c>
-      <c r="D42" t="s">
-        <v>211</v>
-      </c>
-      <c r="E42" t="s">
-        <v>400</v>
-      </c>
-      <c r="F42" t="s">
-        <v>401</v>
-      </c>
-      <c r="H42" s="2" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>400</v>
+      </c>
+      <c r="B43" t="s">
+        <v>401</v>
+      </c>
+      <c r="C43" t="s">
+        <v>235</v>
+      </c>
+      <c r="D43" t="s">
+        <v>211</v>
+      </c>
+      <c r="E43" t="s">
+        <v>402</v>
+      </c>
+      <c r="F43" t="s">
         <v>403</v>
       </c>
-      <c r="B43" t="s">
+      <c r="H43" s="2" t="s">
         <v>404</v>
-      </c>
-      <c r="C43" t="s">
-        <v>197</v>
-      </c>
-      <c r="D43" t="s">
-        <v>211</v>
-      </c>
-      <c r="E43" t="s">
-        <v>405</v>
-      </c>
-      <c r="F43" t="s">
-        <v>406</v>
-      </c>
-      <c r="H43" s="2" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
+        <v>405</v>
+      </c>
+      <c r="B44" t="s">
+        <v>406</v>
+      </c>
+      <c r="C44" t="s">
+        <v>197</v>
+      </c>
+      <c r="D44" t="s">
+        <v>211</v>
+      </c>
+      <c r="E44" t="s">
+        <v>407</v>
+      </c>
+      <c r="F44" t="s">
         <v>408</v>
       </c>
-      <c r="B44" t="s">
+      <c r="H44" s="2" t="s">
         <v>409</v>
-      </c>
-      <c r="C44" t="s">
-        <v>410</v>
-      </c>
-      <c r="D44" t="s">
-        <v>211</v>
-      </c>
-      <c r="E44" t="s">
-        <v>411</v>
-      </c>
-      <c r="F44" t="s">
-        <v>412</v>
-      </c>
-      <c r="H44" s="2" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
+        <v>410</v>
+      </c>
+      <c r="B45" t="s">
+        <v>411</v>
+      </c>
+      <c r="C45" t="s">
+        <v>412</v>
+      </c>
+      <c r="D45" t="s">
+        <v>211</v>
+      </c>
+      <c r="E45" t="s">
+        <v>413</v>
+      </c>
+      <c r="F45" t="s">
         <v>414</v>
       </c>
-      <c r="B45" t="s">
+      <c r="H45" s="2" t="s">
         <v>415</v>
-      </c>
-      <c r="C45" t="s">
-        <v>197</v>
-      </c>
-      <c r="D45" t="s">
-        <v>211</v>
-      </c>
-      <c r="E45" t="s">
-        <v>416</v>
-      </c>
-      <c r="F45" t="s">
-        <v>338</v>
-      </c>
-      <c r="H45" s="2" t="s">
-        <v>417</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
+        <v>416</v>
+      </c>
+      <c r="B46" t="s">
+        <v>417</v>
+      </c>
+      <c r="C46" t="s">
+        <v>197</v>
+      </c>
+      <c r="D46" t="s">
+        <v>211</v>
+      </c>
+      <c r="E46" t="s">
         <v>418</v>
       </c>
-      <c r="B46" t="s">
+      <c r="F46" t="s">
+        <v>338</v>
+      </c>
+      <c r="H46" s="2" t="s">
         <v>419</v>
-      </c>
-      <c r="C46" t="s">
-        <v>420</v>
-      </c>
-      <c r="D46" t="s">
-        <v>211</v>
-      </c>
-      <c r="E46" t="s">
-        <v>192</v>
-      </c>
-      <c r="F46" t="s">
-        <v>421</v>
-      </c>
-      <c r="H46" s="2" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="B47" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="C47" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="D47" t="s">
         <v>211</v>
@@ -4992,110 +5004,110 @@
         <v>192</v>
       </c>
       <c r="F47" t="s">
-        <v>192</v>
+        <v>423</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>425</v>
+      </c>
+      <c r="B48" t="s">
+        <v>426</v>
+      </c>
+      <c r="C48" t="s">
         <v>427</v>
       </c>
-      <c r="B48" t="s">
+      <c r="D48" t="s">
+        <v>211</v>
+      </c>
+      <c r="E48" t="s">
+        <v>192</v>
+      </c>
+      <c r="F48" t="s">
+        <v>192</v>
+      </c>
+      <c r="H48" s="2" t="s">
         <v>428</v>
-      </c>
-      <c r="C48" t="s">
-        <v>197</v>
-      </c>
-      <c r="D48" t="s">
-        <v>211</v>
-      </c>
-      <c r="E48" t="s">
-        <v>429</v>
-      </c>
-      <c r="F48" t="s">
-        <v>430</v>
-      </c>
-      <c r="H48" s="2" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>429</v>
+      </c>
+      <c r="B49" t="s">
+        <v>430</v>
+      </c>
+      <c r="C49" t="s">
+        <v>197</v>
+      </c>
+      <c r="D49" t="s">
+        <v>211</v>
+      </c>
+      <c r="E49" t="s">
+        <v>431</v>
+      </c>
+      <c r="F49" t="s">
         <v>432</v>
       </c>
-      <c r="B49" t="s">
+      <c r="H49" s="2" t="s">
         <v>433</v>
-      </c>
-      <c r="C49" t="s">
-        <v>434</v>
-      </c>
-      <c r="D49" t="s">
-        <v>211</v>
-      </c>
-      <c r="E49" t="s">
-        <v>435</v>
-      </c>
-      <c r="F49" t="s">
-        <v>436</v>
-      </c>
-      <c r="H49" s="2" t="s">
-        <v>437</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>434</v>
+      </c>
+      <c r="B50" t="s">
+        <v>435</v>
+      </c>
+      <c r="C50" t="s">
+        <v>436</v>
+      </c>
+      <c r="D50" t="s">
+        <v>211</v>
+      </c>
+      <c r="E50" t="s">
+        <v>437</v>
+      </c>
+      <c r="F50" t="s">
         <v>438</v>
       </c>
-      <c r="B50" t="s">
+      <c r="H50" s="2" t="s">
         <v>439</v>
-      </c>
-      <c r="C50" t="s">
-        <v>440</v>
-      </c>
-      <c r="D50" t="s">
-        <v>211</v>
-      </c>
-      <c r="E50" t="s">
-        <v>441</v>
-      </c>
-      <c r="F50" t="s">
-        <v>442</v>
-      </c>
-      <c r="H50" s="2" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>440</v>
+      </c>
+      <c r="B51" t="s">
+        <v>441</v>
+      </c>
+      <c r="C51" t="s">
+        <v>442</v>
+      </c>
+      <c r="D51" t="s">
+        <v>211</v>
+      </c>
+      <c r="E51" t="s">
+        <v>443</v>
+      </c>
+      <c r="F51" t="s">
         <v>444</v>
       </c>
-      <c r="B51" t="s">
+      <c r="H51" s="2" t="s">
         <v>445</v>
-      </c>
-      <c r="C51" t="s">
-        <v>235</v>
-      </c>
-      <c r="D51" t="s">
-        <v>211</v>
-      </c>
-      <c r="E51" t="s">
-        <v>446</v>
-      </c>
-      <c r="F51" t="s">
-        <v>447</v>
-      </c>
-      <c r="H51" s="2" t="s">
-        <v>448</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="B52" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="C52" t="s">
         <v>235</v>
@@ -5104,677 +5116,677 @@
         <v>211</v>
       </c>
       <c r="E52" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="F52" t="s">
-        <v>284</v>
+        <v>449</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>451</v>
+      </c>
+      <c r="B53" t="s">
+        <v>452</v>
+      </c>
+      <c r="C53" t="s">
+        <v>235</v>
+      </c>
+      <c r="D53" t="s">
+        <v>211</v>
+      </c>
+      <c r="E53" t="s">
         <v>453</v>
       </c>
-      <c r="B53" t="s">
+      <c r="F53" t="s">
+        <v>284</v>
+      </c>
+      <c r="H53" s="2" t="s">
         <v>454</v>
-      </c>
-      <c r="C53" t="s">
-        <v>455</v>
-      </c>
-      <c r="D53" t="s">
-        <v>211</v>
-      </c>
-      <c r="E53" t="s">
-        <v>456</v>
-      </c>
-      <c r="F53" t="s">
-        <v>457</v>
-      </c>
-      <c r="H53" s="2" t="s">
-        <v>458</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B54" t="s">
+        <v>456</v>
+      </c>
+      <c r="C54" t="s">
+        <v>457</v>
+      </c>
+      <c r="D54" t="s">
+        <v>211</v>
+      </c>
+      <c r="E54" t="s">
+        <v>458</v>
+      </c>
+      <c r="F54" t="s">
         <v>459</v>
       </c>
-      <c r="C54" t="s">
+      <c r="H54" s="2" t="s">
         <v>460</v>
-      </c>
-      <c r="D54" t="s">
-        <v>211</v>
-      </c>
-      <c r="E54" t="s">
-        <v>446</v>
-      </c>
-      <c r="F54" t="s">
-        <v>461</v>
-      </c>
-      <c r="H54" s="2" t="s">
-        <v>462</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B55" t="s">
+        <v>461</v>
+      </c>
+      <c r="C55" t="s">
+        <v>462</v>
+      </c>
+      <c r="D55" t="s">
+        <v>211</v>
+      </c>
+      <c r="E55" t="s">
+        <v>448</v>
+      </c>
+      <c r="F55" t="s">
         <v>463</v>
       </c>
-      <c r="C55" t="s">
-        <v>276</v>
-      </c>
-      <c r="D55" t="s">
-        <v>211</v>
-      </c>
-      <c r="E55" t="s">
+      <c r="H55" s="2" t="s">
         <v>464</v>
-      </c>
-      <c r="F55" t="s">
-        <v>465</v>
-      </c>
-      <c r="H55" s="2" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B56" t="s">
+        <v>465</v>
+      </c>
+      <c r="C56" t="s">
+        <v>276</v>
+      </c>
+      <c r="D56" t="s">
+        <v>211</v>
+      </c>
+      <c r="E56" t="s">
+        <v>466</v>
+      </c>
+      <c r="F56" t="s">
         <v>467</v>
       </c>
-      <c r="C56" t="s">
-        <v>223</v>
-      </c>
-      <c r="D56" t="s">
-        <v>211</v>
-      </c>
-      <c r="E56" t="s">
+      <c r="H56" s="2" t="s">
         <v>468</v>
-      </c>
-      <c r="F56" t="s">
-        <v>469</v>
-      </c>
-      <c r="H56" s="2" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
+        <v>455</v>
+      </c>
+      <c r="B57" t="s">
+        <v>469</v>
+      </c>
+      <c r="C57" t="s">
+        <v>223</v>
+      </c>
+      <c r="D57" t="s">
+        <v>211</v>
+      </c>
+      <c r="E57" t="s">
+        <v>470</v>
+      </c>
+      <c r="F57" t="s">
         <v>471</v>
       </c>
-      <c r="B57" t="s">
+      <c r="H57" s="2" t="s">
         <v>472</v>
-      </c>
-      <c r="C57" t="s">
-        <v>315</v>
-      </c>
-      <c r="D57" t="s">
-        <v>211</v>
-      </c>
-      <c r="E57" t="s">
-        <v>473</v>
-      </c>
-      <c r="F57" t="s">
-        <v>474</v>
-      </c>
-      <c r="H57" s="2" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
+        <v>473</v>
+      </c>
+      <c r="B58" t="s">
+        <v>474</v>
+      </c>
+      <c r="C58" t="s">
+        <v>315</v>
+      </c>
+      <c r="D58" t="s">
+        <v>211</v>
+      </c>
+      <c r="E58" t="s">
+        <v>475</v>
+      </c>
+      <c r="F58" t="s">
         <v>476</v>
       </c>
-      <c r="B58" t="s">
+      <c r="H58" s="2" t="s">
         <v>477</v>
-      </c>
-      <c r="C58" t="s">
-        <v>478</v>
-      </c>
-      <c r="D58" t="s">
-        <v>331</v>
-      </c>
-      <c r="E58" t="s">
-        <v>479</v>
-      </c>
-      <c r="F58" t="s">
-        <v>480</v>
-      </c>
-      <c r="H58" s="2" t="s">
-        <v>481</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
+        <v>478</v>
+      </c>
+      <c r="B59" t="s">
+        <v>479</v>
+      </c>
+      <c r="C59" t="s">
+        <v>480</v>
+      </c>
+      <c r="D59" t="s">
+        <v>331</v>
+      </c>
+      <c r="E59" t="s">
+        <v>481</v>
+      </c>
+      <c r="F59" t="s">
         <v>482</v>
       </c>
-      <c r="B59" t="s">
+      <c r="H59" s="2" t="s">
         <v>483</v>
-      </c>
-      <c r="C59" t="s">
-        <v>484</v>
-      </c>
-      <c r="D59" t="s">
-        <v>211</v>
-      </c>
-      <c r="E59" t="s">
-        <v>485</v>
-      </c>
-      <c r="F59" t="s">
-        <v>192</v>
-      </c>
-      <c r="H59" s="2" t="s">
-        <v>486</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
+        <v>484</v>
+      </c>
+      <c r="B60" t="s">
+        <v>485</v>
+      </c>
+      <c r="C60" t="s">
+        <v>486</v>
+      </c>
+      <c r="D60" t="s">
+        <v>211</v>
+      </c>
+      <c r="E60" t="s">
         <v>487</v>
       </c>
-      <c r="B60" t="s">
+      <c r="F60" t="s">
+        <v>192</v>
+      </c>
+      <c r="H60" s="2" t="s">
         <v>488</v>
-      </c>
-      <c r="C60" t="s">
-        <v>489</v>
-      </c>
-      <c r="D60" t="s">
-        <v>211</v>
-      </c>
-      <c r="E60" t="s">
-        <v>192</v>
-      </c>
-      <c r="F60" t="s">
-        <v>490</v>
-      </c>
-      <c r="H60" s="2" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
+        <v>489</v>
+      </c>
+      <c r="B61" t="s">
+        <v>490</v>
+      </c>
+      <c r="C61" t="s">
+        <v>491</v>
+      </c>
+      <c r="D61" t="s">
+        <v>211</v>
+      </c>
+      <c r="E61" t="s">
+        <v>192</v>
+      </c>
+      <c r="F61" t="s">
         <v>492</v>
       </c>
-      <c r="B61" t="s">
+      <c r="H61" s="2" t="s">
         <v>493</v>
-      </c>
-      <c r="C61" t="s">
-        <v>246</v>
-      </c>
-      <c r="D61" t="s">
-        <v>211</v>
-      </c>
-      <c r="E61" t="s">
-        <v>494</v>
-      </c>
-      <c r="F61" t="s">
-        <v>495</v>
-      </c>
-      <c r="H61" s="2" t="s">
-        <v>496</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
+        <v>494</v>
+      </c>
+      <c r="B62" t="s">
+        <v>495</v>
+      </c>
+      <c r="C62" t="s">
+        <v>246</v>
+      </c>
+      <c r="D62" t="s">
+        <v>211</v>
+      </c>
+      <c r="E62" t="s">
+        <v>496</v>
+      </c>
+      <c r="F62" t="s">
         <v>497</v>
       </c>
-      <c r="B62" t="s">
+      <c r="H62" s="2" t="s">
         <v>498</v>
-      </c>
-      <c r="C62" t="s">
-        <v>499</v>
-      </c>
-      <c r="D62" t="s">
-        <v>211</v>
-      </c>
-      <c r="E62" t="s">
-        <v>500</v>
-      </c>
-      <c r="F62" t="s">
-        <v>192</v>
-      </c>
-      <c r="H62" s="2" t="s">
-        <v>501</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
+        <v>499</v>
+      </c>
+      <c r="B63" t="s">
+        <v>500</v>
+      </c>
+      <c r="C63" t="s">
+        <v>501</v>
+      </c>
+      <c r="D63" t="s">
+        <v>211</v>
+      </c>
+      <c r="E63" t="s">
         <v>502</v>
       </c>
-      <c r="B63" t="s">
+      <c r="F63" t="s">
+        <v>192</v>
+      </c>
+      <c r="H63" s="2" t="s">
         <v>503</v>
-      </c>
-      <c r="C63" t="s">
-        <v>504</v>
-      </c>
-      <c r="D63" t="s">
-        <v>211</v>
-      </c>
-      <c r="E63" t="s">
-        <v>473</v>
-      </c>
-      <c r="F63" t="s">
-        <v>317</v>
-      </c>
-      <c r="H63" s="2" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
+        <v>504</v>
+      </c>
+      <c r="B64" t="s">
+        <v>505</v>
+      </c>
+      <c r="C64" t="s">
         <v>506</v>
       </c>
-      <c r="B64" t="s">
+      <c r="D64" t="s">
+        <v>211</v>
+      </c>
+      <c r="E64" t="s">
+        <v>475</v>
+      </c>
+      <c r="F64" t="s">
+        <v>317</v>
+      </c>
+      <c r="H64" s="2" t="s">
         <v>507</v>
-      </c>
-      <c r="C64" t="s">
-        <v>508</v>
-      </c>
-      <c r="D64" t="s">
-        <v>302</v>
-      </c>
-      <c r="E64" t="s">
-        <v>509</v>
-      </c>
-      <c r="F64" t="s">
-        <v>510</v>
-      </c>
-      <c r="H64" s="2" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
+        <v>508</v>
+      </c>
+      <c r="B65" t="s">
+        <v>509</v>
+      </c>
+      <c r="C65" t="s">
+        <v>510</v>
+      </c>
+      <c r="D65" t="s">
+        <v>302</v>
+      </c>
+      <c r="E65" t="s">
+        <v>511</v>
+      </c>
+      <c r="F65" t="s">
         <v>512</v>
       </c>
-      <c r="B65" t="s">
+      <c r="H65" s="2" t="s">
         <v>513</v>
-      </c>
-      <c r="C65" t="s">
-        <v>514</v>
-      </c>
-      <c r="D65" t="s">
-        <v>211</v>
-      </c>
-      <c r="E65" t="s">
-        <v>515</v>
-      </c>
-      <c r="F65" t="s">
-        <v>516</v>
-      </c>
-      <c r="H65" s="2" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
+        <v>514</v>
+      </c>
+      <c r="B66" t="s">
+        <v>515</v>
+      </c>
+      <c r="C66" t="s">
+        <v>516</v>
+      </c>
+      <c r="D66" t="s">
+        <v>211</v>
+      </c>
+      <c r="E66" t="s">
+        <v>517</v>
+      </c>
+      <c r="F66" t="s">
         <v>518</v>
       </c>
-      <c r="B66" t="s">
-        <v>222</v>
-      </c>
-      <c r="C66" t="s">
-        <v>223</v>
-      </c>
-      <c r="D66" t="s">
-        <v>211</v>
-      </c>
-      <c r="E66" t="s">
+      <c r="H66" s="2" t="s">
         <v>519</v>
-      </c>
-      <c r="F66" t="s">
-        <v>225</v>
-      </c>
-      <c r="H66" s="2" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
+        <v>520</v>
+      </c>
+      <c r="B67" t="s">
+        <v>222</v>
+      </c>
+      <c r="C67" t="s">
+        <v>223</v>
+      </c>
+      <c r="D67" t="s">
+        <v>211</v>
+      </c>
+      <c r="E67" t="s">
         <v>521</v>
       </c>
-      <c r="B67" t="s">
+      <c r="F67" t="s">
+        <v>225</v>
+      </c>
+      <c r="H67" s="2" t="s">
         <v>522</v>
-      </c>
-      <c r="C67" t="s">
-        <v>276</v>
-      </c>
-      <c r="D67" t="s">
-        <v>211</v>
-      </c>
-      <c r="E67" t="s">
-        <v>523</v>
-      </c>
-      <c r="F67" t="s">
-        <v>524</v>
-      </c>
-      <c r="H67" s="2" t="s">
-        <v>525</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
+        <v>523</v>
+      </c>
+      <c r="B68" t="s">
+        <v>524</v>
+      </c>
+      <c r="C68" t="s">
+        <v>276</v>
+      </c>
+      <c r="D68" t="s">
+        <v>211</v>
+      </c>
+      <c r="E68" t="s">
+        <v>525</v>
+      </c>
+      <c r="F68" t="s">
         <v>526</v>
       </c>
-      <c r="B68" t="s">
+      <c r="H68" s="2" t="s">
         <v>527</v>
-      </c>
-      <c r="C68" t="s">
-        <v>336</v>
-      </c>
-      <c r="D68" t="s">
-        <v>331</v>
-      </c>
-      <c r="E68" t="s">
-        <v>528</v>
-      </c>
-      <c r="F68" t="s">
-        <v>529</v>
-      </c>
-      <c r="H68" s="2" t="s">
-        <v>530</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
+        <v>528</v>
+      </c>
+      <c r="B69" t="s">
+        <v>529</v>
+      </c>
+      <c r="C69" t="s">
+        <v>336</v>
+      </c>
+      <c r="D69" t="s">
+        <v>331</v>
+      </c>
+      <c r="E69" t="s">
+        <v>530</v>
+      </c>
+      <c r="F69" t="s">
         <v>531</v>
       </c>
-      <c r="B69" t="s">
+      <c r="H69" s="2" t="s">
         <v>532</v>
-      </c>
-      <c r="C69" t="s">
-        <v>197</v>
-      </c>
-      <c r="D69" t="s">
-        <v>302</v>
-      </c>
-      <c r="E69" t="s">
-        <v>533</v>
-      </c>
-      <c r="F69" t="s">
-        <v>534</v>
-      </c>
-      <c r="H69" s="2" t="s">
-        <v>535</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
+        <v>533</v>
+      </c>
+      <c r="B70" t="s">
+        <v>534</v>
+      </c>
+      <c r="C70" t="s">
+        <v>197</v>
+      </c>
+      <c r="D70" t="s">
+        <v>302</v>
+      </c>
+      <c r="E70" t="s">
+        <v>535</v>
+      </c>
+      <c r="F70" t="s">
         <v>536</v>
       </c>
-      <c r="B70" t="s">
+      <c r="H70" s="2" t="s">
         <v>537</v>
-      </c>
-      <c r="C70" t="s">
-        <v>538</v>
-      </c>
-      <c r="D70" t="s">
-        <v>205</v>
-      </c>
-      <c r="E70" t="s">
-        <v>539</v>
-      </c>
-      <c r="F70" t="s">
-        <v>540</v>
-      </c>
-      <c r="H70" s="2" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
+        <v>538</v>
+      </c>
+      <c r="B71" t="s">
+        <v>539</v>
+      </c>
+      <c r="C71" t="s">
+        <v>540</v>
+      </c>
+      <c r="D71" t="s">
+        <v>205</v>
+      </c>
+      <c r="E71" t="s">
+        <v>541</v>
+      </c>
+      <c r="F71" t="s">
         <v>542</v>
       </c>
-      <c r="B71" t="s">
+      <c r="H71" s="2" t="s">
         <v>543</v>
-      </c>
-      <c r="C71" t="s">
-        <v>544</v>
-      </c>
-      <c r="D71" t="s">
-        <v>211</v>
-      </c>
-      <c r="E71" t="s">
-        <v>545</v>
-      </c>
-      <c r="F71" t="s">
-        <v>546</v>
-      </c>
-      <c r="H71" s="2" t="s">
-        <v>547</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
+        <v>544</v>
+      </c>
+      <c r="B72" t="s">
+        <v>545</v>
+      </c>
+      <c r="C72" t="s">
+        <v>546</v>
+      </c>
+      <c r="D72" t="s">
+        <v>211</v>
+      </c>
+      <c r="E72" t="s">
+        <v>547</v>
+      </c>
+      <c r="F72" t="s">
         <v>548</v>
       </c>
-      <c r="B72" t="s">
-        <v>222</v>
-      </c>
-      <c r="C72" t="s">
-        <v>223</v>
-      </c>
-      <c r="D72" t="s">
-        <v>211</v>
-      </c>
-      <c r="E72" t="s">
+      <c r="H72" s="2" t="s">
         <v>549</v>
-      </c>
-      <c r="F72" t="s">
-        <v>225</v>
-      </c>
-      <c r="H72" s="2" t="s">
-        <v>550</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
+        <v>550</v>
+      </c>
+      <c r="B73" t="s">
+        <v>222</v>
+      </c>
+      <c r="C73" t="s">
+        <v>223</v>
+      </c>
+      <c r="D73" t="s">
+        <v>211</v>
+      </c>
+      <c r="E73" t="s">
         <v>551</v>
       </c>
-      <c r="B73" t="s">
-        <v>341</v>
-      </c>
-      <c r="C73" t="s">
+      <c r="F73" t="s">
+        <v>225</v>
+      </c>
+      <c r="H73" s="2" t="s">
         <v>552</v>
-      </c>
-      <c r="D73" t="s">
-        <v>211</v>
-      </c>
-      <c r="E73" t="s">
-        <v>553</v>
-      </c>
-      <c r="F73" t="s">
-        <v>344</v>
-      </c>
-      <c r="H73" s="2" t="s">
-        <v>554</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
+        <v>553</v>
+      </c>
+      <c r="B74" t="s">
+        <v>341</v>
+      </c>
+      <c r="C74" t="s">
+        <v>554</v>
+      </c>
+      <c r="D74" t="s">
+        <v>211</v>
+      </c>
+      <c r="E74" t="s">
         <v>555</v>
       </c>
-      <c r="B74" t="s">
+      <c r="F74" t="s">
+        <v>344</v>
+      </c>
+      <c r="H74" s="2" t="s">
         <v>556</v>
-      </c>
-      <c r="C74" t="s">
-        <v>557</v>
-      </c>
-      <c r="D74" t="s">
-        <v>211</v>
-      </c>
-      <c r="E74" t="s">
-        <v>558</v>
-      </c>
-      <c r="F74" t="s">
-        <v>559</v>
-      </c>
-      <c r="H74" s="2" t="s">
-        <v>560</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
+        <v>557</v>
+      </c>
+      <c r="B75" t="s">
+        <v>558</v>
+      </c>
+      <c r="C75" t="s">
+        <v>559</v>
+      </c>
+      <c r="D75" t="s">
+        <v>211</v>
+      </c>
+      <c r="E75" t="s">
+        <v>560</v>
+      </c>
+      <c r="F75" t="s">
         <v>561</v>
       </c>
-      <c r="B75" t="s">
+      <c r="H75" s="2" t="s">
         <v>562</v>
-      </c>
-      <c r="C75" t="s">
-        <v>197</v>
-      </c>
-      <c r="D75" t="s">
-        <v>211</v>
-      </c>
-      <c r="E75" t="s">
-        <v>563</v>
-      </c>
-      <c r="F75" t="s">
-        <v>206</v>
-      </c>
-      <c r="H75" s="2" t="s">
-        <v>564</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
+        <v>563</v>
+      </c>
+      <c r="B76" t="s">
+        <v>564</v>
+      </c>
+      <c r="C76" t="s">
+        <v>197</v>
+      </c>
+      <c r="D76" t="s">
+        <v>211</v>
+      </c>
+      <c r="E76" t="s">
         <v>565</v>
       </c>
-      <c r="B76" t="s">
+      <c r="F76" t="s">
+        <v>206</v>
+      </c>
+      <c r="H76" s="2" t="s">
         <v>566</v>
-      </c>
-      <c r="C76" t="s">
-        <v>276</v>
-      </c>
-      <c r="D76" t="s">
-        <v>302</v>
-      </c>
-      <c r="E76" t="s">
-        <v>567</v>
-      </c>
-      <c r="F76" t="s">
-        <v>568</v>
-      </c>
-      <c r="H76" s="2" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
+        <v>567</v>
+      </c>
+      <c r="B77" t="s">
+        <v>568</v>
+      </c>
+      <c r="C77" t="s">
+        <v>276</v>
+      </c>
+      <c r="D77" t="s">
+        <v>302</v>
+      </c>
+      <c r="E77" t="s">
+        <v>569</v>
+      </c>
+      <c r="F77" t="s">
         <v>570</v>
       </c>
-      <c r="B77" t="s">
+      <c r="H77" s="2" t="s">
         <v>571</v>
-      </c>
-      <c r="C77" t="s">
-        <v>223</v>
-      </c>
-      <c r="D77" t="s">
-        <v>211</v>
-      </c>
-      <c r="E77" t="s">
-        <v>572</v>
-      </c>
-      <c r="F77" t="s">
-        <v>540</v>
-      </c>
-      <c r="H77" s="2" t="s">
-        <v>573</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
+        <v>572</v>
+      </c>
+      <c r="B78" t="s">
+        <v>573</v>
+      </c>
+      <c r="C78" t="s">
+        <v>223</v>
+      </c>
+      <c r="D78" t="s">
+        <v>211</v>
+      </c>
+      <c r="E78" t="s">
         <v>574</v>
       </c>
-      <c r="B78" t="s">
+      <c r="F78" t="s">
+        <v>542</v>
+      </c>
+      <c r="H78" s="2" t="s">
         <v>575</v>
-      </c>
-      <c r="C78" t="s">
-        <v>276</v>
-      </c>
-      <c r="D78" t="s">
-        <v>211</v>
-      </c>
-      <c r="E78" t="s">
-        <v>576</v>
-      </c>
-      <c r="F78" t="s">
-        <v>577</v>
-      </c>
-      <c r="H78" s="2" t="s">
-        <v>578</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
+        <v>576</v>
+      </c>
+      <c r="B79" t="s">
+        <v>577</v>
+      </c>
+      <c r="C79" t="s">
+        <v>276</v>
+      </c>
+      <c r="D79" t="s">
+        <v>211</v>
+      </c>
+      <c r="E79" t="s">
+        <v>578</v>
+      </c>
+      <c r="F79" t="s">
         <v>579</v>
       </c>
-      <c r="B79" t="s">
-        <v>358</v>
-      </c>
-      <c r="C79" t="s">
-        <v>197</v>
-      </c>
-      <c r="D79" t="s">
-        <v>211</v>
-      </c>
-      <c r="E79" t="s">
+      <c r="H79" s="2" t="s">
         <v>580</v>
-      </c>
-      <c r="F79" t="s">
-        <v>360</v>
-      </c>
-      <c r="H79" s="2" t="s">
-        <v>581</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
+        <v>581</v>
+      </c>
+      <c r="B80" t="s">
+        <v>360</v>
+      </c>
+      <c r="C80" t="s">
+        <v>197</v>
+      </c>
+      <c r="D80" t="s">
+        <v>211</v>
+      </c>
+      <c r="E80" t="s">
         <v>582</v>
       </c>
-      <c r="B80" t="s">
+      <c r="F80" t="s">
+        <v>362</v>
+      </c>
+      <c r="H80" s="2" t="s">
         <v>583</v>
-      </c>
-      <c r="C80" t="s">
-        <v>276</v>
-      </c>
-      <c r="D80" t="s">
-        <v>211</v>
-      </c>
-      <c r="E80" t="s">
-        <v>584</v>
-      </c>
-      <c r="F80" t="s">
-        <v>585</v>
-      </c>
-      <c r="H80" s="2" t="s">
-        <v>586</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
+        <v>584</v>
+      </c>
+      <c r="B81" t="s">
+        <v>585</v>
+      </c>
+      <c r="C81" t="s">
+        <v>276</v>
+      </c>
+      <c r="D81" t="s">
+        <v>211</v>
+      </c>
+      <c r="E81" t="s">
+        <v>586</v>
+      </c>
+      <c r="F81" t="s">
         <v>587</v>
-      </c>
-      <c r="B81" t="s">
-        <v>234</v>
-      </c>
-      <c r="C81" t="s">
-        <v>235</v>
-      </c>
-      <c r="D81" t="s">
-        <v>211</v>
-      </c>
-      <c r="E81" t="s">
-        <v>236</v>
-      </c>
-      <c r="F81" t="s">
-        <v>237</v>
       </c>
       <c r="H81" s="2" t="s">
         <v>588</v>
@@ -5785,226 +5797,226 @@
         <v>589</v>
       </c>
       <c r="B82" t="s">
+        <v>234</v>
+      </c>
+      <c r="C82" t="s">
+        <v>235</v>
+      </c>
+      <c r="D82" t="s">
+        <v>211</v>
+      </c>
+      <c r="E82" t="s">
+        <v>236</v>
+      </c>
+      <c r="F82" t="s">
+        <v>237</v>
+      </c>
+      <c r="H82" s="2" t="s">
         <v>590</v>
-      </c>
-      <c r="C82" t="s">
-        <v>591</v>
-      </c>
-      <c r="D82" t="s">
-        <v>211</v>
-      </c>
-      <c r="E82" t="s">
-        <v>359</v>
-      </c>
-      <c r="F82" t="s">
-        <v>592</v>
-      </c>
-      <c r="H82" s="2" t="s">
-        <v>593</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
+        <v>591</v>
+      </c>
+      <c r="B83" t="s">
+        <v>592</v>
+      </c>
+      <c r="C83" t="s">
+        <v>593</v>
+      </c>
+      <c r="D83" t="s">
+        <v>211</v>
+      </c>
+      <c r="E83" t="s">
+        <v>361</v>
+      </c>
+      <c r="F83" t="s">
         <v>594</v>
       </c>
-      <c r="B83" t="s">
+      <c r="H83" s="2" t="s">
         <v>595</v>
-      </c>
-      <c r="C83" t="s">
-        <v>596</v>
-      </c>
-      <c r="D83" t="s">
-        <v>211</v>
-      </c>
-      <c r="E83" t="s">
-        <v>597</v>
-      </c>
-      <c r="F83" t="s">
-        <v>225</v>
-      </c>
-      <c r="H83" s="2" t="s">
-        <v>598</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
+        <v>596</v>
+      </c>
+      <c r="B84" t="s">
+        <v>597</v>
+      </c>
+      <c r="C84" t="s">
+        <v>598</v>
+      </c>
+      <c r="D84" t="s">
+        <v>211</v>
+      </c>
+      <c r="E84" t="s">
         <v>599</v>
       </c>
-      <c r="B84" t="s">
+      <c r="F84" t="s">
+        <v>225</v>
+      </c>
+      <c r="H84" s="2" t="s">
         <v>600</v>
-      </c>
-      <c r="C84" t="s">
-        <v>601</v>
-      </c>
-      <c r="D84" t="s">
-        <v>331</v>
-      </c>
-      <c r="E84" t="s">
-        <v>602</v>
-      </c>
-      <c r="F84" t="s">
-        <v>206</v>
-      </c>
-      <c r="H84" s="2" t="s">
-        <v>603</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
+        <v>601</v>
+      </c>
+      <c r="B85" t="s">
+        <v>602</v>
+      </c>
+      <c r="C85" t="s">
+        <v>603</v>
+      </c>
+      <c r="D85" t="s">
+        <v>331</v>
+      </c>
+      <c r="E85" t="s">
         <v>604</v>
       </c>
-      <c r="B85" t="s">
+      <c r="F85" t="s">
+        <v>206</v>
+      </c>
+      <c r="H85" s="2" t="s">
         <v>605</v>
-      </c>
-      <c r="C85" t="s">
-        <v>197</v>
-      </c>
-      <c r="D85" t="s">
-        <v>205</v>
-      </c>
-      <c r="E85" t="s">
-        <v>606</v>
-      </c>
-      <c r="F85" t="s">
-        <v>607</v>
-      </c>
-      <c r="H85" s="2" t="s">
-        <v>608</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="B86" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="C86" t="s">
         <v>197</v>
       </c>
       <c r="D86" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="E86" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="F86" t="s">
-        <v>192</v>
+        <v>609</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
+        <v>611</v>
+      </c>
+      <c r="B87" t="s">
+        <v>612</v>
+      </c>
+      <c r="C87" t="s">
+        <v>197</v>
+      </c>
+      <c r="D87" t="s">
+        <v>211</v>
+      </c>
+      <c r="E87" t="s">
         <v>613</v>
       </c>
-      <c r="B87" t="s">
+      <c r="F87" t="s">
+        <v>192</v>
+      </c>
+      <c r="H87" s="2" t="s">
         <v>614</v>
-      </c>
-      <c r="C87" t="s">
-        <v>615</v>
-      </c>
-      <c r="D87" t="s">
-        <v>211</v>
-      </c>
-      <c r="E87" t="s">
-        <v>616</v>
-      </c>
-      <c r="F87" t="s">
-        <v>617</v>
-      </c>
-      <c r="H87" s="2" t="s">
-        <v>618</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
+        <v>615</v>
+      </c>
+      <c r="B88" t="s">
+        <v>616</v>
+      </c>
+      <c r="C88" t="s">
+        <v>617</v>
+      </c>
+      <c r="D88" t="s">
+        <v>211</v>
+      </c>
+      <c r="E88" t="s">
+        <v>618</v>
+      </c>
+      <c r="F88" t="s">
         <v>619</v>
       </c>
-      <c r="B88" t="s">
+      <c r="H88" s="2" t="s">
         <v>620</v>
-      </c>
-      <c r="C88" t="s">
-        <v>276</v>
-      </c>
-      <c r="D88" t="s">
-        <v>302</v>
-      </c>
-      <c r="E88" t="s">
-        <v>621</v>
-      </c>
-      <c r="F88" t="s">
-        <v>317</v>
-      </c>
-      <c r="H88" s="2" t="s">
-        <v>622</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="B89" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="C89" t="s">
         <v>276</v>
       </c>
       <c r="D89" t="s">
-        <v>211</v>
+        <v>302</v>
       </c>
       <c r="E89" t="s">
-        <v>580</v>
+        <v>623</v>
       </c>
       <c r="F89" t="s">
-        <v>192</v>
+        <v>317</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
+        <v>625</v>
+      </c>
+      <c r="B90" t="s">
         <v>626</v>
       </c>
-      <c r="B90" t="s">
+      <c r="C90" t="s">
+        <v>276</v>
+      </c>
+      <c r="D90" t="s">
+        <v>211</v>
+      </c>
+      <c r="E90" t="s">
+        <v>582</v>
+      </c>
+      <c r="F90" t="s">
+        <v>192</v>
+      </c>
+      <c r="H90" s="2" t="s">
         <v>627</v>
-      </c>
-      <c r="C90" t="s">
-        <v>223</v>
-      </c>
-      <c r="D90" t="s">
-        <v>211</v>
-      </c>
-      <c r="E90" t="s">
-        <v>628</v>
-      </c>
-      <c r="F90" t="s">
-        <v>629</v>
-      </c>
-      <c r="H90" s="2" t="s">
-        <v>630</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
+        <v>628</v>
+      </c>
+      <c r="B91" t="s">
+        <v>629</v>
+      </c>
+      <c r="C91" t="s">
+        <v>223</v>
+      </c>
+      <c r="D91" t="s">
+        <v>211</v>
+      </c>
+      <c r="E91" t="s">
+        <v>630</v>
+      </c>
+      <c r="F91" t="s">
         <v>631</v>
-      </c>
-      <c r="B91" t="s">
-        <v>222</v>
-      </c>
-      <c r="C91" t="s">
-        <v>261</v>
-      </c>
-      <c r="D91" t="s">
-        <v>211</v>
-      </c>
-      <c r="E91" t="s">
-        <v>287</v>
-      </c>
-      <c r="F91" t="s">
-        <v>225</v>
       </c>
       <c r="H91" s="2" t="s">
         <v>632</v>
@@ -6015,272 +6027,272 @@
         <v>633</v>
       </c>
       <c r="B92" t="s">
+        <v>222</v>
+      </c>
+      <c r="C92" t="s">
+        <v>261</v>
+      </c>
+      <c r="D92" t="s">
+        <v>211</v>
+      </c>
+      <c r="E92" t="s">
+        <v>287</v>
+      </c>
+      <c r="F92" t="s">
+        <v>225</v>
+      </c>
+      <c r="H92" s="2" t="s">
         <v>634</v>
-      </c>
-      <c r="C92" t="s">
-        <v>635</v>
-      </c>
-      <c r="D92" t="s">
-        <v>211</v>
-      </c>
-      <c r="E92" t="s">
-        <v>636</v>
-      </c>
-      <c r="F92" t="s">
-        <v>284</v>
-      </c>
-      <c r="H92" s="2" t="s">
-        <v>637</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
+        <v>635</v>
+      </c>
+      <c r="B93" t="s">
+        <v>636</v>
+      </c>
+      <c r="C93" t="s">
+        <v>637</v>
+      </c>
+      <c r="D93" t="s">
+        <v>211</v>
+      </c>
+      <c r="E93" t="s">
         <v>638</v>
       </c>
-      <c r="B93" t="s">
+      <c r="F93" t="s">
+        <v>284</v>
+      </c>
+      <c r="H93" s="2" t="s">
         <v>639</v>
-      </c>
-      <c r="C93" t="s">
-        <v>197</v>
-      </c>
-      <c r="D93" t="s">
-        <v>331</v>
-      </c>
-      <c r="E93" t="s">
-        <v>640</v>
-      </c>
-      <c r="F93" t="s">
-        <v>641</v>
-      </c>
-      <c r="H93" s="2" t="s">
-        <v>642</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
+        <v>640</v>
+      </c>
+      <c r="B94" t="s">
+        <v>641</v>
+      </c>
+      <c r="C94" t="s">
+        <v>197</v>
+      </c>
+      <c r="D94" t="s">
+        <v>331</v>
+      </c>
+      <c r="E94" t="s">
+        <v>642</v>
+      </c>
+      <c r="F94" t="s">
         <v>643</v>
       </c>
-      <c r="B94" t="s">
-        <v>222</v>
-      </c>
-      <c r="C94" t="s">
-        <v>223</v>
-      </c>
-      <c r="D94" t="s">
-        <v>211</v>
-      </c>
-      <c r="E94" t="s">
+      <c r="H94" s="2" t="s">
         <v>644</v>
-      </c>
-      <c r="F94" t="s">
-        <v>225</v>
-      </c>
-      <c r="H94" s="2" t="s">
-        <v>645</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
+        <v>645</v>
+      </c>
+      <c r="B95" t="s">
+        <v>222</v>
+      </c>
+      <c r="C95" t="s">
+        <v>223</v>
+      </c>
+      <c r="D95" t="s">
+        <v>211</v>
+      </c>
+      <c r="E95" t="s">
         <v>646</v>
       </c>
-      <c r="B95" t="s">
+      <c r="F95" t="s">
+        <v>225</v>
+      </c>
+      <c r="H95" s="2" t="s">
         <v>647</v>
-      </c>
-      <c r="C95" t="s">
-        <v>235</v>
-      </c>
-      <c r="D95" t="s">
-        <v>211</v>
-      </c>
-      <c r="E95" t="s">
-        <v>648</v>
-      </c>
-      <c r="F95" t="s">
-        <v>430</v>
-      </c>
-      <c r="H95" s="2" t="s">
-        <v>649</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
+        <v>648</v>
+      </c>
+      <c r="B96" t="s">
+        <v>649</v>
+      </c>
+      <c r="C96" t="s">
+        <v>235</v>
+      </c>
+      <c r="D96" t="s">
+        <v>211</v>
+      </c>
+      <c r="E96" t="s">
         <v>650</v>
       </c>
-      <c r="B96" t="s">
+      <c r="F96" t="s">
+        <v>432</v>
+      </c>
+      <c r="H96" s="2" t="s">
         <v>651</v>
-      </c>
-      <c r="C96" t="s">
-        <v>276</v>
-      </c>
-      <c r="D96" t="s">
-        <v>211</v>
-      </c>
-      <c r="E96" t="s">
-        <v>652</v>
-      </c>
-      <c r="F96" t="s">
-        <v>653</v>
-      </c>
-      <c r="H96" s="2" t="s">
-        <v>654</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
+        <v>652</v>
+      </c>
+      <c r="B97" t="s">
+        <v>653</v>
+      </c>
+      <c r="C97" t="s">
+        <v>276</v>
+      </c>
+      <c r="D97" t="s">
+        <v>211</v>
+      </c>
+      <c r="E97" t="s">
+        <v>654</v>
+      </c>
+      <c r="F97" t="s">
         <v>655</v>
       </c>
-      <c r="B97" t="s">
+      <c r="H97" s="2" t="s">
         <v>656</v>
-      </c>
-      <c r="C97" t="s">
-        <v>210</v>
-      </c>
-      <c r="D97" t="s">
-        <v>211</v>
-      </c>
-      <c r="E97" t="s">
-        <v>558</v>
-      </c>
-      <c r="F97" t="s">
-        <v>657</v>
-      </c>
-      <c r="H97" s="2" t="s">
-        <v>658</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="B98" t="s">
+        <v>658</v>
+      </c>
+      <c r="C98" t="s">
+        <v>210</v>
+      </c>
+      <c r="D98" t="s">
+        <v>211</v>
+      </c>
+      <c r="E98" t="s">
+        <v>560</v>
+      </c>
+      <c r="F98" t="s">
         <v>659</v>
       </c>
-      <c r="C98" t="s">
-        <v>235</v>
-      </c>
-      <c r="D98" t="s">
-        <v>211</v>
-      </c>
-      <c r="E98" t="s">
+      <c r="H98" s="2" t="s">
         <v>660</v>
-      </c>
-      <c r="F98" t="s">
-        <v>661</v>
-      </c>
-      <c r="H98" s="2" t="s">
-        <v>662</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>125</v>
+        <v>657</v>
       </c>
       <c r="B99" t="s">
+        <v>661</v>
+      </c>
+      <c r="C99" t="s">
+        <v>235</v>
+      </c>
+      <c r="D99" t="s">
+        <v>211</v>
+      </c>
+      <c r="E99" t="s">
+        <v>662</v>
+      </c>
+      <c r="F99" t="s">
         <v>663</v>
       </c>
-      <c r="C99" t="s">
-        <v>197</v>
-      </c>
-      <c r="D99" t="s">
-        <v>211</v>
-      </c>
-      <c r="E99" t="s">
+      <c r="H99" s="2" t="s">
         <v>664</v>
-      </c>
-      <c r="F99" t="s">
-        <v>665</v>
-      </c>
-      <c r="H99" s="2" t="s">
-        <v>666</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
+        <v>125</v>
+      </c>
+      <c r="B100" t="s">
+        <v>665</v>
+      </c>
+      <c r="C100" t="s">
+        <v>197</v>
+      </c>
+      <c r="D100" t="s">
+        <v>211</v>
+      </c>
+      <c r="E100" t="s">
+        <v>666</v>
+      </c>
+      <c r="F100" t="s">
         <v>667</v>
       </c>
-      <c r="B100" t="s">
+      <c r="H100" s="2" t="s">
         <v>668</v>
-      </c>
-      <c r="C100" t="s">
-        <v>370</v>
-      </c>
-      <c r="D100" t="s">
-        <v>211</v>
-      </c>
-      <c r="E100" t="s">
-        <v>636</v>
-      </c>
-      <c r="F100" t="s">
-        <v>669</v>
-      </c>
-      <c r="H100" s="2" t="s">
-        <v>670</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
+        <v>669</v>
+      </c>
+      <c r="B101" t="s">
+        <v>670</v>
+      </c>
+      <c r="C101" t="s">
+        <v>372</v>
+      </c>
+      <c r="D101" t="s">
+        <v>211</v>
+      </c>
+      <c r="E101" t="s">
+        <v>638</v>
+      </c>
+      <c r="F101" t="s">
         <v>671</v>
       </c>
-      <c r="B101" t="s">
+      <c r="H101" s="2" t="s">
         <v>672</v>
-      </c>
-      <c r="C101" t="s">
-        <v>673</v>
-      </c>
-      <c r="D101" t="s">
-        <v>211</v>
-      </c>
-      <c r="E101" t="s">
-        <v>558</v>
-      </c>
-      <c r="F101" t="s">
-        <v>674</v>
-      </c>
-      <c r="H101" s="2" t="s">
-        <v>675</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
+        <v>673</v>
+      </c>
+      <c r="B102" t="s">
+        <v>674</v>
+      </c>
+      <c r="C102" t="s">
+        <v>675</v>
+      </c>
+      <c r="D102" t="s">
+        <v>211</v>
+      </c>
+      <c r="E102" t="s">
+        <v>560</v>
+      </c>
+      <c r="F102" t="s">
         <v>676</v>
       </c>
-      <c r="B102" t="s">
+      <c r="H102" s="2" t="s">
         <v>677</v>
-      </c>
-      <c r="C102" t="s">
-        <v>235</v>
-      </c>
-      <c r="D102" t="s">
-        <v>211</v>
-      </c>
-      <c r="E102" t="s">
-        <v>400</v>
-      </c>
-      <c r="F102" t="s">
-        <v>678</v>
-      </c>
-      <c r="H102" s="2" t="s">
-        <v>679</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
+        <v>678</v>
+      </c>
+      <c r="B103" t="s">
+        <v>679</v>
+      </c>
+      <c r="C103" t="s">
+        <v>235</v>
+      </c>
+      <c r="D103" t="s">
+        <v>211</v>
+      </c>
+      <c r="E103" t="s">
+        <v>402</v>
+      </c>
+      <c r="F103" t="s">
         <v>680</v>
-      </c>
-      <c r="B103" t="s">
-        <v>386</v>
-      </c>
-      <c r="C103" t="s">
-        <v>197</v>
-      </c>
-      <c r="D103" t="s">
-        <v>211</v>
-      </c>
-      <c r="E103" t="s">
-        <v>387</v>
-      </c>
-      <c r="F103" t="s">
-        <v>388</v>
       </c>
       <c r="H103" s="2" t="s">
         <v>681</v>
@@ -6291,364 +6303,364 @@
         <v>682</v>
       </c>
       <c r="B104" t="s">
+        <v>388</v>
+      </c>
+      <c r="C104" t="s">
+        <v>197</v>
+      </c>
+      <c r="D104" t="s">
+        <v>211</v>
+      </c>
+      <c r="E104" t="s">
+        <v>389</v>
+      </c>
+      <c r="F104" t="s">
+        <v>390</v>
+      </c>
+      <c r="H104" s="2" t="s">
         <v>683</v>
-      </c>
-      <c r="C104" t="s">
-        <v>276</v>
-      </c>
-      <c r="D104" t="s">
-        <v>211</v>
-      </c>
-      <c r="E104" t="s">
-        <v>400</v>
-      </c>
-      <c r="F104" t="s">
-        <v>684</v>
-      </c>
-      <c r="H104" s="2" t="s">
-        <v>685</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
+        <v>684</v>
+      </c>
+      <c r="B105" t="s">
+        <v>685</v>
+      </c>
+      <c r="C105" t="s">
+        <v>276</v>
+      </c>
+      <c r="D105" t="s">
+        <v>211</v>
+      </c>
+      <c r="E105" t="s">
+        <v>402</v>
+      </c>
+      <c r="F105" t="s">
         <v>686</v>
       </c>
-      <c r="B105" t="s">
-        <v>222</v>
-      </c>
-      <c r="C105" t="s">
+      <c r="H105" s="2" t="s">
         <v>687</v>
-      </c>
-      <c r="D105" t="s">
-        <v>211</v>
-      </c>
-      <c r="E105" t="s">
-        <v>688</v>
-      </c>
-      <c r="F105" t="s">
-        <v>225</v>
-      </c>
-      <c r="H105" s="2" t="s">
-        <v>689</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
+        <v>688</v>
+      </c>
+      <c r="B106" t="s">
+        <v>222</v>
+      </c>
+      <c r="C106" t="s">
+        <v>689</v>
+      </c>
+      <c r="D106" t="s">
+        <v>211</v>
+      </c>
+      <c r="E106" t="s">
         <v>690</v>
       </c>
-      <c r="B106" t="s">
+      <c r="F106" t="s">
+        <v>225</v>
+      </c>
+      <c r="H106" s="2" t="s">
         <v>691</v>
-      </c>
-      <c r="C106" t="s">
-        <v>692</v>
-      </c>
-      <c r="D106" t="s">
-        <v>211</v>
-      </c>
-      <c r="E106" t="s">
-        <v>693</v>
-      </c>
-      <c r="F106" t="s">
-        <v>694</v>
-      </c>
-      <c r="H106" s="2" t="s">
-        <v>695</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
+        <v>692</v>
+      </c>
+      <c r="B107" t="s">
+        <v>693</v>
+      </c>
+      <c r="C107" t="s">
+        <v>694</v>
+      </c>
+      <c r="D107" t="s">
+        <v>211</v>
+      </c>
+      <c r="E107" t="s">
+        <v>695</v>
+      </c>
+      <c r="F107" t="s">
         <v>696</v>
       </c>
-      <c r="B107" t="s">
+      <c r="H107" s="2" t="s">
         <v>697</v>
-      </c>
-      <c r="C107" t="s">
-        <v>210</v>
-      </c>
-      <c r="D107" t="s">
-        <v>211</v>
-      </c>
-      <c r="E107" t="s">
-        <v>580</v>
-      </c>
-      <c r="F107" t="s">
-        <v>698</v>
-      </c>
-      <c r="H107" s="2" t="s">
-        <v>699</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
+        <v>698</v>
+      </c>
+      <c r="B108" t="s">
+        <v>699</v>
+      </c>
+      <c r="C108" t="s">
+        <v>210</v>
+      </c>
+      <c r="D108" t="s">
+        <v>211</v>
+      </c>
+      <c r="E108" t="s">
+        <v>582</v>
+      </c>
+      <c r="F108" t="s">
         <v>700</v>
       </c>
-      <c r="B108" t="s">
+      <c r="H108" s="2" t="s">
         <v>701</v>
-      </c>
-      <c r="C108" t="s">
-        <v>702</v>
-      </c>
-      <c r="D108" t="s">
-        <v>211</v>
-      </c>
-      <c r="E108" t="s">
-        <v>192</v>
-      </c>
-      <c r="F108" t="s">
-        <v>192</v>
-      </c>
-      <c r="H108" s="2" t="s">
-        <v>703</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
+        <v>702</v>
+      </c>
+      <c r="B109" t="s">
+        <v>703</v>
+      </c>
+      <c r="C109" t="s">
         <v>704</v>
       </c>
-      <c r="B109" t="s">
+      <c r="D109" t="s">
+        <v>211</v>
+      </c>
+      <c r="E109" t="s">
+        <v>192</v>
+      </c>
+      <c r="F109" t="s">
+        <v>192</v>
+      </c>
+      <c r="H109" s="2" t="s">
         <v>705</v>
-      </c>
-      <c r="C109" t="s">
-        <v>706</v>
-      </c>
-      <c r="D109" t="s">
-        <v>282</v>
-      </c>
-      <c r="E109" t="s">
-        <v>707</v>
-      </c>
-      <c r="F109" t="s">
-        <v>465</v>
-      </c>
-      <c r="H109" s="2" t="s">
-        <v>708</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
+        <v>706</v>
+      </c>
+      <c r="B110" t="s">
+        <v>707</v>
+      </c>
+      <c r="C110" t="s">
+        <v>708</v>
+      </c>
+      <c r="D110" t="s">
+        <v>282</v>
+      </c>
+      <c r="E110" t="s">
         <v>709</v>
       </c>
-      <c r="B110" t="s">
-        <v>705</v>
-      </c>
-      <c r="C110" t="s">
-        <v>706</v>
-      </c>
-      <c r="D110" t="s">
-        <v>211</v>
-      </c>
-      <c r="E110" t="s">
+      <c r="F110" t="s">
+        <v>467</v>
+      </c>
+      <c r="H110" s="2" t="s">
         <v>710</v>
-      </c>
-      <c r="F110" t="s">
-        <v>465</v>
-      </c>
-      <c r="H110" s="2" t="s">
-        <v>711</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
+        <v>711</v>
+      </c>
+      <c r="B111" t="s">
+        <v>707</v>
+      </c>
+      <c r="C111" t="s">
+        <v>708</v>
+      </c>
+      <c r="D111" t="s">
+        <v>211</v>
+      </c>
+      <c r="E111" t="s">
         <v>712</v>
       </c>
-      <c r="B111" t="s">
+      <c r="F111" t="s">
+        <v>467</v>
+      </c>
+      <c r="H111" s="2" t="s">
         <v>713</v>
-      </c>
-      <c r="C111" t="s">
-        <v>276</v>
-      </c>
-      <c r="D111" t="s">
-        <v>211</v>
-      </c>
-      <c r="E111" t="s">
-        <v>523</v>
-      </c>
-      <c r="F111" t="s">
-        <v>714</v>
-      </c>
-      <c r="H111" s="2" t="s">
-        <v>715</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
+        <v>714</v>
+      </c>
+      <c r="B112" t="s">
+        <v>715</v>
+      </c>
+      <c r="C112" t="s">
+        <v>276</v>
+      </c>
+      <c r="D112" t="s">
+        <v>211</v>
+      </c>
+      <c r="E112" t="s">
+        <v>525</v>
+      </c>
+      <c r="F112" t="s">
         <v>716</v>
       </c>
-      <c r="B112" t="s">
+      <c r="H112" s="2" t="s">
         <v>717</v>
-      </c>
-      <c r="C112" t="s">
-        <v>246</v>
-      </c>
-      <c r="D112" t="s">
-        <v>205</v>
-      </c>
-      <c r="E112" t="s">
-        <v>365</v>
-      </c>
-      <c r="F112" t="s">
-        <v>718</v>
-      </c>
-      <c r="H112" s="2" t="s">
-        <v>719</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
+        <v>718</v>
+      </c>
+      <c r="B113" t="s">
+        <v>719</v>
+      </c>
+      <c r="C113" t="s">
+        <v>246</v>
+      </c>
+      <c r="D113" t="s">
+        <v>205</v>
+      </c>
+      <c r="E113" t="s">
+        <v>367</v>
+      </c>
+      <c r="F113" t="s">
         <v>720</v>
       </c>
-      <c r="B113" t="s">
+      <c r="H113" s="2" t="s">
         <v>721</v>
-      </c>
-      <c r="C113" t="s">
-        <v>276</v>
-      </c>
-      <c r="D113" t="s">
-        <v>282</v>
-      </c>
-      <c r="E113" t="s">
-        <v>722</v>
-      </c>
-      <c r="F113" t="s">
-        <v>206</v>
-      </c>
-      <c r="H113" s="2" t="s">
-        <v>723</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
+        <v>722</v>
+      </c>
+      <c r="B114" t="s">
+        <v>723</v>
+      </c>
+      <c r="C114" t="s">
+        <v>276</v>
+      </c>
+      <c r="D114" t="s">
+        <v>282</v>
+      </c>
+      <c r="E114" t="s">
         <v>724</v>
       </c>
-      <c r="B114" t="s">
+      <c r="F114" t="s">
+        <v>206</v>
+      </c>
+      <c r="H114" s="2" t="s">
         <v>725</v>
-      </c>
-      <c r="C114" t="s">
-        <v>726</v>
-      </c>
-      <c r="D114" t="s">
-        <v>211</v>
-      </c>
-      <c r="E114" t="s">
-        <v>727</v>
-      </c>
-      <c r="F114" t="s">
-        <v>728</v>
-      </c>
-      <c r="H114" s="2" t="s">
-        <v>729</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
+        <v>726</v>
+      </c>
+      <c r="B115" t="s">
+        <v>727</v>
+      </c>
+      <c r="C115" t="s">
+        <v>728</v>
+      </c>
+      <c r="D115" t="s">
+        <v>211</v>
+      </c>
+      <c r="E115" t="s">
+        <v>729</v>
+      </c>
+      <c r="F115" t="s">
         <v>730</v>
       </c>
-      <c r="B115" t="s">
+      <c r="H115" s="2" t="s">
         <v>731</v>
-      </c>
-      <c r="C115" t="s">
-        <v>276</v>
-      </c>
-      <c r="D115" t="s">
-        <v>211</v>
-      </c>
-      <c r="E115" t="s">
-        <v>732</v>
-      </c>
-      <c r="F115" t="s">
-        <v>733</v>
-      </c>
-      <c r="H115" s="2" t="s">
-        <v>734</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
+        <v>732</v>
+      </c>
+      <c r="B116" t="s">
+        <v>733</v>
+      </c>
+      <c r="C116" t="s">
+        <v>276</v>
+      </c>
+      <c r="D116" t="s">
+        <v>211</v>
+      </c>
+      <c r="E116" t="s">
+        <v>734</v>
+      </c>
+      <c r="F116" t="s">
         <v>735</v>
       </c>
-      <c r="B116" t="s">
+      <c r="H116" s="2" t="s">
         <v>736</v>
-      </c>
-      <c r="C116" t="s">
-        <v>737</v>
-      </c>
-      <c r="D116" t="s">
-        <v>211</v>
-      </c>
-      <c r="E116" t="s">
-        <v>738</v>
-      </c>
-      <c r="F116" t="s">
-        <v>739</v>
-      </c>
-      <c r="H116" s="2" t="s">
-        <v>740</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
+        <v>737</v>
+      </c>
+      <c r="B117" t="s">
+        <v>738</v>
+      </c>
+      <c r="C117" t="s">
+        <v>739</v>
+      </c>
+      <c r="D117" t="s">
+        <v>211</v>
+      </c>
+      <c r="E117" t="s">
+        <v>740</v>
+      </c>
+      <c r="F117" t="s">
         <v>741</v>
       </c>
-      <c r="B117" t="s">
+      <c r="H117" s="2" t="s">
         <v>742</v>
-      </c>
-      <c r="C117" t="s">
-        <v>197</v>
-      </c>
-      <c r="D117" t="s">
-        <v>211</v>
-      </c>
-      <c r="E117" t="s">
-        <v>743</v>
-      </c>
-      <c r="F117" t="s">
-        <v>430</v>
-      </c>
-      <c r="H117" s="2" t="s">
-        <v>744</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
+        <v>743</v>
+      </c>
+      <c r="B118" t="s">
+        <v>744</v>
+      </c>
+      <c r="C118" t="s">
+        <v>197</v>
+      </c>
+      <c r="D118" t="s">
+        <v>211</v>
+      </c>
+      <c r="E118" t="s">
         <v>745</v>
       </c>
-      <c r="B118" t="s">
+      <c r="F118" t="s">
+        <v>432</v>
+      </c>
+      <c r="H118" s="2" t="s">
         <v>746</v>
-      </c>
-      <c r="C118" t="s">
-        <v>210</v>
-      </c>
-      <c r="D118" t="s">
-        <v>211</v>
-      </c>
-      <c r="E118" t="s">
-        <v>747</v>
-      </c>
-      <c r="F118" t="s">
-        <v>748</v>
-      </c>
-      <c r="H118" s="2" t="s">
-        <v>749</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
+        <v>747</v>
+      </c>
+      <c r="B119" t="s">
+        <v>748</v>
+      </c>
+      <c r="C119" t="s">
+        <v>210</v>
+      </c>
+      <c r="D119" t="s">
+        <v>211</v>
+      </c>
+      <c r="E119" t="s">
+        <v>749</v>
+      </c>
+      <c r="F119" t="s">
         <v>750</v>
-      </c>
-      <c r="B119" t="s">
-        <v>677</v>
-      </c>
-      <c r="C119" t="s">
-        <v>235</v>
-      </c>
-      <c r="D119" t="s">
-        <v>211</v>
-      </c>
-      <c r="E119" t="s">
-        <v>523</v>
-      </c>
-      <c r="F119" t="s">
-        <v>678</v>
       </c>
       <c r="H119" s="2" t="s">
         <v>751</v>
@@ -6659,157 +6671,157 @@
         <v>752</v>
       </c>
       <c r="B120" t="s">
+        <v>679</v>
+      </c>
+      <c r="C120" t="s">
+        <v>235</v>
+      </c>
+      <c r="D120" t="s">
+        <v>211</v>
+      </c>
+      <c r="E120" t="s">
+        <v>525</v>
+      </c>
+      <c r="F120" t="s">
+        <v>680</v>
+      </c>
+      <c r="H120" s="2" t="s">
         <v>753</v>
-      </c>
-      <c r="C120" t="s">
-        <v>197</v>
-      </c>
-      <c r="D120" t="s">
-        <v>211</v>
-      </c>
-      <c r="E120" t="s">
-        <v>754</v>
-      </c>
-      <c r="F120" t="s">
-        <v>755</v>
-      </c>
-      <c r="H120" s="2" t="s">
-        <v>756</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
+        <v>754</v>
+      </c>
+      <c r="B121" t="s">
+        <v>755</v>
+      </c>
+      <c r="C121" t="s">
+        <v>197</v>
+      </c>
+      <c r="D121" t="s">
+        <v>211</v>
+      </c>
+      <c r="E121" t="s">
+        <v>756</v>
+      </c>
+      <c r="F121" t="s">
         <v>757</v>
       </c>
-      <c r="B121" t="s">
+      <c r="H121" s="2" t="s">
         <v>758</v>
-      </c>
-      <c r="C121" t="s">
-        <v>499</v>
-      </c>
-      <c r="D121" t="s">
-        <v>211</v>
-      </c>
-      <c r="E121" t="s">
-        <v>192</v>
-      </c>
-      <c r="F121" t="s">
-        <v>192</v>
-      </c>
-      <c r="H121" s="2" t="s">
-        <v>759</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
+        <v>759</v>
+      </c>
+      <c r="B122" t="s">
         <v>760</v>
       </c>
-      <c r="B122" t="s">
-        <v>300</v>
-      </c>
       <c r="C122" t="s">
-        <v>301</v>
+        <v>501</v>
       </c>
       <c r="D122" t="s">
         <v>211</v>
       </c>
       <c r="E122" t="s">
+        <v>192</v>
+      </c>
+      <c r="F122" t="s">
+        <v>192</v>
+      </c>
+      <c r="H122" s="2" t="s">
         <v>761</v>
-      </c>
-      <c r="F122" t="s">
-        <v>252</v>
-      </c>
-      <c r="H122" s="2" t="s">
-        <v>762</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
+        <v>762</v>
+      </c>
+      <c r="B123" t="s">
+        <v>300</v>
+      </c>
+      <c r="C123" t="s">
+        <v>301</v>
+      </c>
+      <c r="D123" t="s">
+        <v>211</v>
+      </c>
+      <c r="E123" t="s">
         <v>763</v>
       </c>
-      <c r="B123" t="s">
-        <v>527</v>
-      </c>
-      <c r="C123" t="s">
-        <v>336</v>
-      </c>
-      <c r="D123" t="s">
-        <v>211</v>
-      </c>
-      <c r="E123" t="s">
+      <c r="F123" t="s">
+        <v>252</v>
+      </c>
+      <c r="H123" s="2" t="s">
         <v>764</v>
-      </c>
-      <c r="F123" t="s">
-        <v>765</v>
-      </c>
-      <c r="H123" s="2" t="s">
-        <v>766</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
+        <v>765</v>
+      </c>
+      <c r="B124" t="s">
+        <v>529</v>
+      </c>
+      <c r="C124" t="s">
+        <v>336</v>
+      </c>
+      <c r="D124" t="s">
+        <v>211</v>
+      </c>
+      <c r="E124" t="s">
+        <v>766</v>
+      </c>
+      <c r="F124" t="s">
         <v>767</v>
       </c>
-      <c r="B124" t="s">
+      <c r="H124" s="2" t="s">
         <v>768</v>
-      </c>
-      <c r="C124" t="s">
-        <v>197</v>
-      </c>
-      <c r="D124" t="s">
-        <v>205</v>
-      </c>
-      <c r="E124" t="s">
-        <v>769</v>
-      </c>
-      <c r="F124" t="s">
-        <v>770</v>
-      </c>
-      <c r="H124" s="2" t="s">
-        <v>771</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
+        <v>769</v>
+      </c>
+      <c r="B125" t="s">
+        <v>770</v>
+      </c>
+      <c r="C125" t="s">
+        <v>197</v>
+      </c>
+      <c r="D125" t="s">
+        <v>205</v>
+      </c>
+      <c r="E125" t="s">
+        <v>771</v>
+      </c>
+      <c r="F125" t="s">
         <v>772</v>
       </c>
-      <c r="B125" t="s">
+      <c r="H125" s="2" t="s">
         <v>773</v>
-      </c>
-      <c r="C125" t="s">
-        <v>774</v>
-      </c>
-      <c r="D125" t="s">
-        <v>211</v>
-      </c>
-      <c r="E125" t="s">
-        <v>775</v>
-      </c>
-      <c r="F125" t="s">
-        <v>192</v>
-      </c>
-      <c r="H125" s="2" t="s">
-        <v>776</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
+        <v>774</v>
+      </c>
+      <c r="B126" t="s">
+        <v>775</v>
+      </c>
+      <c r="C126" t="s">
+        <v>776</v>
+      </c>
+      <c r="D126" t="s">
+        <v>211</v>
+      </c>
+      <c r="E126" t="s">
         <v>777</v>
       </c>
-      <c r="B126" t="s">
-        <v>222</v>
-      </c>
-      <c r="C126" t="s">
-        <v>223</v>
-      </c>
-      <c r="D126" t="s">
-        <v>211</v>
-      </c>
-      <c r="E126" t="s">
-        <v>519</v>
-      </c>
       <c r="F126" t="s">
-        <v>225</v>
+        <v>192</v>
       </c>
       <c r="H126" s="2" t="s">
         <v>778</v>
@@ -6820,79 +6832,79 @@
         <v>779</v>
       </c>
       <c r="B127" t="s">
+        <v>222</v>
+      </c>
+      <c r="C127" t="s">
+        <v>223</v>
+      </c>
+      <c r="D127" t="s">
+        <v>211</v>
+      </c>
+      <c r="E127" t="s">
+        <v>521</v>
+      </c>
+      <c r="F127" t="s">
+        <v>225</v>
+      </c>
+      <c r="H127" s="2" t="s">
         <v>780</v>
-      </c>
-      <c r="C127" t="s">
-        <v>348</v>
-      </c>
-      <c r="D127" t="s">
-        <v>211</v>
-      </c>
-      <c r="E127" t="s">
-        <v>303</v>
-      </c>
-      <c r="F127" t="s">
-        <v>781</v>
-      </c>
-      <c r="H127" s="2" t="s">
-        <v>782</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
+        <v>781</v>
+      </c>
+      <c r="B128" t="s">
+        <v>782</v>
+      </c>
+      <c r="C128" t="s">
+        <v>348</v>
+      </c>
+      <c r="D128" t="s">
+        <v>211</v>
+      </c>
+      <c r="E128" t="s">
+        <v>303</v>
+      </c>
+      <c r="F128" t="s">
         <v>783</v>
       </c>
-      <c r="B128" t="s">
+      <c r="H128" s="2" t="s">
         <v>784</v>
-      </c>
-      <c r="C128" t="s">
-        <v>785</v>
-      </c>
-      <c r="D128" t="s">
-        <v>211</v>
-      </c>
-      <c r="E128" t="s">
-        <v>786</v>
-      </c>
-      <c r="F128" t="s">
-        <v>787</v>
-      </c>
-      <c r="H128" s="2" t="s">
-        <v>788</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
+        <v>785</v>
+      </c>
+      <c r="B129" t="s">
+        <v>786</v>
+      </c>
+      <c r="C129" t="s">
+        <v>787</v>
+      </c>
+      <c r="D129" t="s">
+        <v>211</v>
+      </c>
+      <c r="E129" t="s">
+        <v>788</v>
+      </c>
+      <c r="F129" t="s">
         <v>789</v>
       </c>
-      <c r="B129" t="s">
-        <v>240</v>
-      </c>
-      <c r="C129" t="s">
+      <c r="H129" s="2" t="s">
         <v>790</v>
-      </c>
-      <c r="D129" t="s">
-        <v>211</v>
-      </c>
-      <c r="E129" t="s">
-        <v>192</v>
-      </c>
-      <c r="F129" t="s">
-        <v>242</v>
-      </c>
-      <c r="H129" s="2" t="s">
-        <v>791</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="B130" t="s">
         <v>240</v>
       </c>
       <c r="C130" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="D130" t="s">
         <v>211</v>
@@ -6912,203 +6924,203 @@
         <v>794</v>
       </c>
       <c r="B131" t="s">
+        <v>240</v>
+      </c>
+      <c r="C131" t="s">
+        <v>792</v>
+      </c>
+      <c r="D131" t="s">
+        <v>211</v>
+      </c>
+      <c r="E131" t="s">
+        <v>192</v>
+      </c>
+      <c r="F131" t="s">
+        <v>242</v>
+      </c>
+      <c r="H131" s="2" t="s">
         <v>795</v>
-      </c>
-      <c r="C131" t="s">
-        <v>235</v>
-      </c>
-      <c r="D131" t="s">
-        <v>205</v>
-      </c>
-      <c r="E131" t="s">
-        <v>796</v>
-      </c>
-      <c r="F131" t="s">
-        <v>797</v>
-      </c>
-      <c r="H131" s="2" t="s">
-        <v>798</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="B132" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="C132" t="s">
-        <v>197</v>
+        <v>235</v>
       </c>
       <c r="D132" t="s">
         <v>205</v>
       </c>
       <c r="E132" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
       <c r="F132" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="H132" s="2" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="B133" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="C133" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="D133" t="s">
         <v>205</v>
       </c>
       <c r="E133" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="F133" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="H133" s="2" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
+        <v>806</v>
+      </c>
+      <c r="B134" t="s">
+        <v>807</v>
+      </c>
+      <c r="C134" t="s">
+        <v>210</v>
+      </c>
+      <c r="D134" t="s">
+        <v>205</v>
+      </c>
+      <c r="E134" t="s">
+        <v>808</v>
+      </c>
+      <c r="F134" t="s">
         <v>809</v>
       </c>
-      <c r="B134" t="s">
+      <c r="H134" s="2" t="s">
         <v>810</v>
-      </c>
-      <c r="C134" t="s">
-        <v>276</v>
-      </c>
-      <c r="D134" t="s">
-        <v>211</v>
-      </c>
-      <c r="E134" t="s">
-        <v>811</v>
-      </c>
-      <c r="F134" t="s">
-        <v>317</v>
-      </c>
-      <c r="H134" s="2" t="s">
-        <v>812</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
+        <v>811</v>
+      </c>
+      <c r="B135" t="s">
+        <v>812</v>
+      </c>
+      <c r="C135" t="s">
+        <v>276</v>
+      </c>
+      <c r="D135" t="s">
+        <v>211</v>
+      </c>
+      <c r="E135" t="s">
         <v>813</v>
       </c>
-      <c r="B135" t="s">
-        <v>325</v>
-      </c>
-      <c r="C135" t="s">
-        <v>197</v>
-      </c>
-      <c r="D135" t="s">
-        <v>211</v>
-      </c>
-      <c r="E135" t="s">
+      <c r="F135" t="s">
+        <v>317</v>
+      </c>
+      <c r="H135" s="2" t="s">
         <v>814</v>
-      </c>
-      <c r="F135" t="s">
-        <v>327</v>
-      </c>
-      <c r="H135" s="2" t="s">
-        <v>815</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
+        <v>811</v>
+      </c>
+      <c r="B136" t="s">
+        <v>815</v>
+      </c>
+      <c r="C136" t="s">
+        <v>276</v>
+      </c>
+      <c r="D136" t="s">
+        <v>211</v>
+      </c>
+      <c r="E136" t="s">
+        <v>813</v>
+      </c>
+      <c r="F136" t="s">
+        <v>317</v>
+      </c>
+      <c r="H136" s="2" t="s">
         <v>816</v>
-      </c>
-      <c r="B136" t="s">
-        <v>341</v>
-      </c>
-      <c r="C136" t="s">
-        <v>377</v>
-      </c>
-      <c r="D136" t="s">
-        <v>211</v>
-      </c>
-      <c r="E136" t="s">
-        <v>817</v>
-      </c>
-      <c r="F136" t="s">
-        <v>344</v>
-      </c>
-      <c r="H136" s="2" t="s">
-        <v>818</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
+        <v>817</v>
+      </c>
+      <c r="B137" t="s">
+        <v>325</v>
+      </c>
+      <c r="C137" t="s">
+        <v>197</v>
+      </c>
+      <c r="D137" t="s">
+        <v>211</v>
+      </c>
+      <c r="E137" t="s">
+        <v>818</v>
+      </c>
+      <c r="F137" t="s">
+        <v>327</v>
+      </c>
+      <c r="H137" s="2" t="s">
         <v>819</v>
-      </c>
-      <c r="B137" t="s">
-        <v>341</v>
-      </c>
-      <c r="C137" t="s">
-        <v>377</v>
-      </c>
-      <c r="D137" t="s">
-        <v>211</v>
-      </c>
-      <c r="E137" t="s">
-        <v>817</v>
-      </c>
-      <c r="F137" t="s">
-        <v>401</v>
-      </c>
-      <c r="H137" s="2" t="s">
-        <v>820</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="B138" t="s">
         <v>341</v>
       </c>
       <c r="C138" t="s">
-        <v>342</v>
+        <v>379</v>
       </c>
       <c r="D138" t="s">
         <v>211</v>
       </c>
       <c r="E138" t="s">
-        <v>817</v>
+        <v>821</v>
       </c>
       <c r="F138" t="s">
-        <v>401</v>
+        <v>344</v>
       </c>
       <c r="H138" s="2" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="B139" t="s">
         <v>341</v>
       </c>
       <c r="C139" t="s">
-        <v>342</v>
+        <v>379</v>
       </c>
       <c r="D139" t="s">
         <v>211</v>
       </c>
       <c r="E139" t="s">
-        <v>817</v>
+        <v>821</v>
       </c>
       <c r="F139" t="s">
-        <v>823</v>
+        <v>403</v>
       </c>
       <c r="H139" s="2" t="s">
         <v>824</v>
@@ -7116,151 +7128,151 @@
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
+        <v>823</v>
+      </c>
+      <c r="B140" t="s">
+        <v>341</v>
+      </c>
+      <c r="C140" t="s">
+        <v>342</v>
+      </c>
+      <c r="D140" t="s">
+        <v>211</v>
+      </c>
+      <c r="E140" t="s">
+        <v>821</v>
+      </c>
+      <c r="F140" t="s">
+        <v>403</v>
+      </c>
+      <c r="H140" s="2" t="s">
         <v>825</v>
-      </c>
-      <c r="B140" t="s">
-        <v>826</v>
-      </c>
-      <c r="C140" t="s">
-        <v>197</v>
-      </c>
-      <c r="D140" t="s">
-        <v>211</v>
-      </c>
-      <c r="E140" t="s">
-        <v>192</v>
-      </c>
-      <c r="F140" t="s">
-        <v>192</v>
-      </c>
-      <c r="H140" s="2" t="s">
-        <v>827</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
+        <v>826</v>
+      </c>
+      <c r="B141" t="s">
+        <v>341</v>
+      </c>
+      <c r="C141" t="s">
+        <v>342</v>
+      </c>
+      <c r="D141" t="s">
+        <v>211</v>
+      </c>
+      <c r="E141" t="s">
+        <v>821</v>
+      </c>
+      <c r="F141" t="s">
+        <v>827</v>
+      </c>
+      <c r="H141" s="2" t="s">
         <v>828</v>
-      </c>
-      <c r="B141" t="s">
-        <v>829</v>
-      </c>
-      <c r="C141" t="s">
-        <v>830</v>
-      </c>
-      <c r="D141" t="s">
-        <v>302</v>
-      </c>
-      <c r="E141" t="s">
-        <v>831</v>
-      </c>
-      <c r="F141" t="s">
-        <v>832</v>
-      </c>
-      <c r="H141" s="2" t="s">
-        <v>833</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
       <c r="B142" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="C142" t="s">
-        <v>499</v>
+        <v>197</v>
       </c>
       <c r="D142" t="s">
         <v>211</v>
       </c>
       <c r="E142" t="s">
-        <v>836</v>
+        <v>192</v>
       </c>
       <c r="F142" t="s">
-        <v>837</v>
+        <v>192</v>
       </c>
       <c r="H142" s="2" t="s">
-        <v>838</v>
+        <v>831</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>839</v>
+        <v>832</v>
       </c>
       <c r="B143" t="s">
-        <v>840</v>
+        <v>833</v>
       </c>
       <c r="C143" t="s">
-        <v>223</v>
+        <v>834</v>
       </c>
       <c r="D143" t="s">
-        <v>211</v>
+        <v>302</v>
       </c>
       <c r="E143" t="s">
-        <v>841</v>
+        <v>835</v>
       </c>
       <c r="F143" t="s">
-        <v>842</v>
+        <v>836</v>
       </c>
       <c r="H143" s="2" t="s">
-        <v>843</v>
+        <v>837</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>844</v>
+        <v>838</v>
       </c>
       <c r="B144" t="s">
-        <v>488</v>
+        <v>839</v>
       </c>
       <c r="C144" t="s">
-        <v>845</v>
+        <v>501</v>
       </c>
       <c r="D144" t="s">
-        <v>331</v>
+        <v>211</v>
       </c>
       <c r="E144" t="s">
-        <v>192</v>
+        <v>840</v>
       </c>
       <c r="F144" t="s">
-        <v>846</v>
+        <v>841</v>
       </c>
       <c r="H144" s="2" t="s">
-        <v>847</v>
+        <v>842</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>848</v>
+        <v>843</v>
       </c>
       <c r="B145" t="s">
-        <v>488</v>
+        <v>844</v>
       </c>
       <c r="C145" t="s">
-        <v>849</v>
+        <v>223</v>
       </c>
       <c r="D145" t="s">
-        <v>331</v>
+        <v>211</v>
       </c>
       <c r="E145" t="s">
-        <v>192</v>
+        <v>845</v>
       </c>
       <c r="F145" t="s">
         <v>846</v>
       </c>
       <c r="H145" s="2" t="s">
-        <v>850</v>
+        <v>847</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
       <c r="B146" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="C146" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="D146" t="s">
         <v>331</v>
@@ -7269,10 +7281,56 @@
         <v>192</v>
       </c>
       <c r="F146" t="s">
-        <v>846</v>
+        <v>850</v>
       </c>
       <c r="H146" s="2" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>852</v>
+      </c>
+      <c r="B147" t="s">
+        <v>490</v>
+      </c>
+      <c r="C147" t="s">
         <v>853</v>
+      </c>
+      <c r="D147" t="s">
+        <v>331</v>
+      </c>
+      <c r="E147" t="s">
+        <v>192</v>
+      </c>
+      <c r="F147" t="s">
+        <v>850</v>
+      </c>
+      <c r="H147" s="2" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>855</v>
+      </c>
+      <c r="B148" t="s">
+        <v>490</v>
+      </c>
+      <c r="C148" t="s">
+        <v>856</v>
+      </c>
+      <c r="D148" t="s">
+        <v>331</v>
+      </c>
+      <c r="E148" t="s">
+        <v>192</v>
+      </c>
+      <c r="F148" t="s">
+        <v>850</v>
+      </c>
+      <c r="H148" s="2" t="s">
+        <v>857</v>
       </c>
     </row>
   </sheetData>
@@ -7423,6 +7481,8 @@
     <hyperlink ref="H144" r:id="rId143"/>
     <hyperlink ref="H145" r:id="rId144"/>
     <hyperlink ref="H146" r:id="rId145"/>
+    <hyperlink ref="H147" r:id="rId146"/>
+    <hyperlink ref="H148" r:id="rId147"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
